--- a/data/nelly_inventory.xlsx
+++ b/data/nelly_inventory.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -562,6 +562,25 @@
         <v>0</v>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>4788189</v>
+      </c>
+      <c r="C7" t="n">
+        <v>5945947</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -573,112 +592,112 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CY6"/>
+  <dimension ref="A1:CY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
-    <col width="34" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="31" customWidth="1" min="6" max="6"/>
-    <col width="42" customWidth="1" min="7" max="7"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
     <col width="33" customWidth="1" min="8" max="8"/>
-    <col width="35" customWidth="1" min="9" max="9"/>
-    <col width="38" customWidth="1" min="10" max="10"/>
-    <col width="24" customWidth="1" min="11" max="11"/>
-    <col width="31" customWidth="1" min="12" max="12"/>
-    <col width="28" customWidth="1" min="13" max="13"/>
-    <col width="28" customWidth="1" min="14" max="14"/>
-    <col width="25" customWidth="1" min="15" max="15"/>
+    <col width="28" customWidth="1" min="9" max="9"/>
+    <col width="35" customWidth="1" min="10" max="10"/>
+    <col width="28" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="12" max="12"/>
+    <col width="24" customWidth="1" min="13" max="13"/>
+    <col width="24" customWidth="1" min="14" max="14"/>
+    <col width="29" customWidth="1" min="15" max="15"/>
     <col width="29" customWidth="1" min="16" max="16"/>
-    <col width="24" customWidth="1" min="17" max="17"/>
-    <col width="35" customWidth="1" min="18" max="18"/>
-    <col width="37" customWidth="1" min="19" max="19"/>
-    <col width="23" customWidth="1" min="20" max="20"/>
-    <col width="37" customWidth="1" min="21" max="21"/>
-    <col width="29" customWidth="1" min="22" max="22"/>
-    <col width="24" customWidth="1" min="23" max="23"/>
-    <col width="29" customWidth="1" min="24" max="24"/>
-    <col width="24" customWidth="1" min="25" max="25"/>
-    <col width="30" customWidth="1" min="26" max="26"/>
-    <col width="34" customWidth="1" min="27" max="27"/>
-    <col width="16" customWidth="1" min="28" max="28"/>
+    <col width="35" customWidth="1" min="17" max="17"/>
+    <col width="31" customWidth="1" min="18" max="18"/>
+    <col width="26" customWidth="1" min="19" max="19"/>
+    <col width="30" customWidth="1" min="20" max="20"/>
+    <col width="35" customWidth="1" min="21" max="21"/>
+    <col width="24" customWidth="1" min="22" max="22"/>
+    <col width="25" customWidth="1" min="23" max="23"/>
+    <col width="25" customWidth="1" min="24" max="24"/>
+    <col width="34" customWidth="1" min="25" max="25"/>
+    <col width="36" customWidth="1" min="26" max="26"/>
+    <col width="30" customWidth="1" min="27" max="27"/>
+    <col width="31" customWidth="1" min="28" max="28"/>
     <col width="33" customWidth="1" min="29" max="29"/>
-    <col width="25" customWidth="1" min="30" max="30"/>
-    <col width="27" customWidth="1" min="31" max="31"/>
-    <col width="31" customWidth="1" min="32" max="32"/>
-    <col width="25" customWidth="1" min="33" max="33"/>
-    <col width="33" customWidth="1" min="34" max="34"/>
-    <col width="24" customWidth="1" min="35" max="35"/>
-    <col width="35" customWidth="1" min="36" max="36"/>
-    <col width="24" customWidth="1" min="37" max="37"/>
-    <col width="35" customWidth="1" min="38" max="38"/>
-    <col width="23" customWidth="1" min="39" max="39"/>
-    <col width="34" customWidth="1" min="40" max="40"/>
-    <col width="29" customWidth="1" min="41" max="41"/>
-    <col width="39" customWidth="1" min="42" max="42"/>
-    <col width="26" customWidth="1" min="43" max="43"/>
-    <col width="30" customWidth="1" min="44" max="44"/>
-    <col width="40" customWidth="1" min="45" max="45"/>
-    <col width="28" customWidth="1" min="46" max="46"/>
-    <col width="36" customWidth="1" min="47" max="47"/>
-    <col width="28" customWidth="1" min="48" max="48"/>
-    <col width="40" customWidth="1" min="49" max="49"/>
-    <col width="16" customWidth="1" min="50" max="50"/>
-    <col width="26" customWidth="1" min="51" max="51"/>
-    <col width="23" customWidth="1" min="52" max="52"/>
-    <col width="40" customWidth="1" min="53" max="53"/>
-    <col width="23" customWidth="1" min="54" max="54"/>
-    <col width="34" customWidth="1" min="55" max="55"/>
-    <col width="22" customWidth="1" min="56" max="56"/>
-    <col width="31" customWidth="1" min="57" max="57"/>
-    <col width="42" customWidth="1" min="58" max="58"/>
+    <col width="28" customWidth="1" min="30" max="30"/>
+    <col width="25" customWidth="1" min="31" max="31"/>
+    <col width="22" customWidth="1" min="32" max="32"/>
+    <col width="37" customWidth="1" min="33" max="33"/>
+    <col width="40" customWidth="1" min="34" max="34"/>
+    <col width="42" customWidth="1" min="35" max="35"/>
+    <col width="31" customWidth="1" min="36" max="36"/>
+    <col width="37" customWidth="1" min="37" max="37"/>
+    <col width="29" customWidth="1" min="38" max="38"/>
+    <col width="33" customWidth="1" min="39" max="39"/>
+    <col width="40" customWidth="1" min="40" max="40"/>
+    <col width="34" customWidth="1" min="41" max="41"/>
+    <col width="38" customWidth="1" min="42" max="42"/>
+    <col width="39" customWidth="1" min="43" max="43"/>
+    <col width="23" customWidth="1" min="44" max="44"/>
+    <col width="27" customWidth="1" min="45" max="45"/>
+    <col width="16" customWidth="1" min="46" max="46"/>
+    <col width="29" customWidth="1" min="47" max="47"/>
+    <col width="40" customWidth="1" min="48" max="48"/>
+    <col width="16" customWidth="1" min="49" max="49"/>
+    <col width="23" customWidth="1" min="50" max="50"/>
+    <col width="34" customWidth="1" min="51" max="51"/>
+    <col width="26" customWidth="1" min="52" max="52"/>
+    <col width="23" customWidth="1" min="53" max="53"/>
+    <col width="24" customWidth="1" min="54" max="54"/>
+    <col width="35" customWidth="1" min="55" max="55"/>
+    <col width="23" customWidth="1" min="56" max="56"/>
+    <col width="28" customWidth="1" min="57" max="57"/>
+    <col width="24" customWidth="1" min="58" max="58"/>
     <col width="33" customWidth="1" min="59" max="59"/>
-    <col width="35" customWidth="1" min="60" max="60"/>
-    <col width="38" customWidth="1" min="61" max="61"/>
-    <col width="24" customWidth="1" min="62" max="62"/>
-    <col width="31" customWidth="1" min="63" max="63"/>
-    <col width="28" customWidth="1" min="64" max="64"/>
-    <col width="28" customWidth="1" min="65" max="65"/>
-    <col width="25" customWidth="1" min="66" max="66"/>
+    <col width="28" customWidth="1" min="60" max="60"/>
+    <col width="35" customWidth="1" min="61" max="61"/>
+    <col width="28" customWidth="1" min="62" max="62"/>
+    <col width="24" customWidth="1" min="63" max="63"/>
+    <col width="24" customWidth="1" min="64" max="64"/>
+    <col width="24" customWidth="1" min="65" max="65"/>
+    <col width="29" customWidth="1" min="66" max="66"/>
     <col width="29" customWidth="1" min="67" max="67"/>
-    <col width="24" customWidth="1" min="68" max="68"/>
-    <col width="35" customWidth="1" min="69" max="69"/>
-    <col width="37" customWidth="1" min="70" max="70"/>
-    <col width="23" customWidth="1" min="71" max="71"/>
-    <col width="37" customWidth="1" min="72" max="72"/>
-    <col width="29" customWidth="1" min="73" max="73"/>
-    <col width="24" customWidth="1" min="74" max="74"/>
-    <col width="29" customWidth="1" min="75" max="75"/>
-    <col width="24" customWidth="1" min="76" max="76"/>
-    <col width="30" customWidth="1" min="77" max="77"/>
-    <col width="34" customWidth="1" min="78" max="78"/>
-    <col width="16" customWidth="1" min="79" max="79"/>
+    <col width="35" customWidth="1" min="68" max="68"/>
+    <col width="31" customWidth="1" min="69" max="69"/>
+    <col width="26" customWidth="1" min="70" max="70"/>
+    <col width="30" customWidth="1" min="71" max="71"/>
+    <col width="35" customWidth="1" min="72" max="72"/>
+    <col width="24" customWidth="1" min="73" max="73"/>
+    <col width="25" customWidth="1" min="74" max="74"/>
+    <col width="25" customWidth="1" min="75" max="75"/>
+    <col width="34" customWidth="1" min="76" max="76"/>
+    <col width="36" customWidth="1" min="77" max="77"/>
+    <col width="30" customWidth="1" min="78" max="78"/>
+    <col width="31" customWidth="1" min="79" max="79"/>
     <col width="33" customWidth="1" min="80" max="80"/>
-    <col width="25" customWidth="1" min="81" max="81"/>
-    <col width="27" customWidth="1" min="82" max="82"/>
-    <col width="31" customWidth="1" min="83" max="83"/>
-    <col width="25" customWidth="1" min="84" max="84"/>
-    <col width="33" customWidth="1" min="85" max="85"/>
-    <col width="24" customWidth="1" min="86" max="86"/>
-    <col width="35" customWidth="1" min="87" max="87"/>
-    <col width="24" customWidth="1" min="88" max="88"/>
-    <col width="35" customWidth="1" min="89" max="89"/>
-    <col width="23" customWidth="1" min="90" max="90"/>
-    <col width="34" customWidth="1" min="91" max="91"/>
-    <col width="29" customWidth="1" min="92" max="92"/>
-    <col width="39" customWidth="1" min="93" max="93"/>
-    <col width="26" customWidth="1" min="94" max="94"/>
-    <col width="30" customWidth="1" min="95" max="95"/>
-    <col width="40" customWidth="1" min="96" max="96"/>
-    <col width="28" customWidth="1" min="97" max="97"/>
-    <col width="36" customWidth="1" min="98" max="98"/>
-    <col width="28" customWidth="1" min="99" max="99"/>
-    <col width="40" customWidth="1" min="100" max="100"/>
-    <col width="16" customWidth="1" min="101" max="101"/>
-    <col width="26" customWidth="1" min="102" max="102"/>
-    <col width="23" customWidth="1" min="103" max="103"/>
+    <col width="28" customWidth="1" min="81" max="81"/>
+    <col width="25" customWidth="1" min="82" max="82"/>
+    <col width="22" customWidth="1" min="83" max="83"/>
+    <col width="37" customWidth="1" min="84" max="84"/>
+    <col width="40" customWidth="1" min="85" max="85"/>
+    <col width="42" customWidth="1" min="86" max="86"/>
+    <col width="31" customWidth="1" min="87" max="87"/>
+    <col width="37" customWidth="1" min="88" max="88"/>
+    <col width="29" customWidth="1" min="89" max="89"/>
+    <col width="33" customWidth="1" min="90" max="90"/>
+    <col width="40" customWidth="1" min="91" max="91"/>
+    <col width="34" customWidth="1" min="92" max="92"/>
+    <col width="38" customWidth="1" min="93" max="93"/>
+    <col width="39" customWidth="1" min="94" max="94"/>
+    <col width="23" customWidth="1" min="95" max="95"/>
+    <col width="27" customWidth="1" min="96" max="96"/>
+    <col width="16" customWidth="1" min="97" max="97"/>
+    <col width="29" customWidth="1" min="98" max="98"/>
+    <col width="40" customWidth="1" min="99" max="99"/>
+    <col width="16" customWidth="1" min="100" max="100"/>
+    <col width="23" customWidth="1" min="101" max="101"/>
+    <col width="34" customWidth="1" min="102" max="102"/>
+    <col width="26" customWidth="1" min="103" max="103"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -689,512 +708,512 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Kläder&gt;Jeans (Sell)</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Skor&gt;Sneakers (Sell)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Kläder&gt;Toppar &amp; T-shirts (Sell)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Kläder&gt;Byxor (Sell)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Kläder&gt;Klänningar (Sell)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Kläder&gt;Tröjor (Sell)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Kläder&gt;Jackor &amp; Kappor (Sell)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Badkläder&gt;Bikinis (Sell)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Kläder&gt;Blusar &amp; Skjortor (Sell)</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Kläder&gt;Loungewear (Sell)</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Kläder&gt;Kjolar (Sell)</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Kläder&gt;Shorts (Sell)</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Kläder&gt;Jackor (Sell)</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Accessoarer&gt;Väskor (Sell)</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Kläder&gt;Underkläder (Sell)</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Kläder&gt;Kavajer &amp; Blazers (Sell)</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Skor&gt;Flats &amp; Lågskor (Sell)</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Kläder&gt;Skjortor (Sell)</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Skor&gt;Boots &amp; Kängor (Sell)</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Kläder&gt;T-Shirts &amp; Linnen (Sell)</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Skor&gt;Sandaler (Sell)</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Kläder&gt;Stickat (Sell)</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Skor&gt;Klackskor (Sell)</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Accessoarer&gt;Solglasögon (Sell)</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Kläder&gt;Kavajer &amp; Kostymer (Sell)</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>Accessoarer&gt;Smycken (Sell)</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>Sport&gt;Träningskläder (Sell)</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>Badkläder&gt;Strandkläder (Sell)</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>Kläder&gt;Nattkläder (Sell)</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>Skor&gt;Platåskor (Sell)</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>Kläder&gt;Piké (Sell)</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>Accessoarer&gt;Bälten &amp; Skärp (Sell)</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>Kläder&gt;Strumpor &amp; Strumpbyxor (Sell)</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>Accessoarer&gt;Halsdukar &amp; Scarves (Sell)</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>Badkläder&gt;Baddräkter (Sell)</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>Accessoarer&gt;Håraccessoarer (Sell)</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>Accessoarer&gt;Kepsar (Sell)</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>Accessoarer&gt;Bag Charms (Sell)</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>Accessoarer&gt;Handskar &amp; Vantar (Sell)</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>Accessoarer&gt;Herrsmycken (Sell)</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>Accessoarer&gt;Mössor &amp; Kepsar (Sell)</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>Accessoarer&gt;Tech accessoarer (Sell)</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>Skor&gt;Finskor (Sell)</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>Kläder&gt;Badkläder (Sell)</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>Sport (Sell)</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>Accessoarer&gt;Mössor (Sell)</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
           <t>Kläder&gt;Sovkläder &amp; Loungewear (Sell)</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Kläder&gt;Byxor (Sell)</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>Other (Sell)</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>Skor&gt;Tofflor (Sell)</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>Kläder&gt;Jumpsuits &amp; Sets (Sell)</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Kläder&gt;Piké (Sell)</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Skor&gt;Flats &amp; Lågskor (Sell)</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Accessoarer&gt;Halsdukar &amp; Scarves (Sell)</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Badkläder&gt;Strandkläder (Sell)</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Kläder&gt;Toppar &amp; T-shirts (Sell)</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Accessoarer&gt;Mössor &amp; Kepsar (Sell)</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Kläder&gt;Shorts (Sell)</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Sport&gt;Träningskläder (Sell)</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Kläder&gt;Loungewear (Sell)</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Kläder&gt;Nattkläder (Sell)</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>Skor&gt;Platåskor (Sell)</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>Accessoarer&gt;Väskor (Sell)</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>Kläder&gt;Jackor (Sell)</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>Kläder&gt;Kavajer &amp; Blazers (Sell)</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>Accessoarer&gt;Bälten &amp; Skärp (Sell)</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>Skor&gt;Finskor (Sell)</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>Accessoarer&gt;Håraccessoarer (Sell)</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>Accessoarer&gt;Kepsar (Sell)</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>Kläder&gt;Kjolar (Sell)</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>Accessoarer&gt;Mössor (Sell)</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>Skor&gt;Sneakers (Sell)</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>Skor&gt;Boots &amp; Kängor (Sell)</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>Accessoarer&gt;Solglasögon (Sell)</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>Other (Sell)</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>Accessoarer&gt;Bag Charms (Sell)</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>Skor&gt;Klackskor (Sell)</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>Kläder&gt;Badkläder (Sell)</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>Badkläder&gt;Baddräkter (Sell)</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>Kläder&gt;Stickat (Sell)</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>Kläder&gt;Jackor &amp; Kappor (Sell)</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>Kläder&gt;Tröjor (Sell)</t>
-        </is>
-      </c>
-      <c r="AJ1" s="1" t="inlineStr">
-        <is>
-          <t>Kläder&gt;Blusar &amp; Skjortor (Sell)</t>
-        </is>
-      </c>
-      <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>Skor&gt;Sandaler (Sell)</t>
-        </is>
-      </c>
-      <c r="AL1" s="1" t="inlineStr">
-        <is>
-          <t>Kläder&gt;T-Shirts &amp; Linnen (Sell)</t>
-        </is>
-      </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>Skor&gt;Tofflor (Sell)</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
-        <is>
-          <t>Accessoarer&gt;Herrsmycken (Sell)</t>
-        </is>
-      </c>
-      <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>Kläder&gt;Underkläder (Sell)</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>Accessoarer&gt;Tech accessoarer (Sell)</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>Skor&gt;Flip-Flops (Sell)</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>Accessoarer&gt;Smycken (Sell)</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>Kläder&gt;Strumpor &amp; Strumpbyxor (Sell)</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>Kläder&gt;Klänningar (Sell)</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>Kläder&gt;Kavajer &amp; Kostymer (Sell)</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>Badkläder&gt;Bikinis (Sell)</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>Accessoarer&gt;Handskar &amp; Vantar (Sell)</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>Sport (Sell)</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>Kläder&gt;Skjortor (Sell)</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>Kläder&gt;Jeans (Sell)</t>
-        </is>
-      </c>
       <c r="BA1" s="1" t="inlineStr">
         <is>
+          <t>Kläder&gt;Jeans (List)</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>Skor&gt;Sneakers (List)</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>Kläder&gt;Toppar &amp; T-shirts (List)</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>Kläder&gt;Byxor (List)</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>Kläder&gt;Klänningar (List)</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>Kläder&gt;Tröjor (List)</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>Kläder&gt;Jackor &amp; Kappor (List)</t>
+        </is>
+      </c>
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>Badkläder&gt;Bikinis (List)</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>Kläder&gt;Blusar &amp; Skjortor (List)</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>Kläder&gt;Loungewear (List)</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>Kläder&gt;Kjolar (List)</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>Kläder&gt;Shorts (List)</t>
+        </is>
+      </c>
+      <c r="BM1" s="1" t="inlineStr">
+        <is>
+          <t>Kläder&gt;Jackor (List)</t>
+        </is>
+      </c>
+      <c r="BN1" s="1" t="inlineStr">
+        <is>
+          <t>Accessoarer&gt;Väskor (List)</t>
+        </is>
+      </c>
+      <c r="BO1" s="1" t="inlineStr">
+        <is>
+          <t>Kläder&gt;Underkläder (List)</t>
+        </is>
+      </c>
+      <c r="BP1" s="1" t="inlineStr">
+        <is>
+          <t>Kläder&gt;Kavajer &amp; Blazers (List)</t>
+        </is>
+      </c>
+      <c r="BQ1" s="1" t="inlineStr">
+        <is>
+          <t>Skor&gt;Flats &amp; Lågskor (List)</t>
+        </is>
+      </c>
+      <c r="BR1" s="1" t="inlineStr">
+        <is>
+          <t>Kläder&gt;Skjortor (List)</t>
+        </is>
+      </c>
+      <c r="BS1" s="1" t="inlineStr">
+        <is>
+          <t>Skor&gt;Boots &amp; Kängor (List)</t>
+        </is>
+      </c>
+      <c r="BT1" s="1" t="inlineStr">
+        <is>
+          <t>Kläder&gt;T-Shirts &amp; Linnen (List)</t>
+        </is>
+      </c>
+      <c r="BU1" s="1" t="inlineStr">
+        <is>
+          <t>Skor&gt;Sandaler (List)</t>
+        </is>
+      </c>
+      <c r="BV1" s="1" t="inlineStr">
+        <is>
+          <t>Kläder&gt;Stickat (List)</t>
+        </is>
+      </c>
+      <c r="BW1" s="1" t="inlineStr">
+        <is>
+          <t>Skor&gt;Klackskor (List)</t>
+        </is>
+      </c>
+      <c r="BX1" s="1" t="inlineStr">
+        <is>
+          <t>Accessoarer&gt;Solglasögon (List)</t>
+        </is>
+      </c>
+      <c r="BY1" s="1" t="inlineStr">
+        <is>
+          <t>Kläder&gt;Kavajer &amp; Kostymer (List)</t>
+        </is>
+      </c>
+      <c r="BZ1" s="1" t="inlineStr">
+        <is>
+          <t>Accessoarer&gt;Smycken (List)</t>
+        </is>
+      </c>
+      <c r="CA1" s="1" t="inlineStr">
+        <is>
+          <t>Sport&gt;Träningskläder (List)</t>
+        </is>
+      </c>
+      <c r="CB1" s="1" t="inlineStr">
+        <is>
+          <t>Badkläder&gt;Strandkläder (List)</t>
+        </is>
+      </c>
+      <c r="CC1" s="1" t="inlineStr">
+        <is>
+          <t>Kläder&gt;Nattkläder (List)</t>
+        </is>
+      </c>
+      <c r="CD1" s="1" t="inlineStr">
+        <is>
+          <t>Skor&gt;Platåskor (List)</t>
+        </is>
+      </c>
+      <c r="CE1" s="1" t="inlineStr">
+        <is>
+          <t>Kläder&gt;Piké (List)</t>
+        </is>
+      </c>
+      <c r="CF1" s="1" t="inlineStr">
+        <is>
+          <t>Accessoarer&gt;Bälten &amp; Skärp (List)</t>
+        </is>
+      </c>
+      <c r="CG1" s="1" t="inlineStr">
+        <is>
+          <t>Kläder&gt;Strumpor &amp; Strumpbyxor (List)</t>
+        </is>
+      </c>
+      <c r="CH1" s="1" t="inlineStr">
+        <is>
+          <t>Accessoarer&gt;Halsdukar &amp; Scarves (List)</t>
+        </is>
+      </c>
+      <c r="CI1" s="1" t="inlineStr">
+        <is>
+          <t>Badkläder&gt;Baddräkter (List)</t>
+        </is>
+      </c>
+      <c r="CJ1" s="1" t="inlineStr">
+        <is>
+          <t>Accessoarer&gt;Håraccessoarer (List)</t>
+        </is>
+      </c>
+      <c r="CK1" s="1" t="inlineStr">
+        <is>
+          <t>Accessoarer&gt;Kepsar (List)</t>
+        </is>
+      </c>
+      <c r="CL1" s="1" t="inlineStr">
+        <is>
+          <t>Accessoarer&gt;Bag Charms (List)</t>
+        </is>
+      </c>
+      <c r="CM1" s="1" t="inlineStr">
+        <is>
+          <t>Accessoarer&gt;Handskar &amp; Vantar (List)</t>
+        </is>
+      </c>
+      <c r="CN1" s="1" t="inlineStr">
+        <is>
+          <t>Accessoarer&gt;Herrsmycken (List)</t>
+        </is>
+      </c>
+      <c r="CO1" s="1" t="inlineStr">
+        <is>
+          <t>Accessoarer&gt;Mössor &amp; Kepsar (List)</t>
+        </is>
+      </c>
+      <c r="CP1" s="1" t="inlineStr">
+        <is>
+          <t>Accessoarer&gt;Tech accessoarer (List)</t>
+        </is>
+      </c>
+      <c r="CQ1" s="1" t="inlineStr">
+        <is>
+          <t>Skor&gt;Finskor (List)</t>
+        </is>
+      </c>
+      <c r="CR1" s="1" t="inlineStr">
+        <is>
+          <t>Kläder&gt;Badkläder (List)</t>
+        </is>
+      </c>
+      <c r="CS1" s="1" t="inlineStr">
+        <is>
+          <t>Sport (List)</t>
+        </is>
+      </c>
+      <c r="CT1" s="1" t="inlineStr">
+        <is>
+          <t>Accessoarer&gt;Mössor (List)</t>
+        </is>
+      </c>
+      <c r="CU1" s="1" t="inlineStr">
+        <is>
           <t>Kläder&gt;Sovkläder &amp; Loungewear (List)</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>Kläder&gt;Byxor (List)</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="CV1" s="1" t="inlineStr">
+        <is>
+          <t>Other (List)</t>
+        </is>
+      </c>
+      <c r="CW1" s="1" t="inlineStr">
+        <is>
+          <t>Skor&gt;Tofflor (List)</t>
+        </is>
+      </c>
+      <c r="CX1" s="1" t="inlineStr">
         <is>
           <t>Kläder&gt;Jumpsuits &amp; Sets (List)</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>Kläder&gt;Piké (List)</t>
-        </is>
-      </c>
-      <c r="BE1" s="1" t="inlineStr">
-        <is>
-          <t>Skor&gt;Flats &amp; Lågskor (List)</t>
-        </is>
-      </c>
-      <c r="BF1" s="1" t="inlineStr">
-        <is>
-          <t>Accessoarer&gt;Halsdukar &amp; Scarves (List)</t>
-        </is>
-      </c>
-      <c r="BG1" s="1" t="inlineStr">
-        <is>
-          <t>Badkläder&gt;Strandkläder (List)</t>
-        </is>
-      </c>
-      <c r="BH1" s="1" t="inlineStr">
-        <is>
-          <t>Kläder&gt;Toppar &amp; T-shirts (List)</t>
-        </is>
-      </c>
-      <c r="BI1" s="1" t="inlineStr">
-        <is>
-          <t>Accessoarer&gt;Mössor &amp; Kepsar (List)</t>
-        </is>
-      </c>
-      <c r="BJ1" s="1" t="inlineStr">
-        <is>
-          <t>Kläder&gt;Shorts (List)</t>
-        </is>
-      </c>
-      <c r="BK1" s="1" t="inlineStr">
-        <is>
-          <t>Sport&gt;Träningskläder (List)</t>
-        </is>
-      </c>
-      <c r="BL1" s="1" t="inlineStr">
-        <is>
-          <t>Kläder&gt;Loungewear (List)</t>
-        </is>
-      </c>
-      <c r="BM1" s="1" t="inlineStr">
-        <is>
-          <t>Kläder&gt;Nattkläder (List)</t>
-        </is>
-      </c>
-      <c r="BN1" s="1" t="inlineStr">
-        <is>
-          <t>Skor&gt;Platåskor (List)</t>
-        </is>
-      </c>
-      <c r="BO1" s="1" t="inlineStr">
-        <is>
-          <t>Accessoarer&gt;Väskor (List)</t>
-        </is>
-      </c>
-      <c r="BP1" s="1" t="inlineStr">
-        <is>
-          <t>Kläder&gt;Jackor (List)</t>
-        </is>
-      </c>
-      <c r="BQ1" s="1" t="inlineStr">
-        <is>
-          <t>Kläder&gt;Kavajer &amp; Blazers (List)</t>
-        </is>
-      </c>
-      <c r="BR1" s="1" t="inlineStr">
-        <is>
-          <t>Accessoarer&gt;Bälten &amp; Skärp (List)</t>
-        </is>
-      </c>
-      <c r="BS1" s="1" t="inlineStr">
-        <is>
-          <t>Skor&gt;Finskor (List)</t>
-        </is>
-      </c>
-      <c r="BT1" s="1" t="inlineStr">
-        <is>
-          <t>Accessoarer&gt;Håraccessoarer (List)</t>
-        </is>
-      </c>
-      <c r="BU1" s="1" t="inlineStr">
-        <is>
-          <t>Accessoarer&gt;Kepsar (List)</t>
-        </is>
-      </c>
-      <c r="BV1" s="1" t="inlineStr">
-        <is>
-          <t>Kläder&gt;Kjolar (List)</t>
-        </is>
-      </c>
-      <c r="BW1" s="1" t="inlineStr">
-        <is>
-          <t>Accessoarer&gt;Mössor (List)</t>
-        </is>
-      </c>
-      <c r="BX1" s="1" t="inlineStr">
-        <is>
-          <t>Skor&gt;Sneakers (List)</t>
-        </is>
-      </c>
-      <c r="BY1" s="1" t="inlineStr">
-        <is>
-          <t>Skor&gt;Boots &amp; Kängor (List)</t>
-        </is>
-      </c>
-      <c r="BZ1" s="1" t="inlineStr">
-        <is>
-          <t>Accessoarer&gt;Solglasögon (List)</t>
-        </is>
-      </c>
-      <c r="CA1" s="1" t="inlineStr">
-        <is>
-          <t>Other (List)</t>
-        </is>
-      </c>
-      <c r="CB1" s="1" t="inlineStr">
-        <is>
-          <t>Accessoarer&gt;Bag Charms (List)</t>
-        </is>
-      </c>
-      <c r="CC1" s="1" t="inlineStr">
-        <is>
-          <t>Skor&gt;Klackskor (List)</t>
-        </is>
-      </c>
-      <c r="CD1" s="1" t="inlineStr">
-        <is>
-          <t>Kläder&gt;Badkläder (List)</t>
-        </is>
-      </c>
-      <c r="CE1" s="1" t="inlineStr">
-        <is>
-          <t>Badkläder&gt;Baddräkter (List)</t>
-        </is>
-      </c>
-      <c r="CF1" s="1" t="inlineStr">
-        <is>
-          <t>Kläder&gt;Stickat (List)</t>
-        </is>
-      </c>
-      <c r="CG1" s="1" t="inlineStr">
-        <is>
-          <t>Kläder&gt;Jackor &amp; Kappor (List)</t>
-        </is>
-      </c>
-      <c r="CH1" s="1" t="inlineStr">
-        <is>
-          <t>Kläder&gt;Tröjor (List)</t>
-        </is>
-      </c>
-      <c r="CI1" s="1" t="inlineStr">
-        <is>
-          <t>Kläder&gt;Blusar &amp; Skjortor (List)</t>
-        </is>
-      </c>
-      <c r="CJ1" s="1" t="inlineStr">
-        <is>
-          <t>Skor&gt;Sandaler (List)</t>
-        </is>
-      </c>
-      <c r="CK1" s="1" t="inlineStr">
-        <is>
-          <t>Kläder&gt;T-Shirts &amp; Linnen (List)</t>
-        </is>
-      </c>
-      <c r="CL1" s="1" t="inlineStr">
-        <is>
-          <t>Skor&gt;Tofflor (List)</t>
-        </is>
-      </c>
-      <c r="CM1" s="1" t="inlineStr">
-        <is>
-          <t>Accessoarer&gt;Herrsmycken (List)</t>
-        </is>
-      </c>
-      <c r="CN1" s="1" t="inlineStr">
-        <is>
-          <t>Kläder&gt;Underkläder (List)</t>
-        </is>
-      </c>
-      <c r="CO1" s="1" t="inlineStr">
-        <is>
-          <t>Accessoarer&gt;Tech accessoarer (List)</t>
-        </is>
-      </c>
-      <c r="CP1" s="1" t="inlineStr">
+      <c r="CY1" s="1" t="inlineStr">
         <is>
           <t>Skor&gt;Flip-Flops (List)</t>
-        </is>
-      </c>
-      <c r="CQ1" s="1" t="inlineStr">
-        <is>
-          <t>Accessoarer&gt;Smycken (List)</t>
-        </is>
-      </c>
-      <c r="CR1" s="1" t="inlineStr">
-        <is>
-          <t>Kläder&gt;Strumpor &amp; Strumpbyxor (List)</t>
-        </is>
-      </c>
-      <c r="CS1" s="1" t="inlineStr">
-        <is>
-          <t>Kläder&gt;Klänningar (List)</t>
-        </is>
-      </c>
-      <c r="CT1" s="1" t="inlineStr">
-        <is>
-          <t>Kläder&gt;Kavajer &amp; Kostymer (List)</t>
-        </is>
-      </c>
-      <c r="CU1" s="1" t="inlineStr">
-        <is>
-          <t>Badkläder&gt;Bikinis (List)</t>
-        </is>
-      </c>
-      <c r="CV1" s="1" t="inlineStr">
-        <is>
-          <t>Accessoarer&gt;Handskar &amp; Vantar (List)</t>
-        </is>
-      </c>
-      <c r="CW1" s="1" t="inlineStr">
-        <is>
-          <t>Sport (List)</t>
-        </is>
-      </c>
-      <c r="CX1" s="1" t="inlineStr">
-        <is>
-          <t>Kläder&gt;Skjortor (List)</t>
-        </is>
-      </c>
-      <c r="CY1" s="1" t="inlineStr">
-        <is>
-          <t>Kläder&gt;Jeans (List)</t>
         </is>
       </c>
     </row>
@@ -1518,310 +1537,310 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>898883</v>
       </c>
       <c r="C3" t="n">
+        <v>587055</v>
+      </c>
+      <c r="D3" t="n">
+        <v>329934</v>
+      </c>
+      <c r="E3" t="n">
         <v>396112</v>
       </c>
-      <c r="D3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
+        <v>228008</v>
+      </c>
+      <c r="G3" t="n">
+        <v>395959</v>
+      </c>
+      <c r="H3" t="n">
+        <v>207571</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>146693</v>
+      </c>
+      <c r="K3" t="n">
+        <v>127684</v>
+      </c>
+      <c r="L3" t="n">
+        <v>61336</v>
+      </c>
+      <c r="M3" t="n">
+        <v>67339</v>
+      </c>
+      <c r="N3" t="n">
+        <v>100633</v>
+      </c>
+      <c r="O3" t="n">
+        <v>50963</v>
+      </c>
+      <c r="P3" t="n">
+        <v>80844</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>36991</v>
+      </c>
+      <c r="R3" t="n">
+        <v>37070</v>
+      </c>
+      <c r="S3" t="n">
+        <v>73593</v>
+      </c>
+      <c r="T3" t="n">
+        <v>37285</v>
+      </c>
+      <c r="U3" t="n">
+        <v>49729</v>
+      </c>
+      <c r="V3" t="n">
+        <v>35008</v>
+      </c>
+      <c r="W3" t="n">
+        <v>25260</v>
+      </c>
+      <c r="X3" t="n">
+        <v>21182</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>6769</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1999</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>24186</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>2494</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>6332</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>4347</v>
+      </c>
+      <c r="AF3" t="n">
         <v>15284</v>
       </c>
-      <c r="F3" t="n">
-        <v>37070</v>
-      </c>
-      <c r="G3" t="n">
+      <c r="AG3" t="n">
+        <v>7078</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>3023</v>
+      </c>
+      <c r="AI3" t="n">
         <v>2493</v>
       </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" t="n">
-        <v>329934</v>
-      </c>
-      <c r="J3" t="n">
+      <c r="AJ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>1175</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>599</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>707</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>238</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>299</v>
+      </c>
+      <c r="AP3" t="n">
         <v>119</v>
       </c>
-      <c r="K3" t="n">
-        <v>67339</v>
-      </c>
-      <c r="L3" t="n">
+      <c r="AQ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>4598</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>7496</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>993055</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>604111</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>361040</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>425875</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>273379</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>418692</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>223827</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>159932</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>127684</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>70803</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>73046</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>101633</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>52213</v>
+      </c>
+      <c r="BO3" t="n">
+        <v>86032</v>
+      </c>
+      <c r="BP3" t="n">
+        <v>38364</v>
+      </c>
+      <c r="BQ3" t="n">
+        <v>40335</v>
+      </c>
+      <c r="BR3" t="n">
+        <v>79368</v>
+      </c>
+      <c r="BS3" t="n">
+        <v>42195</v>
+      </c>
+      <c r="BT3" t="n">
+        <v>50749</v>
+      </c>
+      <c r="BU3" t="n">
+        <v>35258</v>
+      </c>
+      <c r="BV3" t="n">
+        <v>33620</v>
+      </c>
+      <c r="BW3" t="n">
+        <v>27287</v>
+      </c>
+      <c r="BX3" t="n">
+        <v>7329</v>
+      </c>
+      <c r="BY3" t="n">
+        <v>1999</v>
+      </c>
+      <c r="BZ3" t="n">
+        <v>24186</v>
+      </c>
+      <c r="CA3" t="n">
         <v>2494</v>
       </c>
-      <c r="M3" t="n">
-        <v>127684</v>
-      </c>
-      <c r="N3" t="n">
-        <v>6332</v>
-      </c>
-      <c r="O3" t="n">
+      <c r="CB3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC3" t="n">
+        <v>7634</v>
+      </c>
+      <c r="CD3" t="n">
         <v>4347</v>
       </c>
-      <c r="P3" t="n">
-        <v>50963</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>100633</v>
-      </c>
-      <c r="R3" t="n">
-        <v>36991</v>
-      </c>
-      <c r="S3" t="n">
-        <v>7078</v>
-      </c>
-      <c r="T3" t="n">
+      <c r="CE3" t="n">
+        <v>17169</v>
+      </c>
+      <c r="CF3" t="n">
+        <v>7541</v>
+      </c>
+      <c r="CG3" t="n">
+        <v>3173</v>
+      </c>
+      <c r="CH3" t="n">
+        <v>2493</v>
+      </c>
+      <c r="CI3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ3" t="n">
+        <v>1365</v>
+      </c>
+      <c r="CK3" t="n">
+        <v>599</v>
+      </c>
+      <c r="CL3" t="n">
+        <v>707</v>
+      </c>
+      <c r="CM3" t="n">
+        <v>238</v>
+      </c>
+      <c r="CN3" t="n">
+        <v>499</v>
+      </c>
+      <c r="CO3" t="n">
+        <v>200</v>
+      </c>
+      <c r="CP3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ3" t="n">
         <v>4598</v>
       </c>
-      <c r="U3" t="n">
-        <v>1175</v>
-      </c>
-      <c r="V3" t="n">
-        <v>599</v>
-      </c>
-      <c r="W3" t="n">
-        <v>61336</v>
-      </c>
-      <c r="X3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>587055</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>37285</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>6769</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>707</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>21182</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>25260</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>207571</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>395959</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>146693</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>35008</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>49729</v>
-      </c>
-      <c r="AM3" t="n">
+      <c r="CR3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW3" t="n">
         <v>7496</v>
       </c>
-      <c r="AN3" t="n">
-        <v>299</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>80844</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>24186</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>3023</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>228008</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>1999</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>238</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>73593</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>898883</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>425875</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>17169</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>40335</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>2493</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH3" t="n">
-        <v>361040</v>
-      </c>
-      <c r="BI3" t="n">
-        <v>200</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>73046</v>
-      </c>
-      <c r="BK3" t="n">
-        <v>2494</v>
-      </c>
-      <c r="BL3" t="n">
-        <v>127684</v>
-      </c>
-      <c r="BM3" t="n">
-        <v>7634</v>
-      </c>
-      <c r="BN3" t="n">
-        <v>4347</v>
-      </c>
-      <c r="BO3" t="n">
-        <v>52213</v>
-      </c>
-      <c r="BP3" t="n">
-        <v>101633</v>
-      </c>
-      <c r="BQ3" t="n">
-        <v>38364</v>
-      </c>
-      <c r="BR3" t="n">
-        <v>7541</v>
-      </c>
-      <c r="BS3" t="n">
-        <v>4598</v>
-      </c>
-      <c r="BT3" t="n">
-        <v>1365</v>
-      </c>
-      <c r="BU3" t="n">
-        <v>599</v>
-      </c>
-      <c r="BV3" t="n">
-        <v>70803</v>
-      </c>
-      <c r="BW3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX3" t="n">
-        <v>604111</v>
-      </c>
-      <c r="BY3" t="n">
-        <v>42195</v>
-      </c>
-      <c r="BZ3" t="n">
-        <v>7329</v>
-      </c>
-      <c r="CA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB3" t="n">
-        <v>707</v>
-      </c>
-      <c r="CC3" t="n">
-        <v>27287</v>
-      </c>
-      <c r="CD3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF3" t="n">
-        <v>33620</v>
-      </c>
-      <c r="CG3" t="n">
-        <v>223827</v>
-      </c>
-      <c r="CH3" t="n">
-        <v>418692</v>
-      </c>
-      <c r="CI3" t="n">
-        <v>159932</v>
-      </c>
-      <c r="CJ3" t="n">
-        <v>35258</v>
-      </c>
-      <c r="CK3" t="n">
-        <v>50749</v>
-      </c>
-      <c r="CL3" t="n">
-        <v>7496</v>
-      </c>
-      <c r="CM3" t="n">
-        <v>499</v>
-      </c>
-      <c r="CN3" t="n">
-        <v>86032</v>
-      </c>
-      <c r="CO3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ3" t="n">
-        <v>24186</v>
-      </c>
-      <c r="CR3" t="n">
-        <v>3173</v>
-      </c>
-      <c r="CS3" t="n">
-        <v>273379</v>
-      </c>
-      <c r="CT3" t="n">
-        <v>1999</v>
-      </c>
-      <c r="CU3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CV3" t="n">
-        <v>238</v>
-      </c>
-      <c r="CW3" t="n">
-        <v>0</v>
-      </c>
       <c r="CX3" t="n">
-        <v>79368</v>
+        <v>0</v>
       </c>
       <c r="CY3" t="n">
-        <v>993055</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -1831,310 +1850,310 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>961758</v>
       </c>
       <c r="C4" t="n">
+        <v>730742</v>
+      </c>
+      <c r="D4" t="n">
+        <v>433947</v>
+      </c>
+      <c r="E4" t="n">
         <v>504865</v>
       </c>
-      <c r="D4" t="n">
+      <c r="F4" t="n">
+        <v>231963</v>
+      </c>
+      <c r="G4" t="n">
+        <v>421318</v>
+      </c>
+      <c r="H4" t="n">
+        <v>286834</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>151074</v>
+      </c>
+      <c r="K4" t="n">
+        <v>194941</v>
+      </c>
+      <c r="L4" t="n">
+        <v>60245</v>
+      </c>
+      <c r="M4" t="n">
+        <v>61562</v>
+      </c>
+      <c r="N4" t="n">
+        <v>75341</v>
+      </c>
+      <c r="O4" t="n">
+        <v>47978</v>
+      </c>
+      <c r="P4" t="n">
+        <v>67239</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>58973</v>
+      </c>
+      <c r="R4" t="n">
+        <v>32246</v>
+      </c>
+      <c r="S4" t="n">
+        <v>217598</v>
+      </c>
+      <c r="T4" t="n">
+        <v>24405</v>
+      </c>
+      <c r="U4" t="n">
+        <v>116190</v>
+      </c>
+      <c r="V4" t="n">
+        <v>24659</v>
+      </c>
+      <c r="W4" t="n">
+        <v>39013</v>
+      </c>
+      <c r="X4" t="n">
+        <v>26881</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>21030</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>1999</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>16702</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1495</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>10252</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>8860</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>1706</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>2757</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>2607</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>1145</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>1294</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1383</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>-240</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>349</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>600</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>249</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>1899</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>1699</v>
+      </c>
+      <c r="AY4" t="n">
         <v>-449</v>
       </c>
-      <c r="E4" t="n">
-        <v>8860</v>
-      </c>
-      <c r="F4" t="n">
-        <v>32246</v>
-      </c>
-      <c r="G4" t="n">
+      <c r="AZ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>1056554</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>736222</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>476212</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>531286</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>279352</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>453007</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>306138</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>165065</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>194941</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>70166</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>67059</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>79252</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>49518</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>71423</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>60409</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>34311</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>217648</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>29753</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>117225</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>28119</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>52773</v>
+      </c>
+      <c r="BW4" t="n">
+        <v>29331</v>
+      </c>
+      <c r="BX4" t="n">
+        <v>21380</v>
+      </c>
+      <c r="BY4" t="n">
+        <v>1999</v>
+      </c>
+      <c r="BZ4" t="n">
+        <v>16827</v>
+      </c>
+      <c r="CA4" t="n">
+        <v>895</v>
+      </c>
+      <c r="CB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC4" t="n">
+        <v>11645</v>
+      </c>
+      <c r="CD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE4" t="n">
+        <v>8478</v>
+      </c>
+      <c r="CF4" t="n">
+        <v>1931</v>
+      </c>
+      <c r="CG4" t="n">
+        <v>2782</v>
+      </c>
+      <c r="CH4" t="n">
         <v>2607</v>
       </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>433947</v>
-      </c>
-      <c r="J4" t="n">
+      <c r="CI4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ4" t="n">
+        <v>1145</v>
+      </c>
+      <c r="CK4" t="n">
+        <v>1294</v>
+      </c>
+      <c r="CL4" t="n">
+        <v>1383</v>
+      </c>
+      <c r="CM4" t="n">
+        <v>-240</v>
+      </c>
+      <c r="CN4" t="n">
+        <v>349</v>
+      </c>
+      <c r="CO4" t="n">
         <v>600</v>
       </c>
-      <c r="K4" t="n">
-        <v>61562</v>
-      </c>
-      <c r="L4" t="n">
-        <v>1495</v>
-      </c>
-      <c r="M4" t="n">
-        <v>194941</v>
-      </c>
-      <c r="N4" t="n">
-        <v>10252</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>47978</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>75341</v>
-      </c>
-      <c r="R4" t="n">
-        <v>58973</v>
-      </c>
-      <c r="S4" t="n">
-        <v>1706</v>
-      </c>
-      <c r="T4" t="n">
+      <c r="CP4" t="n">
+        <v>249</v>
+      </c>
+      <c r="CQ4" t="n">
         <v>1899</v>
       </c>
-      <c r="U4" t="n">
-        <v>1145</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1294</v>
-      </c>
-      <c r="W4" t="n">
-        <v>60245</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>730742</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>24405</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>21030</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>1383</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>26881</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>39013</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>286834</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>421318</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>151074</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>24659</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>116190</v>
-      </c>
-      <c r="AM4" t="n">
+      <c r="CR4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW4" t="n">
         <v>1699</v>
       </c>
-      <c r="AN4" t="n">
-        <v>349</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>67239</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>249</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>16702</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>2757</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>231963</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>1999</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>-240</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>217598</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>961758</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>531286</v>
-      </c>
-      <c r="BC4" t="n">
+      <c r="CX4" t="n">
         <v>-449</v>
       </c>
-      <c r="BD4" t="n">
-        <v>8478</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>34311</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>2607</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>476212</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>600</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>67059</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>895</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>194941</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>11645</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO4" t="n">
-        <v>49518</v>
-      </c>
-      <c r="BP4" t="n">
-        <v>79252</v>
-      </c>
-      <c r="BQ4" t="n">
-        <v>60409</v>
-      </c>
-      <c r="BR4" t="n">
-        <v>1931</v>
-      </c>
-      <c r="BS4" t="n">
-        <v>1899</v>
-      </c>
-      <c r="BT4" t="n">
-        <v>1145</v>
-      </c>
-      <c r="BU4" t="n">
-        <v>1294</v>
-      </c>
-      <c r="BV4" t="n">
-        <v>70166</v>
-      </c>
-      <c r="BW4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX4" t="n">
-        <v>736222</v>
-      </c>
-      <c r="BY4" t="n">
-        <v>29753</v>
-      </c>
-      <c r="BZ4" t="n">
-        <v>21380</v>
-      </c>
-      <c r="CA4" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB4" t="n">
-        <v>1383</v>
-      </c>
-      <c r="CC4" t="n">
-        <v>29331</v>
-      </c>
-      <c r="CD4" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE4" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF4" t="n">
-        <v>52773</v>
-      </c>
-      <c r="CG4" t="n">
-        <v>306138</v>
-      </c>
-      <c r="CH4" t="n">
-        <v>453007</v>
-      </c>
-      <c r="CI4" t="n">
-        <v>165065</v>
-      </c>
-      <c r="CJ4" t="n">
-        <v>28119</v>
-      </c>
-      <c r="CK4" t="n">
-        <v>117225</v>
-      </c>
-      <c r="CL4" t="n">
-        <v>1699</v>
-      </c>
-      <c r="CM4" t="n">
-        <v>349</v>
-      </c>
-      <c r="CN4" t="n">
-        <v>71423</v>
-      </c>
-      <c r="CO4" t="n">
-        <v>249</v>
-      </c>
-      <c r="CP4" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ4" t="n">
-        <v>16827</v>
-      </c>
-      <c r="CR4" t="n">
-        <v>2782</v>
-      </c>
-      <c r="CS4" t="n">
-        <v>279352</v>
-      </c>
-      <c r="CT4" t="n">
-        <v>1999</v>
-      </c>
-      <c r="CU4" t="n">
-        <v>0</v>
-      </c>
-      <c r="CV4" t="n">
-        <v>-240</v>
-      </c>
-      <c r="CW4" t="n">
-        <v>0</v>
-      </c>
-      <c r="CX4" t="n">
-        <v>217648</v>
-      </c>
       <c r="CY4" t="n">
-        <v>1056554</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -2144,310 +2163,310 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>713526</v>
       </c>
       <c r="C5" t="n">
+        <v>690356</v>
+      </c>
+      <c r="D5" t="n">
+        <v>328243</v>
+      </c>
+      <c r="E5" t="n">
         <v>367286</v>
       </c>
-      <c r="D5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
+        <v>144287</v>
+      </c>
+      <c r="G5" t="n">
+        <v>345498</v>
+      </c>
+      <c r="H5" t="n">
+        <v>288730</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>116926</v>
+      </c>
+      <c r="K5" t="n">
+        <v>133483</v>
+      </c>
+      <c r="L5" t="n">
+        <v>56893</v>
+      </c>
+      <c r="M5" t="n">
+        <v>74303</v>
+      </c>
+      <c r="N5" t="n">
+        <v>68098</v>
+      </c>
+      <c r="O5" t="n">
+        <v>69556</v>
+      </c>
+      <c r="P5" t="n">
+        <v>48017</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>38842</v>
+      </c>
+      <c r="R5" t="n">
+        <v>24236</v>
+      </c>
+      <c r="S5" t="n">
+        <v>58934</v>
+      </c>
+      <c r="T5" t="n">
+        <v>36208</v>
+      </c>
+      <c r="U5" t="n">
+        <v>64592</v>
+      </c>
+      <c r="V5" t="n">
+        <v>19520</v>
+      </c>
+      <c r="W5" t="n">
+        <v>27278</v>
+      </c>
+      <c r="X5" t="n">
+        <v>22365</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>26214</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>5496</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>17872</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>9663</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>3944</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>7453</v>
+      </c>
+      <c r="AF5" t="n">
         <v>10005</v>
       </c>
-      <c r="F5" t="n">
-        <v>24236</v>
-      </c>
-      <c r="G5" t="n">
+      <c r="AG5" t="n">
+        <v>3791</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>1966</v>
+      </c>
+      <c r="AI5" t="n">
         <v>2642</v>
       </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>328243</v>
-      </c>
-      <c r="J5" t="n">
+      <c r="AJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>2329</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>359</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>645</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>921</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP5" t="n">
         <v>-209</v>
       </c>
-      <c r="K5" t="n">
-        <v>74303</v>
-      </c>
-      <c r="L5" t="n">
-        <v>9663</v>
-      </c>
-      <c r="M5" t="n">
-        <v>133483</v>
-      </c>
-      <c r="N5" t="n">
-        <v>3944</v>
-      </c>
-      <c r="O5" t="n">
-        <v>7453</v>
-      </c>
-      <c r="P5" t="n">
-        <v>69556</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>68098</v>
-      </c>
-      <c r="R5" t="n">
-        <v>38842</v>
-      </c>
-      <c r="S5" t="n">
-        <v>3791</v>
-      </c>
-      <c r="T5" t="n">
+      <c r="AQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR5" t="n">
         <v>3158</v>
       </c>
-      <c r="U5" t="n">
-        <v>2329</v>
-      </c>
-      <c r="V5" t="n">
-        <v>359</v>
-      </c>
-      <c r="W5" t="n">
-        <v>56893</v>
-      </c>
-      <c r="X5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>690356</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>36208</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>26214</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>645</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>22365</v>
-      </c>
-      <c r="AE5" t="n">
+      <c r="AS5" t="n">
         <v>2097</v>
       </c>
-      <c r="AF5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>27278</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>288730</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>345498</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>116926</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>19520</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>64592</v>
-      </c>
-      <c r="AM5" t="n">
+      <c r="AT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX5" t="n">
         <v>2718</v>
       </c>
-      <c r="AN5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>48017</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>17872</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>1966</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>144287</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>5496</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>921</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>0</v>
-      </c>
       <c r="AY5" t="n">
-        <v>58934</v>
+        <v>0</v>
       </c>
       <c r="AZ5" t="n">
-        <v>713526</v>
+        <v>0</v>
       </c>
       <c r="BA5" t="n">
-        <v>0</v>
+        <v>927463</v>
       </c>
       <c r="BB5" t="n">
+        <v>816682</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>378136</v>
+      </c>
+      <c r="BD5" t="n">
         <v>435706</v>
       </c>
-      <c r="BC5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD5" t="n">
+      <c r="BE5" t="n">
+        <v>165468</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>436078</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>342601</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>144702</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>138503</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>61647</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>88168</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>89339</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>78026</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>64575</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>39821</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>31486</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>76607</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>75103</v>
+      </c>
+      <c r="BT5" t="n">
+        <v>75634</v>
+      </c>
+      <c r="BU5" t="n">
+        <v>19820</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>54468</v>
+      </c>
+      <c r="BW5" t="n">
+        <v>25890</v>
+      </c>
+      <c r="BX5" t="n">
+        <v>26389</v>
+      </c>
+      <c r="BY5" t="n">
+        <v>8596</v>
+      </c>
+      <c r="BZ5" t="n">
+        <v>24257</v>
+      </c>
+      <c r="CA5" t="n">
+        <v>13623</v>
+      </c>
+      <c r="CB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC5" t="n">
+        <v>5402</v>
+      </c>
+      <c r="CD5" t="n">
+        <v>10443</v>
+      </c>
+      <c r="CE5" t="n">
         <v>13779</v>
       </c>
-      <c r="BE5" t="n">
-        <v>31486</v>
-      </c>
-      <c r="BF5" t="n">
+      <c r="CF5" t="n">
+        <v>4379</v>
+      </c>
+      <c r="CG5" t="n">
+        <v>2377</v>
+      </c>
+      <c r="CH5" t="n">
         <v>3377</v>
       </c>
-      <c r="BG5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>378136</v>
-      </c>
-      <c r="BI5" t="n">
+      <c r="CI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ5" t="n">
+        <v>3277</v>
+      </c>
+      <c r="CK5" t="n">
+        <v>599</v>
+      </c>
+      <c r="CL5" t="n">
+        <v>975</v>
+      </c>
+      <c r="CM5" t="n">
+        <v>1497</v>
+      </c>
+      <c r="CN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO5" t="n">
         <v>-300</v>
       </c>
-      <c r="BJ5" t="n">
-        <v>88168</v>
-      </c>
-      <c r="BK5" t="n">
-        <v>13623</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>138503</v>
-      </c>
-      <c r="BM5" t="n">
-        <v>5402</v>
-      </c>
-      <c r="BN5" t="n">
-        <v>10443</v>
-      </c>
-      <c r="BO5" t="n">
-        <v>78026</v>
-      </c>
-      <c r="BP5" t="n">
-        <v>89339</v>
-      </c>
-      <c r="BQ5" t="n">
-        <v>39821</v>
-      </c>
-      <c r="BR5" t="n">
-        <v>4379</v>
-      </c>
-      <c r="BS5" t="n">
+      <c r="CP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ5" t="n">
         <v>3798</v>
       </c>
-      <c r="BT5" t="n">
-        <v>3277</v>
-      </c>
-      <c r="BU5" t="n">
-        <v>599</v>
-      </c>
-      <c r="BV5" t="n">
-        <v>61647</v>
-      </c>
-      <c r="BW5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX5" t="n">
-        <v>816682</v>
-      </c>
-      <c r="BY5" t="n">
-        <v>75103</v>
-      </c>
-      <c r="BZ5" t="n">
-        <v>26389</v>
-      </c>
-      <c r="CA5" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB5" t="n">
-        <v>975</v>
-      </c>
-      <c r="CC5" t="n">
-        <v>25890</v>
-      </c>
-      <c r="CD5" t="n">
+      <c r="CR5" t="n">
         <v>2097</v>
       </c>
-      <c r="CE5" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF5" t="n">
-        <v>54468</v>
-      </c>
-      <c r="CG5" t="n">
-        <v>342601</v>
-      </c>
-      <c r="CH5" t="n">
-        <v>436078</v>
-      </c>
-      <c r="CI5" t="n">
-        <v>144702</v>
-      </c>
-      <c r="CJ5" t="n">
-        <v>19820</v>
-      </c>
-      <c r="CK5" t="n">
-        <v>75634</v>
-      </c>
-      <c r="CL5" t="n">
+      <c r="CS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW5" t="n">
         <v>3398</v>
       </c>
-      <c r="CM5" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN5" t="n">
-        <v>64575</v>
-      </c>
-      <c r="CO5" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP5" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ5" t="n">
-        <v>24257</v>
-      </c>
-      <c r="CR5" t="n">
-        <v>2377</v>
-      </c>
-      <c r="CS5" t="n">
-        <v>165468</v>
-      </c>
-      <c r="CT5" t="n">
-        <v>8596</v>
-      </c>
-      <c r="CU5" t="n">
-        <v>0</v>
-      </c>
-      <c r="CV5" t="n">
-        <v>1497</v>
-      </c>
-      <c r="CW5" t="n">
-        <v>0</v>
-      </c>
       <c r="CX5" t="n">
-        <v>76607</v>
+        <v>0</v>
       </c>
       <c r="CY5" t="n">
-        <v>927463</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -2760,6 +2779,319 @@
         <v>0</v>
       </c>
       <c r="CY6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1124651</v>
+      </c>
+      <c r="C7" t="n">
+        <v>674280</v>
+      </c>
+      <c r="D7" t="n">
+        <v>459297</v>
+      </c>
+      <c r="E7" t="n">
+        <v>453421</v>
+      </c>
+      <c r="F7" t="n">
+        <v>301080</v>
+      </c>
+      <c r="G7" t="n">
+        <v>298970</v>
+      </c>
+      <c r="H7" t="n">
+        <v>274813</v>
+      </c>
+      <c r="I7" t="n">
+        <v>201681</v>
+      </c>
+      <c r="J7" t="n">
+        <v>162674</v>
+      </c>
+      <c r="K7" t="n">
+        <v>124602</v>
+      </c>
+      <c r="L7" t="n">
+        <v>78173</v>
+      </c>
+      <c r="M7" t="n">
+        <v>75075</v>
+      </c>
+      <c r="N7" t="n">
+        <v>64179</v>
+      </c>
+      <c r="O7" t="n">
+        <v>56918</v>
+      </c>
+      <c r="P7" t="n">
+        <v>53126</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>46615</v>
+      </c>
+      <c r="R7" t="n">
+        <v>41340</v>
+      </c>
+      <c r="S7" t="n">
+        <v>40461</v>
+      </c>
+      <c r="T7" t="n">
+        <v>39969</v>
+      </c>
+      <c r="U7" t="n">
+        <v>36394</v>
+      </c>
+      <c r="V7" t="n">
+        <v>28257</v>
+      </c>
+      <c r="W7" t="n">
+        <v>24354</v>
+      </c>
+      <c r="X7" t="n">
+        <v>22400</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>22115</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>19469</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>14787</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>9563</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>6086</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>6058</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>5855</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>5309</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>3844</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>2309</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>2255</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1919</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>1557</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>1244</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1032</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>714</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>628</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>418</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>298</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>1454660</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>906692</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>526072</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>542333</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>366778</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>369652</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>348013</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>207978</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>197903</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>124842</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>88233</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>105397</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>82050</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>63763</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>65745</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>51450</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>47095</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>49235</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>76809</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>41531</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>29217</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>47884</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>25540</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>22500</v>
+      </c>
+      <c r="BY7" t="n">
+        <v>23789</v>
+      </c>
+      <c r="BZ7" t="n">
+        <v>18687</v>
+      </c>
+      <c r="CA7" t="n">
+        <v>10883</v>
+      </c>
+      <c r="CB7" t="n">
+        <v>6086</v>
+      </c>
+      <c r="CC7" t="n">
+        <v>7845</v>
+      </c>
+      <c r="CD7" t="n">
+        <v>7595</v>
+      </c>
+      <c r="CE7" t="n">
+        <v>8792</v>
+      </c>
+      <c r="CF7" t="n">
+        <v>4401</v>
+      </c>
+      <c r="CG7" t="n">
+        <v>2616</v>
+      </c>
+      <c r="CH7" t="n">
+        <v>2725</v>
+      </c>
+      <c r="CI7" t="n">
+        <v>2094</v>
+      </c>
+      <c r="CJ7" t="n">
+        <v>2511</v>
+      </c>
+      <c r="CK7" t="n">
+        <v>1244</v>
+      </c>
+      <c r="CL7" t="n">
+        <v>1642</v>
+      </c>
+      <c r="CM7" t="n">
+        <v>1920</v>
+      </c>
+      <c r="CN7" t="n">
+        <v>748</v>
+      </c>
+      <c r="CO7" t="n">
+        <v>600</v>
+      </c>
+      <c r="CP7" t="n">
+        <v>398</v>
+      </c>
+      <c r="CQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2774,208 +3106,208 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:GQ6"/>
+  <dimension ref="A1:GQ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="19" customWidth="1" min="5" max="5"/>
-    <col width="21" customWidth="1" min="6" max="6"/>
-    <col width="19" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="25" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="24" customWidth="1" min="12" max="12"/>
-    <col width="15" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
-    <col width="22" customWidth="1" min="15" max="15"/>
-    <col width="15" customWidth="1" min="16" max="16"/>
-    <col width="24" customWidth="1" min="17" max="17"/>
-    <col width="17" customWidth="1" min="18" max="18"/>
-    <col width="23" customWidth="1" min="19" max="19"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="19" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="10" max="10"/>
+    <col width="17" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="23" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="15" customWidth="1" min="15" max="15"/>
+    <col width="23" customWidth="1" min="16" max="16"/>
+    <col width="19" customWidth="1" min="17" max="17"/>
+    <col width="21" customWidth="1" min="18" max="18"/>
+    <col width="27" customWidth="1" min="19" max="19"/>
     <col width="17" customWidth="1" min="20" max="20"/>
-    <col width="18" customWidth="1" min="21" max="21"/>
-    <col width="16" customWidth="1" min="22" max="22"/>
-    <col width="17" customWidth="1" min="23" max="23"/>
+    <col width="26" customWidth="1" min="21" max="21"/>
+    <col width="25" customWidth="1" min="22" max="22"/>
+    <col width="19" customWidth="1" min="23" max="23"/>
     <col width="22" customWidth="1" min="24" max="24"/>
-    <col width="16" customWidth="1" min="25" max="25"/>
-    <col width="18" customWidth="1" min="26" max="26"/>
+    <col width="23" customWidth="1" min="25" max="25"/>
+    <col width="24" customWidth="1" min="26" max="26"/>
     <col width="21" customWidth="1" min="27" max="27"/>
-    <col width="27" customWidth="1" min="28" max="28"/>
+    <col width="26" customWidth="1" min="28" max="28"/>
     <col width="19" customWidth="1" min="29" max="29"/>
-    <col width="14" customWidth="1" min="30" max="30"/>
-    <col width="24" customWidth="1" min="31" max="31"/>
-    <col width="25" customWidth="1" min="32" max="32"/>
-    <col width="22" customWidth="1" min="33" max="33"/>
+    <col width="16" customWidth="1" min="30" max="30"/>
+    <col width="28" customWidth="1" min="31" max="31"/>
+    <col width="14" customWidth="1" min="32" max="32"/>
+    <col width="19" customWidth="1" min="33" max="33"/>
     <col width="23" customWidth="1" min="34" max="34"/>
-    <col width="24" customWidth="1" min="35" max="35"/>
-    <col width="17" customWidth="1" min="36" max="36"/>
-    <col width="17" customWidth="1" min="37" max="37"/>
-    <col width="16" customWidth="1" min="38" max="38"/>
-    <col width="19" customWidth="1" min="39" max="39"/>
-    <col width="19" customWidth="1" min="40" max="40"/>
-    <col width="26" customWidth="1" min="41" max="41"/>
-    <col width="17" customWidth="1" min="42" max="42"/>
-    <col width="23" customWidth="1" min="43" max="43"/>
+    <col width="19" customWidth="1" min="35" max="35"/>
+    <col width="23" customWidth="1" min="36" max="36"/>
+    <col width="16" customWidth="1" min="37" max="37"/>
+    <col width="33" customWidth="1" min="38" max="38"/>
+    <col width="22" customWidth="1" min="39" max="39"/>
+    <col width="18" customWidth="1" min="40" max="40"/>
+    <col width="18" customWidth="1" min="41" max="41"/>
+    <col width="23" customWidth="1" min="42" max="42"/>
+    <col width="17" customWidth="1" min="43" max="43"/>
     <col width="17" customWidth="1" min="44" max="44"/>
-    <col width="19" customWidth="1" min="45" max="45"/>
-    <col width="18" customWidth="1" min="46" max="46"/>
-    <col width="20" customWidth="1" min="47" max="47"/>
-    <col width="23" customWidth="1" min="48" max="48"/>
-    <col width="15" customWidth="1" min="49" max="49"/>
-    <col width="21" customWidth="1" min="50" max="50"/>
-    <col width="24" customWidth="1" min="51" max="51"/>
-    <col width="17" customWidth="1" min="52" max="52"/>
-    <col width="23" customWidth="1" min="53" max="53"/>
-    <col width="19" customWidth="1" min="54" max="54"/>
-    <col width="23" customWidth="1" min="55" max="55"/>
-    <col width="22" customWidth="1" min="56" max="56"/>
-    <col width="24" customWidth="1" min="57" max="57"/>
+    <col width="17" customWidth="1" min="45" max="45"/>
+    <col width="15" customWidth="1" min="46" max="46"/>
+    <col width="15" customWidth="1" min="47" max="47"/>
+    <col width="15" customWidth="1" min="48" max="48"/>
+    <col width="17" customWidth="1" min="49" max="49"/>
+    <col width="16" customWidth="1" min="50" max="50"/>
+    <col width="22" customWidth="1" min="51" max="51"/>
+    <col width="16" customWidth="1" min="52" max="52"/>
+    <col width="18" customWidth="1" min="53" max="53"/>
+    <col width="18" customWidth="1" min="54" max="54"/>
+    <col width="24" customWidth="1" min="55" max="55"/>
+    <col width="20" customWidth="1" min="56" max="56"/>
+    <col width="23" customWidth="1" min="57" max="57"/>
     <col width="19" customWidth="1" min="58" max="58"/>
-    <col width="22" customWidth="1" min="59" max="59"/>
-    <col width="22" customWidth="1" min="60" max="60"/>
-    <col width="22" customWidth="1" min="61" max="61"/>
-    <col width="20" customWidth="1" min="62" max="62"/>
-    <col width="14" customWidth="1" min="63" max="63"/>
-    <col width="17" customWidth="1" min="64" max="64"/>
-    <col width="20" customWidth="1" min="65" max="65"/>
-    <col width="14" customWidth="1" min="66" max="66"/>
-    <col width="25" customWidth="1" min="67" max="67"/>
-    <col width="18" customWidth="1" min="68" max="68"/>
-    <col width="29" customWidth="1" min="69" max="69"/>
-    <col width="18" customWidth="1" min="70" max="70"/>
-    <col width="16" customWidth="1" min="71" max="71"/>
-    <col width="27" customWidth="1" min="72" max="72"/>
-    <col width="22" customWidth="1" min="73" max="73"/>
-    <col width="15" customWidth="1" min="74" max="74"/>
-    <col width="24" customWidth="1" min="75" max="75"/>
-    <col width="22" customWidth="1" min="76" max="76"/>
-    <col width="23" customWidth="1" min="77" max="77"/>
-    <col width="20" customWidth="1" min="78" max="78"/>
-    <col width="15" customWidth="1" min="79" max="79"/>
-    <col width="33" customWidth="1" min="80" max="80"/>
-    <col width="16" customWidth="1" min="81" max="81"/>
-    <col width="17" customWidth="1" min="82" max="82"/>
+    <col width="24" customWidth="1" min="59" max="59"/>
+    <col width="23" customWidth="1" min="60" max="60"/>
+    <col width="25" customWidth="1" min="61" max="61"/>
+    <col width="17" customWidth="1" min="62" max="62"/>
+    <col width="20" customWidth="1" min="63" max="63"/>
+    <col width="21" customWidth="1" min="64" max="64"/>
+    <col width="17" customWidth="1" min="65" max="65"/>
+    <col width="22" customWidth="1" min="66" max="66"/>
+    <col width="14" customWidth="1" min="67" max="67"/>
+    <col width="16" customWidth="1" min="68" max="68"/>
+    <col width="24" customWidth="1" min="69" max="69"/>
+    <col width="23" customWidth="1" min="70" max="70"/>
+    <col width="14" customWidth="1" min="71" max="71"/>
+    <col width="15" customWidth="1" min="72" max="72"/>
+    <col width="18" customWidth="1" min="73" max="73"/>
+    <col width="14" customWidth="1" min="74" max="74"/>
+    <col width="22" customWidth="1" min="75" max="75"/>
+    <col width="21" customWidth="1" min="76" max="76"/>
+    <col width="25" customWidth="1" min="77" max="77"/>
+    <col width="17" customWidth="1" min="78" max="78"/>
+    <col width="22" customWidth="1" min="79" max="79"/>
+    <col width="25" customWidth="1" min="80" max="80"/>
+    <col width="20" customWidth="1" min="81" max="81"/>
+    <col width="20" customWidth="1" min="82" max="82"/>
     <col width="22" customWidth="1" min="83" max="83"/>
-    <col width="15" customWidth="1" min="84" max="84"/>
-    <col width="15" customWidth="1" min="85" max="85"/>
-    <col width="23" customWidth="1" min="86" max="86"/>
-    <col width="22" customWidth="1" min="87" max="87"/>
-    <col width="17" customWidth="1" min="88" max="88"/>
-    <col width="15" customWidth="1" min="89" max="89"/>
-    <col width="28" customWidth="1" min="90" max="90"/>
-    <col width="21" customWidth="1" min="91" max="91"/>
-    <col width="28" customWidth="1" min="92" max="92"/>
-    <col width="27" customWidth="1" min="93" max="93"/>
-    <col width="25" customWidth="1" min="94" max="94"/>
-    <col width="15" customWidth="1" min="95" max="95"/>
-    <col width="23" customWidth="1" min="96" max="96"/>
-    <col width="26" customWidth="1" min="97" max="97"/>
+    <col width="19" customWidth="1" min="84" max="84"/>
+    <col width="18" customWidth="1" min="85" max="85"/>
+    <col width="16" customWidth="1" min="86" max="86"/>
+    <col width="27" customWidth="1" min="87" max="87"/>
+    <col width="15" customWidth="1" min="88" max="88"/>
+    <col width="29" customWidth="1" min="89" max="89"/>
+    <col width="15" customWidth="1" min="90" max="90"/>
+    <col width="17" customWidth="1" min="91" max="91"/>
+    <col width="24" customWidth="1" min="92" max="92"/>
+    <col width="28" customWidth="1" min="93" max="93"/>
+    <col width="15" customWidth="1" min="94" max="94"/>
+    <col width="18" customWidth="1" min="95" max="95"/>
+    <col width="19" customWidth="1" min="96" max="96"/>
+    <col width="22" customWidth="1" min="97" max="97"/>
     <col width="15" customWidth="1" min="98" max="98"/>
-    <col width="16" customWidth="1" min="99" max="99"/>
-    <col width="18" customWidth="1" min="100" max="100"/>
-    <col width="23" customWidth="1" min="101" max="101"/>
-    <col width="19" customWidth="1" min="102" max="102"/>
-    <col width="16" customWidth="1" min="103" max="103"/>
-    <col width="19" customWidth="1" min="104" max="104"/>
-    <col width="21" customWidth="1" min="105" max="105"/>
-    <col width="19" customWidth="1" min="106" max="106"/>
-    <col width="22" customWidth="1" min="107" max="107"/>
-    <col width="25" customWidth="1" min="108" max="108"/>
-    <col width="20" customWidth="1" min="109" max="109"/>
-    <col width="18" customWidth="1" min="110" max="110"/>
-    <col width="24" customWidth="1" min="111" max="111"/>
-    <col width="15" customWidth="1" min="112" max="112"/>
-    <col width="14" customWidth="1" min="113" max="113"/>
-    <col width="22" customWidth="1" min="114" max="114"/>
-    <col width="15" customWidth="1" min="115" max="115"/>
-    <col width="24" customWidth="1" min="116" max="116"/>
-    <col width="17" customWidth="1" min="117" max="117"/>
-    <col width="23" customWidth="1" min="118" max="118"/>
+    <col width="23" customWidth="1" min="99" max="99"/>
+    <col width="22" customWidth="1" min="100" max="100"/>
+    <col width="16" customWidth="1" min="101" max="101"/>
+    <col width="27" customWidth="1" min="102" max="102"/>
+    <col width="22" customWidth="1" min="103" max="103"/>
+    <col width="17" customWidth="1" min="104" max="104"/>
+    <col width="15" customWidth="1" min="105" max="105"/>
+    <col width="24" customWidth="1" min="106" max="106"/>
+    <col width="19" customWidth="1" min="107" max="107"/>
+    <col width="20" customWidth="1" min="108" max="108"/>
+    <col width="24" customWidth="1" min="109" max="109"/>
+    <col width="17" customWidth="1" min="110" max="110"/>
+    <col width="22" customWidth="1" min="111" max="111"/>
+    <col width="23" customWidth="1" min="112" max="112"/>
+    <col width="22" customWidth="1" min="113" max="113"/>
+    <col width="15" customWidth="1" min="114" max="114"/>
+    <col width="23" customWidth="1" min="115" max="115"/>
+    <col width="19" customWidth="1" min="116" max="116"/>
+    <col width="21" customWidth="1" min="117" max="117"/>
+    <col width="27" customWidth="1" min="118" max="118"/>
     <col width="17" customWidth="1" min="119" max="119"/>
-    <col width="18" customWidth="1" min="120" max="120"/>
-    <col width="16" customWidth="1" min="121" max="121"/>
-    <col width="17" customWidth="1" min="122" max="122"/>
+    <col width="26" customWidth="1" min="120" max="120"/>
+    <col width="25" customWidth="1" min="121" max="121"/>
+    <col width="19" customWidth="1" min="122" max="122"/>
     <col width="22" customWidth="1" min="123" max="123"/>
-    <col width="16" customWidth="1" min="124" max="124"/>
-    <col width="18" customWidth="1" min="125" max="125"/>
+    <col width="23" customWidth="1" min="124" max="124"/>
+    <col width="24" customWidth="1" min="125" max="125"/>
     <col width="21" customWidth="1" min="126" max="126"/>
-    <col width="27" customWidth="1" min="127" max="127"/>
+    <col width="26" customWidth="1" min="127" max="127"/>
     <col width="19" customWidth="1" min="128" max="128"/>
-    <col width="14" customWidth="1" min="129" max="129"/>
-    <col width="24" customWidth="1" min="130" max="130"/>
-    <col width="25" customWidth="1" min="131" max="131"/>
-    <col width="22" customWidth="1" min="132" max="132"/>
+    <col width="16" customWidth="1" min="129" max="129"/>
+    <col width="28" customWidth="1" min="130" max="130"/>
+    <col width="14" customWidth="1" min="131" max="131"/>
+    <col width="19" customWidth="1" min="132" max="132"/>
     <col width="23" customWidth="1" min="133" max="133"/>
-    <col width="24" customWidth="1" min="134" max="134"/>
-    <col width="17" customWidth="1" min="135" max="135"/>
-    <col width="17" customWidth="1" min="136" max="136"/>
-    <col width="16" customWidth="1" min="137" max="137"/>
-    <col width="19" customWidth="1" min="138" max="138"/>
-    <col width="19" customWidth="1" min="139" max="139"/>
-    <col width="26" customWidth="1" min="140" max="140"/>
-    <col width="17" customWidth="1" min="141" max="141"/>
-    <col width="23" customWidth="1" min="142" max="142"/>
+    <col width="19" customWidth="1" min="134" max="134"/>
+    <col width="23" customWidth="1" min="135" max="135"/>
+    <col width="16" customWidth="1" min="136" max="136"/>
+    <col width="33" customWidth="1" min="137" max="137"/>
+    <col width="22" customWidth="1" min="138" max="138"/>
+    <col width="18" customWidth="1" min="139" max="139"/>
+    <col width="18" customWidth="1" min="140" max="140"/>
+    <col width="23" customWidth="1" min="141" max="141"/>
+    <col width="17" customWidth="1" min="142" max="142"/>
     <col width="17" customWidth="1" min="143" max="143"/>
-    <col width="19" customWidth="1" min="144" max="144"/>
-    <col width="18" customWidth="1" min="145" max="145"/>
-    <col width="20" customWidth="1" min="146" max="146"/>
-    <col width="23" customWidth="1" min="147" max="147"/>
-    <col width="15" customWidth="1" min="148" max="148"/>
-    <col width="21" customWidth="1" min="149" max="149"/>
-    <col width="24" customWidth="1" min="150" max="150"/>
-    <col width="17" customWidth="1" min="151" max="151"/>
-    <col width="23" customWidth="1" min="152" max="152"/>
-    <col width="19" customWidth="1" min="153" max="153"/>
-    <col width="23" customWidth="1" min="154" max="154"/>
-    <col width="22" customWidth="1" min="155" max="155"/>
-    <col width="24" customWidth="1" min="156" max="156"/>
+    <col width="17" customWidth="1" min="144" max="144"/>
+    <col width="15" customWidth="1" min="145" max="145"/>
+    <col width="15" customWidth="1" min="146" max="146"/>
+    <col width="15" customWidth="1" min="147" max="147"/>
+    <col width="17" customWidth="1" min="148" max="148"/>
+    <col width="16" customWidth="1" min="149" max="149"/>
+    <col width="22" customWidth="1" min="150" max="150"/>
+    <col width="16" customWidth="1" min="151" max="151"/>
+    <col width="18" customWidth="1" min="152" max="152"/>
+    <col width="18" customWidth="1" min="153" max="153"/>
+    <col width="24" customWidth="1" min="154" max="154"/>
+    <col width="20" customWidth="1" min="155" max="155"/>
+    <col width="23" customWidth="1" min="156" max="156"/>
     <col width="19" customWidth="1" min="157" max="157"/>
-    <col width="22" customWidth="1" min="158" max="158"/>
-    <col width="22" customWidth="1" min="159" max="159"/>
-    <col width="22" customWidth="1" min="160" max="160"/>
-    <col width="20" customWidth="1" min="161" max="161"/>
-    <col width="14" customWidth="1" min="162" max="162"/>
-    <col width="17" customWidth="1" min="163" max="163"/>
-    <col width="20" customWidth="1" min="164" max="164"/>
-    <col width="14" customWidth="1" min="165" max="165"/>
-    <col width="25" customWidth="1" min="166" max="166"/>
-    <col width="18" customWidth="1" min="167" max="167"/>
-    <col width="29" customWidth="1" min="168" max="168"/>
-    <col width="18" customWidth="1" min="169" max="169"/>
-    <col width="16" customWidth="1" min="170" max="170"/>
-    <col width="27" customWidth="1" min="171" max="171"/>
-    <col width="22" customWidth="1" min="172" max="172"/>
-    <col width="15" customWidth="1" min="173" max="173"/>
-    <col width="24" customWidth="1" min="174" max="174"/>
-    <col width="22" customWidth="1" min="175" max="175"/>
-    <col width="23" customWidth="1" min="176" max="176"/>
-    <col width="20" customWidth="1" min="177" max="177"/>
-    <col width="15" customWidth="1" min="178" max="178"/>
-    <col width="33" customWidth="1" min="179" max="179"/>
-    <col width="16" customWidth="1" min="180" max="180"/>
-    <col width="17" customWidth="1" min="181" max="181"/>
+    <col width="24" customWidth="1" min="158" max="158"/>
+    <col width="23" customWidth="1" min="159" max="159"/>
+    <col width="25" customWidth="1" min="160" max="160"/>
+    <col width="17" customWidth="1" min="161" max="161"/>
+    <col width="20" customWidth="1" min="162" max="162"/>
+    <col width="21" customWidth="1" min="163" max="163"/>
+    <col width="17" customWidth="1" min="164" max="164"/>
+    <col width="22" customWidth="1" min="165" max="165"/>
+    <col width="14" customWidth="1" min="166" max="166"/>
+    <col width="16" customWidth="1" min="167" max="167"/>
+    <col width="24" customWidth="1" min="168" max="168"/>
+    <col width="23" customWidth="1" min="169" max="169"/>
+    <col width="14" customWidth="1" min="170" max="170"/>
+    <col width="15" customWidth="1" min="171" max="171"/>
+    <col width="18" customWidth="1" min="172" max="172"/>
+    <col width="14" customWidth="1" min="173" max="173"/>
+    <col width="22" customWidth="1" min="174" max="174"/>
+    <col width="21" customWidth="1" min="175" max="175"/>
+    <col width="25" customWidth="1" min="176" max="176"/>
+    <col width="17" customWidth="1" min="177" max="177"/>
+    <col width="22" customWidth="1" min="178" max="178"/>
+    <col width="25" customWidth="1" min="179" max="179"/>
+    <col width="20" customWidth="1" min="180" max="180"/>
+    <col width="20" customWidth="1" min="181" max="181"/>
     <col width="22" customWidth="1" min="182" max="182"/>
-    <col width="15" customWidth="1" min="183" max="183"/>
-    <col width="15" customWidth="1" min="184" max="184"/>
-    <col width="23" customWidth="1" min="185" max="185"/>
-    <col width="22" customWidth="1" min="186" max="186"/>
-    <col width="17" customWidth="1" min="187" max="187"/>
-    <col width="15" customWidth="1" min="188" max="188"/>
-    <col width="28" customWidth="1" min="189" max="189"/>
-    <col width="21" customWidth="1" min="190" max="190"/>
-    <col width="28" customWidth="1" min="191" max="191"/>
-    <col width="27" customWidth="1" min="192" max="192"/>
-    <col width="25" customWidth="1" min="193" max="193"/>
-    <col width="15" customWidth="1" min="194" max="194"/>
-    <col width="23" customWidth="1" min="195" max="195"/>
-    <col width="26" customWidth="1" min="196" max="196"/>
+    <col width="19" customWidth="1" min="183" max="183"/>
+    <col width="18" customWidth="1" min="184" max="184"/>
+    <col width="16" customWidth="1" min="185" max="185"/>
+    <col width="27" customWidth="1" min="186" max="186"/>
+    <col width="15" customWidth="1" min="187" max="187"/>
+    <col width="29" customWidth="1" min="188" max="188"/>
+    <col width="15" customWidth="1" min="189" max="189"/>
+    <col width="17" customWidth="1" min="190" max="190"/>
+    <col width="24" customWidth="1" min="191" max="191"/>
+    <col width="28" customWidth="1" min="192" max="192"/>
+    <col width="15" customWidth="1" min="193" max="193"/>
+    <col width="18" customWidth="1" min="194" max="194"/>
+    <col width="19" customWidth="1" min="195" max="195"/>
+    <col width="22" customWidth="1" min="196" max="196"/>
     <col width="15" customWidth="1" min="197" max="197"/>
-    <col width="16" customWidth="1" min="198" max="198"/>
-    <col width="18" customWidth="1" min="199" max="199"/>
+    <col width="23" customWidth="1" min="198" max="198"/>
+    <col width="22" customWidth="1" min="199" max="199"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2986,992 +3318,992 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Nelly (Sell)</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Adidas Originals (Sell)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>New Balance (Sell)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Pieces (Sell)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Only (Sell)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Que Sera Sera (Sell)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Neo Noir (Sell)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Vero Moda (Sell)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>True Religion (Sell)</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Levi's (Sell)</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Gina Tricot (Sell)</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Selected Men (Sell)</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Only &amp; Sons (Sell)</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Nike (Sell)</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Jack &amp; Jones (Sell)</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Dr Denim (Sell)</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Lois Jeans (Sell)</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>By Malene Birger (Sell)</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Malina (Sell)</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>BECKSÖNDERGAARD (Sell)</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>The North Face (Sell)</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Woodbird (Sell)</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Birkenstock (Sell)</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Carhartt WIP (Sell)</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Samsøe Samsøe (Sell)</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>A.Kjærbede (Sell)</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>Muli Collection (Sell)</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>Pavement (Sell)</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>Aim'n (Sell)</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>Polo Ralph Lauren (Sell)</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>UGG (Sell)</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>Converse (Sell)</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>Abrand Jeans (Sell)</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>Les Deux (Sell)</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>Sneaky Steve (Sell)</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>Asics (Sell)</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>Calvin Klein Underwear (Sell)</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>Hunkemöller (Sell)</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>Ciszere (Sell)</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>Inuikii (Sell)</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>One Teaspoon (Sell)</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>Hunter (Sell)</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>DORINA (Sell)</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>Diesel (Sell)</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>Gant (Sell)</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>Puma (Sell)</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>MONO (Sell)</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>Colmar (Sell)</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>Solid (Sell)</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>ATP ATELIER (Sell)</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>Rains (Sell)</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>Bye Bra (Sell)</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>Pilgrim (Sell)</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>Mads Nørgaard (Sell)</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>Havaianas (Sell)</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>Brand Island (Sell)</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>Le Specs (Sell)</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>Casual Friday (Sell)</t>
+        </is>
+      </c>
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>STICKYBESTIE (Sell)</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>Selected Femme (Sell)</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>OBJECT (Sell)</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>Bluebella (Sell)</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>Björn Borg (Sell)</t>
+        </is>
+      </c>
+      <c r="BM1" s="1" t="inlineStr">
+        <is>
+          <t>ANNARR (Sell)</t>
+        </is>
+      </c>
+      <c r="BN1" s="1" t="inlineStr">
+        <is>
+          <t>By Billgren (Sell)</t>
+        </is>
+      </c>
+      <c r="BO1" s="1" t="inlineStr">
+        <is>
+          <t>JDY (Sell)</t>
+        </is>
+      </c>
+      <c r="BP1" s="1" t="inlineStr">
+        <is>
+          <t>Spanx (Sell)</t>
+        </is>
+      </c>
+      <c r="BQ1" s="1" t="inlineStr">
+        <is>
+          <t>Juicy Couture (Sell)</t>
+        </is>
+      </c>
+      <c r="BR1" s="1" t="inlineStr">
+        <is>
+          <t>Michael Kors (Sell)</t>
+        </is>
+      </c>
+      <c r="BS1" s="1" t="inlineStr">
+        <is>
+          <t>IRO (Sell)</t>
+        </is>
+      </c>
+      <c r="BT1" s="1" t="inlineStr">
+        <is>
+          <t>VANS (Sell)</t>
+        </is>
+      </c>
+      <c r="BU1" s="1" t="inlineStr">
+        <is>
+          <t>Dockers (Sell)</t>
+        </is>
+      </c>
+      <c r="BV1" s="1" t="inlineStr">
+        <is>
+          <t>OAS (Sell)</t>
+        </is>
+      </c>
+      <c r="BW1" s="1" t="inlineStr">
+        <is>
+          <t>Marc Jacobs (Sell)</t>
+        </is>
+      </c>
+      <c r="BX1" s="1" t="inlineStr">
+        <is>
+          <t>Timberland (Sell)</t>
+        </is>
+      </c>
+      <c r="BY1" s="1" t="inlineStr">
+        <is>
+          <t>Corlin Eyewear (Sell)</t>
+        </is>
+      </c>
+      <c r="BZ1" s="1" t="inlineStr">
+        <is>
+          <t>DAY ET (Sell)</t>
+        </is>
+      </c>
+      <c r="CA1" s="1" t="inlineStr">
+        <is>
+          <t>J Lindeberg (Sell)</t>
+        </is>
+      </c>
+      <c r="CB1" s="1" t="inlineStr">
+        <is>
+          <t>Bread &amp; Boxers (Sell)</t>
+        </is>
+      </c>
+      <c r="CC1" s="1" t="inlineStr">
+        <is>
+          <t>Le Bonnet (Sell)</t>
+        </is>
+      </c>
+      <c r="CD1" s="1" t="inlineStr">
+        <is>
+          <t>Moon Boot (Sell)</t>
+        </is>
+      </c>
+      <c r="CE1" s="1" t="inlineStr">
+        <is>
+          <t>Tommy Jeans (Sell)</t>
+        </is>
+      </c>
+      <c r="CF1" s="1" t="inlineStr">
+        <is>
+          <t>Columbia (Sell)</t>
+        </is>
+      </c>
+      <c r="CG1" s="1" t="inlineStr">
+        <is>
+          <t>Dickies (Sell)</t>
+        </is>
+      </c>
+      <c r="CH1" s="1" t="inlineStr">
+        <is>
+          <t>GABBA (Sell)</t>
+        </is>
+      </c>
+      <c r="CI1" s="1" t="inlineStr">
+        <is>
+          <t>Mercer Amsterdam (Sell)</t>
+        </is>
+      </c>
+      <c r="CJ1" s="1" t="inlineStr">
+        <is>
+          <t>JJXX (Sell)</t>
+        </is>
+      </c>
+      <c r="CK1" s="1" t="inlineStr">
+        <is>
+          <t>Calvin Klein Jeans (Sell)</t>
+        </is>
+      </c>
+      <c r="CL1" s="1" t="inlineStr">
+        <is>
+          <t>Teva (Sell)</t>
+        </is>
+      </c>
+      <c r="CM1" s="1" t="inlineStr">
+        <is>
+          <t>Scholl (Sell)</t>
+        </is>
+      </c>
+      <c r="CN1" s="1" t="inlineStr">
+        <is>
+          <t>Messy Weekend (Sell)</t>
+        </is>
+      </c>
+      <c r="CO1" s="1" t="inlineStr">
+        <is>
+          <t>Magic Bodyfashion (Sell)</t>
+        </is>
+      </c>
+      <c r="CP1" s="1" t="inlineStr">
+        <is>
+          <t>Cras (Sell)</t>
+        </is>
+      </c>
+      <c r="CQ1" s="1" t="inlineStr">
+        <is>
+          <t>Playboy (Sell)</t>
+        </is>
+      </c>
+      <c r="CR1" s="1" t="inlineStr">
+        <is>
+          <t>Shepherd (Sell)</t>
+        </is>
+      </c>
+      <c r="CS1" s="1" t="inlineStr">
+        <is>
+          <t>ROCKANDBLUE (Sell)</t>
+        </is>
+      </c>
+      <c r="CT1" s="1" t="inlineStr">
+        <is>
+          <t>Neuw (Sell)</t>
+        </is>
+      </c>
+      <c r="CU1" s="1" t="inlineStr">
+        <is>
           <t>Lyle &amp; Scott (Sell)</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Dr Denim (Sell)</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>GABBA (Sell)</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Les Deux (Sell)</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Björn Borg (Sell)</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Columbia (Sell)</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Birkenstock (Sell)</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Selected Femme (Sell)</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Moon Boot (Sell)</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Inuikii (Sell)</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>True Religion (Sell)</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Neuw (Sell)</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>IRO (Sell)</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>Only &amp; Sons (Sell)</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>Teva (Sell)</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>Casual Friday (Sell)</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>Pieces (Sell)</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>Abrand Jeans (Sell)</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>DORINA (Sell)</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>Dockers (Sell)</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>Aim'n (Sell)</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>Colmar (Sell)</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="CV1" s="1" t="inlineStr">
         <is>
           <t>Daily Paper (Sell)</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>Spanx (Sell)</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>Ciszere (Sell)</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>Lois Jeans (Sell)</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>By Malene Birger (Sell)</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>Woodbird (Sell)</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>JDY (Sell)</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>Mads Nørgaard (Sell)</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>Corlin Eyewear (Sell)</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>Tommy Jeans (Sell)</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>Jack &amp; Jones (Sell)</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>Samsøe Samsøe (Sell)</t>
-        </is>
-      </c>
-      <c r="AJ1" s="1" t="inlineStr">
-        <is>
-          <t>Diesel (Sell)</t>
-        </is>
-      </c>
-      <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>Hunter (Sell)</t>
-        </is>
-      </c>
-      <c r="AL1" s="1" t="inlineStr">
-        <is>
-          <t>Rains (Sell)</t>
-        </is>
-      </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>Neo Noir (Sell)</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
-        <is>
-          <t>Pavement (Sell)</t>
-        </is>
-      </c>
-      <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>BECKSÖNDERGAARD (Sell)</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>ANNARR (Sell)</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>Sneaky Steve (Sell)</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>OBJECT (Sell)</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>Le Specs (Sell)</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>Playboy (Sell)</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>Le Bonnet (Sell)</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>STICKYBESTIE (Sell)</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>Only (Sell)</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>A.Kjærbede (Sell)</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>Messy Weekend (Sell)</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>Malina (Sell)</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>Selected Men (Sell)</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>Converse (Sell)</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>Michael Kors (Sell)</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>J Lindeberg (Sell)</t>
-        </is>
-      </c>
-      <c r="BE1" s="1" t="inlineStr">
-        <is>
-          <t>Juicy Couture (Sell)</t>
-        </is>
-      </c>
-      <c r="BF1" s="1" t="inlineStr">
-        <is>
-          <t>Shepherd (Sell)</t>
-        </is>
-      </c>
-      <c r="BG1" s="1" t="inlineStr">
-        <is>
-          <t>New Balance (Sell)</t>
-        </is>
-      </c>
-      <c r="BH1" s="1" t="inlineStr">
-        <is>
-          <t>Marc Jacobs (Sell)</t>
-        </is>
-      </c>
-      <c r="BI1" s="1" t="inlineStr">
-        <is>
-          <t>ROCKANDBLUE (Sell)</t>
-        </is>
-      </c>
-      <c r="BJ1" s="1" t="inlineStr">
-        <is>
-          <t>Vero Moda (Sell)</t>
-        </is>
-      </c>
-      <c r="BK1" s="1" t="inlineStr">
-        <is>
-          <t>UGG (Sell)</t>
-        </is>
-      </c>
-      <c r="BL1" s="1" t="inlineStr">
-        <is>
-          <t>Levi's (Sell)</t>
-        </is>
-      </c>
-      <c r="BM1" s="1" t="inlineStr">
-        <is>
-          <t>Bluebella (Sell)</t>
-        </is>
-      </c>
-      <c r="BN1" s="1" t="inlineStr">
-        <is>
-          <t>OAS (Sell)</t>
-        </is>
-      </c>
-      <c r="BO1" s="1" t="inlineStr">
-        <is>
-          <t>Bread &amp; Boxers (Sell)</t>
-        </is>
-      </c>
-      <c r="BP1" s="1" t="inlineStr">
-        <is>
-          <t>Dickies (Sell)</t>
-        </is>
-      </c>
-      <c r="BQ1" s="1" t="inlineStr">
-        <is>
-          <t>Calvin Klein Jeans (Sell)</t>
-        </is>
-      </c>
-      <c r="BR1" s="1" t="inlineStr">
-        <is>
-          <t>Bye Bra (Sell)</t>
-        </is>
-      </c>
-      <c r="BS1" s="1" t="inlineStr">
-        <is>
-          <t>Nelly (Sell)</t>
-        </is>
-      </c>
-      <c r="BT1" s="1" t="inlineStr">
-        <is>
-          <t>Mercer Amsterdam (Sell)</t>
-        </is>
-      </c>
-      <c r="BU1" s="1" t="inlineStr">
-        <is>
-          <t>ATP ATELIER (Sell)</t>
-        </is>
-      </c>
-      <c r="BV1" s="1" t="inlineStr">
-        <is>
-          <t>Nike (Sell)</t>
-        </is>
-      </c>
-      <c r="BW1" s="1" t="inlineStr">
-        <is>
-          <t>Que Sera Sera (Sell)</t>
-        </is>
-      </c>
-      <c r="BX1" s="1" t="inlineStr">
-        <is>
-          <t>By Billgren (Sell)</t>
-        </is>
-      </c>
-      <c r="BY1" s="1" t="inlineStr">
-        <is>
-          <t>Carhartt WIP (Sell)</t>
-        </is>
-      </c>
-      <c r="BZ1" s="1" t="inlineStr">
-        <is>
-          <t>Havaianas (Sell)</t>
-        </is>
-      </c>
-      <c r="CA1" s="1" t="inlineStr">
-        <is>
-          <t>MONO (Sell)</t>
-        </is>
-      </c>
-      <c r="CB1" s="1" t="inlineStr">
-        <is>
-          <t>Calvin Klein Underwear (Sell)</t>
-        </is>
-      </c>
-      <c r="CC1" s="1" t="inlineStr">
-        <is>
-          <t>Asics (Sell)</t>
-        </is>
-      </c>
-      <c r="CD1" s="1" t="inlineStr">
-        <is>
-          <t>DAY ET (Sell)</t>
-        </is>
-      </c>
-      <c r="CE1" s="1" t="inlineStr">
-        <is>
-          <t>Hunkemöller (Sell)</t>
-        </is>
-      </c>
-      <c r="CF1" s="1" t="inlineStr">
-        <is>
-          <t>Puma (Sell)</t>
-        </is>
-      </c>
-      <c r="CG1" s="1" t="inlineStr">
-        <is>
-          <t>Cras (Sell)</t>
-        </is>
-      </c>
-      <c r="CH1" s="1" t="inlineStr">
-        <is>
-          <t>Brand Island (Sell)</t>
-        </is>
-      </c>
-      <c r="CI1" s="1" t="inlineStr">
-        <is>
-          <t>Gina Tricot (Sell)</t>
-        </is>
-      </c>
-      <c r="CJ1" s="1" t="inlineStr">
-        <is>
-          <t>Scholl (Sell)</t>
-        </is>
-      </c>
-      <c r="CK1" s="1" t="inlineStr">
-        <is>
-          <t>Gant (Sell)</t>
-        </is>
-      </c>
-      <c r="CL1" s="1" t="inlineStr">
-        <is>
-          <t>Polo Ralph Lauren (Sell)</t>
-        </is>
-      </c>
-      <c r="CM1" s="1" t="inlineStr">
-        <is>
-          <t>Timberland (Sell)</t>
-        </is>
-      </c>
-      <c r="CN1" s="1" t="inlineStr">
-        <is>
-          <t>Magic Bodyfashion (Sell)</t>
-        </is>
-      </c>
-      <c r="CO1" s="1" t="inlineStr">
-        <is>
-          <t>Adidas Originals (Sell)</t>
-        </is>
-      </c>
-      <c r="CP1" s="1" t="inlineStr">
-        <is>
-          <t>The North Face (Sell)</t>
-        </is>
-      </c>
-      <c r="CQ1" s="1" t="inlineStr">
-        <is>
-          <t>JJXX (Sell)</t>
-        </is>
-      </c>
-      <c r="CR1" s="1" t="inlineStr">
-        <is>
-          <t>One Teaspoon (Sell)</t>
-        </is>
-      </c>
-      <c r="CS1" s="1" t="inlineStr">
-        <is>
-          <t>Muli Collection (Sell)</t>
-        </is>
-      </c>
-      <c r="CT1" s="1" t="inlineStr">
-        <is>
-          <t>VANS (Sell)</t>
-        </is>
-      </c>
-      <c r="CU1" s="1" t="inlineStr">
-        <is>
-          <t>Solid (Sell)</t>
-        </is>
-      </c>
-      <c r="CV1" s="1" t="inlineStr">
-        <is>
-          <t>Pilgrim (Sell)</t>
-        </is>
-      </c>
       <c r="CW1" s="1" t="inlineStr">
         <is>
+          <t>Nelly (List)</t>
+        </is>
+      </c>
+      <c r="CX1" s="1" t="inlineStr">
+        <is>
+          <t>Adidas Originals (List)</t>
+        </is>
+      </c>
+      <c r="CY1" s="1" t="inlineStr">
+        <is>
+          <t>New Balance (List)</t>
+        </is>
+      </c>
+      <c r="CZ1" s="1" t="inlineStr">
+        <is>
+          <t>Pieces (List)</t>
+        </is>
+      </c>
+      <c r="DA1" s="1" t="inlineStr">
+        <is>
+          <t>Only (List)</t>
+        </is>
+      </c>
+      <c r="DB1" s="1" t="inlineStr">
+        <is>
+          <t>Que Sera Sera (List)</t>
+        </is>
+      </c>
+      <c r="DC1" s="1" t="inlineStr">
+        <is>
+          <t>Neo Noir (List)</t>
+        </is>
+      </c>
+      <c r="DD1" s="1" t="inlineStr">
+        <is>
+          <t>Vero Moda (List)</t>
+        </is>
+      </c>
+      <c r="DE1" s="1" t="inlineStr">
+        <is>
+          <t>True Religion (List)</t>
+        </is>
+      </c>
+      <c r="DF1" s="1" t="inlineStr">
+        <is>
+          <t>Levi's (List)</t>
+        </is>
+      </c>
+      <c r="DG1" s="1" t="inlineStr">
+        <is>
+          <t>Gina Tricot (List)</t>
+        </is>
+      </c>
+      <c r="DH1" s="1" t="inlineStr">
+        <is>
+          <t>Selected Men (List)</t>
+        </is>
+      </c>
+      <c r="DI1" s="1" t="inlineStr">
+        <is>
+          <t>Only &amp; Sons (List)</t>
+        </is>
+      </c>
+      <c r="DJ1" s="1" t="inlineStr">
+        <is>
+          <t>Nike (List)</t>
+        </is>
+      </c>
+      <c r="DK1" s="1" t="inlineStr">
+        <is>
+          <t>Jack &amp; Jones (List)</t>
+        </is>
+      </c>
+      <c r="DL1" s="1" t="inlineStr">
+        <is>
+          <t>Dr Denim (List)</t>
+        </is>
+      </c>
+      <c r="DM1" s="1" t="inlineStr">
+        <is>
+          <t>Lois Jeans (List)</t>
+        </is>
+      </c>
+      <c r="DN1" s="1" t="inlineStr">
+        <is>
+          <t>By Malene Birger (List)</t>
+        </is>
+      </c>
+      <c r="DO1" s="1" t="inlineStr">
+        <is>
+          <t>Malina (List)</t>
+        </is>
+      </c>
+      <c r="DP1" s="1" t="inlineStr">
+        <is>
+          <t>BECKSÖNDERGAARD (List)</t>
+        </is>
+      </c>
+      <c r="DQ1" s="1" t="inlineStr">
+        <is>
+          <t>The North Face (List)</t>
+        </is>
+      </c>
+      <c r="DR1" s="1" t="inlineStr">
+        <is>
+          <t>Woodbird (List)</t>
+        </is>
+      </c>
+      <c r="DS1" s="1" t="inlineStr">
+        <is>
+          <t>Birkenstock (List)</t>
+        </is>
+      </c>
+      <c r="DT1" s="1" t="inlineStr">
+        <is>
+          <t>Carhartt WIP (List)</t>
+        </is>
+      </c>
+      <c r="DU1" s="1" t="inlineStr">
+        <is>
+          <t>Samsøe Samsøe (List)</t>
+        </is>
+      </c>
+      <c r="DV1" s="1" t="inlineStr">
+        <is>
+          <t>A.Kjærbede (List)</t>
+        </is>
+      </c>
+      <c r="DW1" s="1" t="inlineStr">
+        <is>
+          <t>Muli Collection (List)</t>
+        </is>
+      </c>
+      <c r="DX1" s="1" t="inlineStr">
+        <is>
+          <t>Pavement (List)</t>
+        </is>
+      </c>
+      <c r="DY1" s="1" t="inlineStr">
+        <is>
+          <t>Aim'n (List)</t>
+        </is>
+      </c>
+      <c r="DZ1" s="1" t="inlineStr">
+        <is>
+          <t>Polo Ralph Lauren (List)</t>
+        </is>
+      </c>
+      <c r="EA1" s="1" t="inlineStr">
+        <is>
+          <t>UGG (List)</t>
+        </is>
+      </c>
+      <c r="EB1" s="1" t="inlineStr">
+        <is>
+          <t>Converse (List)</t>
+        </is>
+      </c>
+      <c r="EC1" s="1" t="inlineStr">
+        <is>
+          <t>Abrand Jeans (List)</t>
+        </is>
+      </c>
+      <c r="ED1" s="1" t="inlineStr">
+        <is>
+          <t>Les Deux (List)</t>
+        </is>
+      </c>
+      <c r="EE1" s="1" t="inlineStr">
+        <is>
+          <t>Sneaky Steve (List)</t>
+        </is>
+      </c>
+      <c r="EF1" s="1" t="inlineStr">
+        <is>
+          <t>Asics (List)</t>
+        </is>
+      </c>
+      <c r="EG1" s="1" t="inlineStr">
+        <is>
+          <t>Calvin Klein Underwear (List)</t>
+        </is>
+      </c>
+      <c r="EH1" s="1" t="inlineStr">
+        <is>
+          <t>Hunkemöller (List)</t>
+        </is>
+      </c>
+      <c r="EI1" s="1" t="inlineStr">
+        <is>
+          <t>Ciszere (List)</t>
+        </is>
+      </c>
+      <c r="EJ1" s="1" t="inlineStr">
+        <is>
+          <t>Inuikii (List)</t>
+        </is>
+      </c>
+      <c r="EK1" s="1" t="inlineStr">
+        <is>
+          <t>One Teaspoon (List)</t>
+        </is>
+      </c>
+      <c r="EL1" s="1" t="inlineStr">
+        <is>
+          <t>Hunter (List)</t>
+        </is>
+      </c>
+      <c r="EM1" s="1" t="inlineStr">
+        <is>
+          <t>DORINA (List)</t>
+        </is>
+      </c>
+      <c r="EN1" s="1" t="inlineStr">
+        <is>
+          <t>Diesel (List)</t>
+        </is>
+      </c>
+      <c r="EO1" s="1" t="inlineStr">
+        <is>
+          <t>Gant (List)</t>
+        </is>
+      </c>
+      <c r="EP1" s="1" t="inlineStr">
+        <is>
+          <t>Puma (List)</t>
+        </is>
+      </c>
+      <c r="EQ1" s="1" t="inlineStr">
+        <is>
+          <t>MONO (List)</t>
+        </is>
+      </c>
+      <c r="ER1" s="1" t="inlineStr">
+        <is>
+          <t>Colmar (List)</t>
+        </is>
+      </c>
+      <c r="ES1" s="1" t="inlineStr">
+        <is>
+          <t>Solid (List)</t>
+        </is>
+      </c>
+      <c r="ET1" s="1" t="inlineStr">
+        <is>
+          <t>ATP ATELIER (List)</t>
+        </is>
+      </c>
+      <c r="EU1" s="1" t="inlineStr">
+        <is>
+          <t>Rains (List)</t>
+        </is>
+      </c>
+      <c r="EV1" s="1" t="inlineStr">
+        <is>
+          <t>Bye Bra (List)</t>
+        </is>
+      </c>
+      <c r="EW1" s="1" t="inlineStr">
+        <is>
+          <t>Pilgrim (List)</t>
+        </is>
+      </c>
+      <c r="EX1" s="1" t="inlineStr">
+        <is>
+          <t>Mads Nørgaard (List)</t>
+        </is>
+      </c>
+      <c r="EY1" s="1" t="inlineStr">
+        <is>
+          <t>Havaianas (List)</t>
+        </is>
+      </c>
+      <c r="EZ1" s="1" t="inlineStr">
+        <is>
+          <t>Brand Island (List)</t>
+        </is>
+      </c>
+      <c r="FA1" s="1" t="inlineStr">
+        <is>
+          <t>Le Specs (List)</t>
+        </is>
+      </c>
+      <c r="FB1" s="1" t="inlineStr">
+        <is>
+          <t>Casual Friday (List)</t>
+        </is>
+      </c>
+      <c r="FC1" s="1" t="inlineStr">
+        <is>
+          <t>STICKYBESTIE (List)</t>
+        </is>
+      </c>
+      <c r="FD1" s="1" t="inlineStr">
+        <is>
+          <t>Selected Femme (List)</t>
+        </is>
+      </c>
+      <c r="FE1" s="1" t="inlineStr">
+        <is>
+          <t>OBJECT (List)</t>
+        </is>
+      </c>
+      <c r="FF1" s="1" t="inlineStr">
+        <is>
+          <t>Bluebella (List)</t>
+        </is>
+      </c>
+      <c r="FG1" s="1" t="inlineStr">
+        <is>
+          <t>Björn Borg (List)</t>
+        </is>
+      </c>
+      <c r="FH1" s="1" t="inlineStr">
+        <is>
+          <t>ANNARR (List)</t>
+        </is>
+      </c>
+      <c r="FI1" s="1" t="inlineStr">
+        <is>
+          <t>By Billgren (List)</t>
+        </is>
+      </c>
+      <c r="FJ1" s="1" t="inlineStr">
+        <is>
+          <t>JDY (List)</t>
+        </is>
+      </c>
+      <c r="FK1" s="1" t="inlineStr">
+        <is>
+          <t>Spanx (List)</t>
+        </is>
+      </c>
+      <c r="FL1" s="1" t="inlineStr">
+        <is>
+          <t>Juicy Couture (List)</t>
+        </is>
+      </c>
+      <c r="FM1" s="1" t="inlineStr">
+        <is>
+          <t>Michael Kors (List)</t>
+        </is>
+      </c>
+      <c r="FN1" s="1" t="inlineStr">
+        <is>
+          <t>IRO (List)</t>
+        </is>
+      </c>
+      <c r="FO1" s="1" t="inlineStr">
+        <is>
+          <t>VANS (List)</t>
+        </is>
+      </c>
+      <c r="FP1" s="1" t="inlineStr">
+        <is>
+          <t>Dockers (List)</t>
+        </is>
+      </c>
+      <c r="FQ1" s="1" t="inlineStr">
+        <is>
+          <t>OAS (List)</t>
+        </is>
+      </c>
+      <c r="FR1" s="1" t="inlineStr">
+        <is>
+          <t>Marc Jacobs (List)</t>
+        </is>
+      </c>
+      <c r="FS1" s="1" t="inlineStr">
+        <is>
+          <t>Timberland (List)</t>
+        </is>
+      </c>
+      <c r="FT1" s="1" t="inlineStr">
+        <is>
+          <t>Corlin Eyewear (List)</t>
+        </is>
+      </c>
+      <c r="FU1" s="1" t="inlineStr">
+        <is>
+          <t>DAY ET (List)</t>
+        </is>
+      </c>
+      <c r="FV1" s="1" t="inlineStr">
+        <is>
+          <t>J Lindeberg (List)</t>
+        </is>
+      </c>
+      <c r="FW1" s="1" t="inlineStr">
+        <is>
+          <t>Bread &amp; Boxers (List)</t>
+        </is>
+      </c>
+      <c r="FX1" s="1" t="inlineStr">
+        <is>
+          <t>Le Bonnet (List)</t>
+        </is>
+      </c>
+      <c r="FY1" s="1" t="inlineStr">
+        <is>
+          <t>Moon Boot (List)</t>
+        </is>
+      </c>
+      <c r="FZ1" s="1" t="inlineStr">
+        <is>
+          <t>Tommy Jeans (List)</t>
+        </is>
+      </c>
+      <c r="GA1" s="1" t="inlineStr">
+        <is>
+          <t>Columbia (List)</t>
+        </is>
+      </c>
+      <c r="GB1" s="1" t="inlineStr">
+        <is>
+          <t>Dickies (List)</t>
+        </is>
+      </c>
+      <c r="GC1" s="1" t="inlineStr">
+        <is>
+          <t>GABBA (List)</t>
+        </is>
+      </c>
+      <c r="GD1" s="1" t="inlineStr">
+        <is>
+          <t>Mercer Amsterdam (List)</t>
+        </is>
+      </c>
+      <c r="GE1" s="1" t="inlineStr">
+        <is>
+          <t>JJXX (List)</t>
+        </is>
+      </c>
+      <c r="GF1" s="1" t="inlineStr">
+        <is>
+          <t>Calvin Klein Jeans (List)</t>
+        </is>
+      </c>
+      <c r="GG1" s="1" t="inlineStr">
+        <is>
+          <t>Teva (List)</t>
+        </is>
+      </c>
+      <c r="GH1" s="1" t="inlineStr">
+        <is>
+          <t>Scholl (List)</t>
+        </is>
+      </c>
+      <c r="GI1" s="1" t="inlineStr">
+        <is>
+          <t>Messy Weekend (List)</t>
+        </is>
+      </c>
+      <c r="GJ1" s="1" t="inlineStr">
+        <is>
+          <t>Magic Bodyfashion (List)</t>
+        </is>
+      </c>
+      <c r="GK1" s="1" t="inlineStr">
+        <is>
+          <t>Cras (List)</t>
+        </is>
+      </c>
+      <c r="GL1" s="1" t="inlineStr">
+        <is>
+          <t>Playboy (List)</t>
+        </is>
+      </c>
+      <c r="GM1" s="1" t="inlineStr">
+        <is>
+          <t>Shepherd (List)</t>
+        </is>
+      </c>
+      <c r="GN1" s="1" t="inlineStr">
+        <is>
+          <t>ROCKANDBLUE (List)</t>
+        </is>
+      </c>
+      <c r="GO1" s="1" t="inlineStr">
+        <is>
+          <t>Neuw (List)</t>
+        </is>
+      </c>
+      <c r="GP1" s="1" t="inlineStr">
+        <is>
           <t>Lyle &amp; Scott (List)</t>
         </is>
       </c>
-      <c r="CX1" s="1" t="inlineStr">
-        <is>
-          <t>Dr Denim (List)</t>
-        </is>
-      </c>
-      <c r="CY1" s="1" t="inlineStr">
-        <is>
-          <t>GABBA (List)</t>
-        </is>
-      </c>
-      <c r="CZ1" s="1" t="inlineStr">
-        <is>
-          <t>Les Deux (List)</t>
-        </is>
-      </c>
-      <c r="DA1" s="1" t="inlineStr">
-        <is>
-          <t>Björn Borg (List)</t>
-        </is>
-      </c>
-      <c r="DB1" s="1" t="inlineStr">
-        <is>
-          <t>Columbia (List)</t>
-        </is>
-      </c>
-      <c r="DC1" s="1" t="inlineStr">
-        <is>
-          <t>Birkenstock (List)</t>
-        </is>
-      </c>
-      <c r="DD1" s="1" t="inlineStr">
-        <is>
-          <t>Selected Femme (List)</t>
-        </is>
-      </c>
-      <c r="DE1" s="1" t="inlineStr">
-        <is>
-          <t>Moon Boot (List)</t>
-        </is>
-      </c>
-      <c r="DF1" s="1" t="inlineStr">
-        <is>
-          <t>Inuikii (List)</t>
-        </is>
-      </c>
-      <c r="DG1" s="1" t="inlineStr">
-        <is>
-          <t>True Religion (List)</t>
-        </is>
-      </c>
-      <c r="DH1" s="1" t="inlineStr">
-        <is>
-          <t>Neuw (List)</t>
-        </is>
-      </c>
-      <c r="DI1" s="1" t="inlineStr">
-        <is>
-          <t>IRO (List)</t>
-        </is>
-      </c>
-      <c r="DJ1" s="1" t="inlineStr">
-        <is>
-          <t>Only &amp; Sons (List)</t>
-        </is>
-      </c>
-      <c r="DK1" s="1" t="inlineStr">
-        <is>
-          <t>Teva (List)</t>
-        </is>
-      </c>
-      <c r="DL1" s="1" t="inlineStr">
-        <is>
-          <t>Casual Friday (List)</t>
-        </is>
-      </c>
-      <c r="DM1" s="1" t="inlineStr">
-        <is>
-          <t>Pieces (List)</t>
-        </is>
-      </c>
-      <c r="DN1" s="1" t="inlineStr">
-        <is>
-          <t>Abrand Jeans (List)</t>
-        </is>
-      </c>
-      <c r="DO1" s="1" t="inlineStr">
-        <is>
-          <t>DORINA (List)</t>
-        </is>
-      </c>
-      <c r="DP1" s="1" t="inlineStr">
-        <is>
-          <t>Dockers (List)</t>
-        </is>
-      </c>
-      <c r="DQ1" s="1" t="inlineStr">
-        <is>
-          <t>Aim'n (List)</t>
-        </is>
-      </c>
-      <c r="DR1" s="1" t="inlineStr">
-        <is>
-          <t>Colmar (List)</t>
-        </is>
-      </c>
-      <c r="DS1" s="1" t="inlineStr">
+      <c r="GQ1" s="1" t="inlineStr">
         <is>
           <t>Daily Paper (List)</t>
-        </is>
-      </c>
-      <c r="DT1" s="1" t="inlineStr">
-        <is>
-          <t>Spanx (List)</t>
-        </is>
-      </c>
-      <c r="DU1" s="1" t="inlineStr">
-        <is>
-          <t>Ciszere (List)</t>
-        </is>
-      </c>
-      <c r="DV1" s="1" t="inlineStr">
-        <is>
-          <t>Lois Jeans (List)</t>
-        </is>
-      </c>
-      <c r="DW1" s="1" t="inlineStr">
-        <is>
-          <t>By Malene Birger (List)</t>
-        </is>
-      </c>
-      <c r="DX1" s="1" t="inlineStr">
-        <is>
-          <t>Woodbird (List)</t>
-        </is>
-      </c>
-      <c r="DY1" s="1" t="inlineStr">
-        <is>
-          <t>JDY (List)</t>
-        </is>
-      </c>
-      <c r="DZ1" s="1" t="inlineStr">
-        <is>
-          <t>Mads Nørgaard (List)</t>
-        </is>
-      </c>
-      <c r="EA1" s="1" t="inlineStr">
-        <is>
-          <t>Corlin Eyewear (List)</t>
-        </is>
-      </c>
-      <c r="EB1" s="1" t="inlineStr">
-        <is>
-          <t>Tommy Jeans (List)</t>
-        </is>
-      </c>
-      <c r="EC1" s="1" t="inlineStr">
-        <is>
-          <t>Jack &amp; Jones (List)</t>
-        </is>
-      </c>
-      <c r="ED1" s="1" t="inlineStr">
-        <is>
-          <t>Samsøe Samsøe (List)</t>
-        </is>
-      </c>
-      <c r="EE1" s="1" t="inlineStr">
-        <is>
-          <t>Diesel (List)</t>
-        </is>
-      </c>
-      <c r="EF1" s="1" t="inlineStr">
-        <is>
-          <t>Hunter (List)</t>
-        </is>
-      </c>
-      <c r="EG1" s="1" t="inlineStr">
-        <is>
-          <t>Rains (List)</t>
-        </is>
-      </c>
-      <c r="EH1" s="1" t="inlineStr">
-        <is>
-          <t>Neo Noir (List)</t>
-        </is>
-      </c>
-      <c r="EI1" s="1" t="inlineStr">
-        <is>
-          <t>Pavement (List)</t>
-        </is>
-      </c>
-      <c r="EJ1" s="1" t="inlineStr">
-        <is>
-          <t>BECKSÖNDERGAARD (List)</t>
-        </is>
-      </c>
-      <c r="EK1" s="1" t="inlineStr">
-        <is>
-          <t>ANNARR (List)</t>
-        </is>
-      </c>
-      <c r="EL1" s="1" t="inlineStr">
-        <is>
-          <t>Sneaky Steve (List)</t>
-        </is>
-      </c>
-      <c r="EM1" s="1" t="inlineStr">
-        <is>
-          <t>OBJECT (List)</t>
-        </is>
-      </c>
-      <c r="EN1" s="1" t="inlineStr">
-        <is>
-          <t>Le Specs (List)</t>
-        </is>
-      </c>
-      <c r="EO1" s="1" t="inlineStr">
-        <is>
-          <t>Playboy (List)</t>
-        </is>
-      </c>
-      <c r="EP1" s="1" t="inlineStr">
-        <is>
-          <t>Le Bonnet (List)</t>
-        </is>
-      </c>
-      <c r="EQ1" s="1" t="inlineStr">
-        <is>
-          <t>STICKYBESTIE (List)</t>
-        </is>
-      </c>
-      <c r="ER1" s="1" t="inlineStr">
-        <is>
-          <t>Only (List)</t>
-        </is>
-      </c>
-      <c r="ES1" s="1" t="inlineStr">
-        <is>
-          <t>A.Kjærbede (List)</t>
-        </is>
-      </c>
-      <c r="ET1" s="1" t="inlineStr">
-        <is>
-          <t>Messy Weekend (List)</t>
-        </is>
-      </c>
-      <c r="EU1" s="1" t="inlineStr">
-        <is>
-          <t>Malina (List)</t>
-        </is>
-      </c>
-      <c r="EV1" s="1" t="inlineStr">
-        <is>
-          <t>Selected Men (List)</t>
-        </is>
-      </c>
-      <c r="EW1" s="1" t="inlineStr">
-        <is>
-          <t>Converse (List)</t>
-        </is>
-      </c>
-      <c r="EX1" s="1" t="inlineStr">
-        <is>
-          <t>Michael Kors (List)</t>
-        </is>
-      </c>
-      <c r="EY1" s="1" t="inlineStr">
-        <is>
-          <t>J Lindeberg (List)</t>
-        </is>
-      </c>
-      <c r="EZ1" s="1" t="inlineStr">
-        <is>
-          <t>Juicy Couture (List)</t>
-        </is>
-      </c>
-      <c r="FA1" s="1" t="inlineStr">
-        <is>
-          <t>Shepherd (List)</t>
-        </is>
-      </c>
-      <c r="FB1" s="1" t="inlineStr">
-        <is>
-          <t>New Balance (List)</t>
-        </is>
-      </c>
-      <c r="FC1" s="1" t="inlineStr">
-        <is>
-          <t>Marc Jacobs (List)</t>
-        </is>
-      </c>
-      <c r="FD1" s="1" t="inlineStr">
-        <is>
-          <t>ROCKANDBLUE (List)</t>
-        </is>
-      </c>
-      <c r="FE1" s="1" t="inlineStr">
-        <is>
-          <t>Vero Moda (List)</t>
-        </is>
-      </c>
-      <c r="FF1" s="1" t="inlineStr">
-        <is>
-          <t>UGG (List)</t>
-        </is>
-      </c>
-      <c r="FG1" s="1" t="inlineStr">
-        <is>
-          <t>Levi's (List)</t>
-        </is>
-      </c>
-      <c r="FH1" s="1" t="inlineStr">
-        <is>
-          <t>Bluebella (List)</t>
-        </is>
-      </c>
-      <c r="FI1" s="1" t="inlineStr">
-        <is>
-          <t>OAS (List)</t>
-        </is>
-      </c>
-      <c r="FJ1" s="1" t="inlineStr">
-        <is>
-          <t>Bread &amp; Boxers (List)</t>
-        </is>
-      </c>
-      <c r="FK1" s="1" t="inlineStr">
-        <is>
-          <t>Dickies (List)</t>
-        </is>
-      </c>
-      <c r="FL1" s="1" t="inlineStr">
-        <is>
-          <t>Calvin Klein Jeans (List)</t>
-        </is>
-      </c>
-      <c r="FM1" s="1" t="inlineStr">
-        <is>
-          <t>Bye Bra (List)</t>
-        </is>
-      </c>
-      <c r="FN1" s="1" t="inlineStr">
-        <is>
-          <t>Nelly (List)</t>
-        </is>
-      </c>
-      <c r="FO1" s="1" t="inlineStr">
-        <is>
-          <t>Mercer Amsterdam (List)</t>
-        </is>
-      </c>
-      <c r="FP1" s="1" t="inlineStr">
-        <is>
-          <t>ATP ATELIER (List)</t>
-        </is>
-      </c>
-      <c r="FQ1" s="1" t="inlineStr">
-        <is>
-          <t>Nike (List)</t>
-        </is>
-      </c>
-      <c r="FR1" s="1" t="inlineStr">
-        <is>
-          <t>Que Sera Sera (List)</t>
-        </is>
-      </c>
-      <c r="FS1" s="1" t="inlineStr">
-        <is>
-          <t>By Billgren (List)</t>
-        </is>
-      </c>
-      <c r="FT1" s="1" t="inlineStr">
-        <is>
-          <t>Carhartt WIP (List)</t>
-        </is>
-      </c>
-      <c r="FU1" s="1" t="inlineStr">
-        <is>
-          <t>Havaianas (List)</t>
-        </is>
-      </c>
-      <c r="FV1" s="1" t="inlineStr">
-        <is>
-          <t>MONO (List)</t>
-        </is>
-      </c>
-      <c r="FW1" s="1" t="inlineStr">
-        <is>
-          <t>Calvin Klein Underwear (List)</t>
-        </is>
-      </c>
-      <c r="FX1" s="1" t="inlineStr">
-        <is>
-          <t>Asics (List)</t>
-        </is>
-      </c>
-      <c r="FY1" s="1" t="inlineStr">
-        <is>
-          <t>DAY ET (List)</t>
-        </is>
-      </c>
-      <c r="FZ1" s="1" t="inlineStr">
-        <is>
-          <t>Hunkemöller (List)</t>
-        </is>
-      </c>
-      <c r="GA1" s="1" t="inlineStr">
-        <is>
-          <t>Puma (List)</t>
-        </is>
-      </c>
-      <c r="GB1" s="1" t="inlineStr">
-        <is>
-          <t>Cras (List)</t>
-        </is>
-      </c>
-      <c r="GC1" s="1" t="inlineStr">
-        <is>
-          <t>Brand Island (List)</t>
-        </is>
-      </c>
-      <c r="GD1" s="1" t="inlineStr">
-        <is>
-          <t>Gina Tricot (List)</t>
-        </is>
-      </c>
-      <c r="GE1" s="1" t="inlineStr">
-        <is>
-          <t>Scholl (List)</t>
-        </is>
-      </c>
-      <c r="GF1" s="1" t="inlineStr">
-        <is>
-          <t>Gant (List)</t>
-        </is>
-      </c>
-      <c r="GG1" s="1" t="inlineStr">
-        <is>
-          <t>Polo Ralph Lauren (List)</t>
-        </is>
-      </c>
-      <c r="GH1" s="1" t="inlineStr">
-        <is>
-          <t>Timberland (List)</t>
-        </is>
-      </c>
-      <c r="GI1" s="1" t="inlineStr">
-        <is>
-          <t>Magic Bodyfashion (List)</t>
-        </is>
-      </c>
-      <c r="GJ1" s="1" t="inlineStr">
-        <is>
-          <t>Adidas Originals (List)</t>
-        </is>
-      </c>
-      <c r="GK1" s="1" t="inlineStr">
-        <is>
-          <t>The North Face (List)</t>
-        </is>
-      </c>
-      <c r="GL1" s="1" t="inlineStr">
-        <is>
-          <t>JJXX (List)</t>
-        </is>
-      </c>
-      <c r="GM1" s="1" t="inlineStr">
-        <is>
-          <t>One Teaspoon (List)</t>
-        </is>
-      </c>
-      <c r="GN1" s="1" t="inlineStr">
-        <is>
-          <t>Muli Collection (List)</t>
-        </is>
-      </c>
-      <c r="GO1" s="1" t="inlineStr">
-        <is>
-          <t>VANS (List)</t>
-        </is>
-      </c>
-      <c r="GP1" s="1" t="inlineStr">
-        <is>
-          <t>Solid (List)</t>
-        </is>
-      </c>
-      <c r="GQ1" s="1" t="inlineStr">
-        <is>
-          <t>Pilgrim (List)</t>
         </is>
       </c>
     </row>
@@ -4583,568 +4915,568 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>1894974</v>
       </c>
       <c r="C3" t="n">
+        <v>252617</v>
+      </c>
+      <c r="D3" t="n">
+        <v>290506</v>
+      </c>
+      <c r="E3" t="n">
+        <v>120751</v>
+      </c>
+      <c r="F3" t="n">
+        <v>134394</v>
+      </c>
+      <c r="G3" t="n">
+        <v>169070</v>
+      </c>
+      <c r="H3" t="n">
+        <v>108946</v>
+      </c>
+      <c r="I3" t="n">
+        <v>101891</v>
+      </c>
+      <c r="J3" t="n">
+        <v>81262</v>
+      </c>
+      <c r="K3" t="n">
+        <v>82521</v>
+      </c>
+      <c r="L3" t="n">
+        <v>34987</v>
+      </c>
+      <c r="M3" t="n">
+        <v>89108</v>
+      </c>
+      <c r="N3" t="n">
+        <v>70490</v>
+      </c>
+      <c r="O3" t="n">
+        <v>45000</v>
+      </c>
+      <c r="P3" t="n">
+        <v>61938</v>
+      </c>
+      <c r="Q3" t="n">
         <v>30065</v>
       </c>
-      <c r="D3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" t="n">
+      <c r="R3" t="n">
+        <v>10695</v>
+      </c>
+      <c r="S3" t="n">
+        <v>28381</v>
+      </c>
+      <c r="T3" t="n">
+        <v>21791</v>
+      </c>
+      <c r="U3" t="n">
+        <v>7731</v>
+      </c>
+      <c r="V3" t="n">
+        <v>9035</v>
+      </c>
+      <c r="W3" t="n">
+        <v>61743</v>
+      </c>
+      <c r="X3" t="n">
+        <v>29537</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>14092</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>52481</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>6769</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>20954</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>11693</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>2195</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>37938</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>10235</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>5237</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>14985</v>
+      </c>
+      <c r="AI3" t="n">
         <v>20446</v>
       </c>
-      <c r="F3" t="n">
+      <c r="AJ3" t="n">
+        <v>17490</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>2118</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>11536</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>8105</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>14429</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>7597</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>12442</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>7192</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>9071</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>4198</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>5974</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>3499</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>4799</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>5396</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>5199</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>2098</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>1595</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>2674</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>12089</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>4280</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>988</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>629</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>349</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>299</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>568</v>
+      </c>
+      <c r="BL3" t="n">
         <v>496</v>
       </c>
-      <c r="G3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" t="n">
+      <c r="BM3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>299</v>
+      </c>
+      <c r="BO3" t="n">
+        <v>314</v>
+      </c>
+      <c r="BP3" t="n">
+        <v>499</v>
+      </c>
+      <c r="BQ3" t="n">
+        <v>598</v>
+      </c>
+      <c r="BR3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD3" t="n">
+        <v>2539</v>
+      </c>
+      <c r="CE3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK3" t="n">
+        <v>549</v>
+      </c>
+      <c r="CL3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW3" t="n">
+        <v>2083325</v>
+      </c>
+      <c r="CX3" t="n">
+        <v>260992</v>
+      </c>
+      <c r="CY3" t="n">
+        <v>297828</v>
+      </c>
+      <c r="CZ3" t="n">
+        <v>150580</v>
+      </c>
+      <c r="DA3" t="n">
+        <v>148222</v>
+      </c>
+      <c r="DB3" t="n">
+        <v>172450</v>
+      </c>
+      <c r="DC3" t="n">
+        <v>110961</v>
+      </c>
+      <c r="DD3" t="n">
+        <v>115977</v>
+      </c>
+      <c r="DE3" t="n">
+        <v>98042</v>
+      </c>
+      <c r="DF3" t="n">
+        <v>87401</v>
+      </c>
+      <c r="DG3" t="n">
+        <v>38267</v>
+      </c>
+      <c r="DH3" t="n">
+        <v>91109</v>
+      </c>
+      <c r="DI3" t="n">
+        <v>74972</v>
+      </c>
+      <c r="DJ3" t="n">
+        <v>45000</v>
+      </c>
+      <c r="DK3" t="n">
+        <v>64573</v>
+      </c>
+      <c r="DL3" t="n">
+        <v>33305</v>
+      </c>
+      <c r="DM3" t="n">
+        <v>10695</v>
+      </c>
+      <c r="DN3" t="n">
+        <v>28381</v>
+      </c>
+      <c r="DO3" t="n">
+        <v>21791</v>
+      </c>
+      <c r="DP3" t="n">
+        <v>8921</v>
+      </c>
+      <c r="DQ3" t="n">
+        <v>10195</v>
+      </c>
+      <c r="DR3" t="n">
+        <v>65143</v>
+      </c>
+      <c r="DS3" t="n">
         <v>29537</v>
       </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" t="n">
+      <c r="DT3" t="n">
+        <v>14092</v>
+      </c>
+      <c r="DU3" t="n">
+        <v>52871</v>
+      </c>
+      <c r="DV3" t="n">
+        <v>7329</v>
+      </c>
+      <c r="DW3" t="n">
+        <v>20954</v>
+      </c>
+      <c r="DX3" t="n">
+        <v>11693</v>
+      </c>
+      <c r="DY3" t="n">
+        <v>2195</v>
+      </c>
+      <c r="DZ3" t="n">
+        <v>39616</v>
+      </c>
+      <c r="EA3" t="n">
+        <v>10895</v>
+      </c>
+      <c r="EB3" t="n">
+        <v>5697</v>
+      </c>
+      <c r="EC3" t="n">
+        <v>14985</v>
+      </c>
+      <c r="ED3" t="n">
+        <v>21886</v>
+      </c>
+      <c r="EE3" t="n">
+        <v>17490</v>
+      </c>
+      <c r="EF3" t="n">
+        <v>2798</v>
+      </c>
+      <c r="EG3" t="n">
+        <v>11536</v>
+      </c>
+      <c r="EH3" t="n">
+        <v>9931</v>
+      </c>
+      <c r="EI3" t="n">
+        <v>14789</v>
+      </c>
+      <c r="EJ3" t="n">
+        <v>7597</v>
+      </c>
+      <c r="EK3" t="n">
+        <v>15037</v>
+      </c>
+      <c r="EL3" t="n">
+        <v>7192</v>
+      </c>
+      <c r="EM3" t="n">
+        <v>9446</v>
+      </c>
+      <c r="EN3" t="n">
+        <v>4198</v>
+      </c>
+      <c r="EO3" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP3" t="n">
+        <v>7895</v>
+      </c>
+      <c r="EQ3" t="n">
+        <v>3499</v>
+      </c>
+      <c r="ER3" t="n">
+        <v>4799</v>
+      </c>
+      <c r="ES3" t="n">
+        <v>6198</v>
+      </c>
+      <c r="ET3" t="n">
+        <v>5199</v>
+      </c>
+      <c r="EU3" t="n">
+        <v>2098</v>
+      </c>
+      <c r="EV3" t="n">
+        <v>1595</v>
+      </c>
+      <c r="EW3" t="n">
+        <v>2674</v>
+      </c>
+      <c r="EX3" t="n">
+        <v>12089</v>
+      </c>
+      <c r="EY3" t="n">
+        <v>4280</v>
+      </c>
+      <c r="EZ3" t="n">
+        <v>1898</v>
+      </c>
+      <c r="FA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB3" t="n">
+        <v>899</v>
+      </c>
+      <c r="FC3" t="n">
+        <v>349</v>
+      </c>
+      <c r="FD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE3" t="n">
+        <v>600</v>
+      </c>
+      <c r="FF3" t="n">
+        <v>1138</v>
+      </c>
+      <c r="FG3" t="n">
+        <v>496</v>
+      </c>
+      <c r="FH3" t="n">
+        <v>0</v>
+      </c>
+      <c r="FI3" t="n">
+        <v>499</v>
+      </c>
+      <c r="FJ3" t="n">
+        <v>629</v>
+      </c>
+      <c r="FK3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="FL3" t="n">
+        <v>1198</v>
+      </c>
+      <c r="FM3" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN3" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO3" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP3" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="FR3" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS3" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT3" t="n">
+        <v>0</v>
+      </c>
+      <c r="FU3" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV3" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW3" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX3" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY3" t="n">
         <v>2539</v>
       </c>
-      <c r="K3" t="n">
-        <v>7597</v>
-      </c>
-      <c r="L3" t="n">
-        <v>81262</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>70490</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>629</v>
-      </c>
-      <c r="R3" t="n">
-        <v>120751</v>
-      </c>
-      <c r="S3" t="n">
-        <v>14985</v>
-      </c>
-      <c r="T3" t="n">
-        <v>9071</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" t="n">
-        <v>2195</v>
-      </c>
-      <c r="W3" t="n">
-        <v>4799</v>
-      </c>
-      <c r="X3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>499</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>14429</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>10695</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>28381</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>61743</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>314</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>12089</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>61938</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>52481</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>4198</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>7192</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>2098</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>108946</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>11693</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>7731</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>17490</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>299</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>349</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>134394</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>6769</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>21791</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>89108</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>5237</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>598</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>290506</v>
-      </c>
-      <c r="BH3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>101891</v>
-      </c>
-      <c r="BK3" t="n">
-        <v>10235</v>
-      </c>
-      <c r="BL3" t="n">
-        <v>82521</v>
-      </c>
-      <c r="BM3" t="n">
-        <v>568</v>
-      </c>
-      <c r="BN3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ3" t="n">
-        <v>549</v>
-      </c>
-      <c r="BR3" t="n">
-        <v>1595</v>
-      </c>
-      <c r="BS3" t="n">
-        <v>1894974</v>
-      </c>
-      <c r="BT3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU3" t="n">
-        <v>5199</v>
-      </c>
-      <c r="BV3" t="n">
-        <v>45000</v>
-      </c>
-      <c r="BW3" t="n">
-        <v>169070</v>
-      </c>
-      <c r="BX3" t="n">
-        <v>299</v>
-      </c>
-      <c r="BY3" t="n">
-        <v>14092</v>
-      </c>
-      <c r="BZ3" t="n">
-        <v>4280</v>
-      </c>
-      <c r="CA3" t="n">
-        <v>3499</v>
-      </c>
-      <c r="CB3" t="n">
-        <v>11536</v>
-      </c>
-      <c r="CC3" t="n">
-        <v>2118</v>
-      </c>
-      <c r="CD3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE3" t="n">
-        <v>8105</v>
-      </c>
-      <c r="CF3" t="n">
-        <v>5974</v>
-      </c>
-      <c r="CG3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH3" t="n">
-        <v>988</v>
-      </c>
-      <c r="CI3" t="n">
-        <v>34987</v>
-      </c>
-      <c r="CJ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CK3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL3" t="n">
-        <v>37938</v>
-      </c>
-      <c r="CM3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO3" t="n">
-        <v>252617</v>
-      </c>
-      <c r="CP3" t="n">
-        <v>9035</v>
-      </c>
-      <c r="CQ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CR3" t="n">
-        <v>12442</v>
-      </c>
-      <c r="CS3" t="n">
-        <v>20954</v>
-      </c>
-      <c r="CT3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CU3" t="n">
-        <v>5396</v>
-      </c>
-      <c r="CV3" t="n">
-        <v>2674</v>
-      </c>
-      <c r="CW3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CX3" t="n">
-        <v>33305</v>
-      </c>
-      <c r="CY3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CZ3" t="n">
-        <v>21886</v>
-      </c>
-      <c r="DA3" t="n">
-        <v>496</v>
-      </c>
-      <c r="DB3" t="n">
-        <v>0</v>
-      </c>
-      <c r="DC3" t="n">
-        <v>29537</v>
-      </c>
-      <c r="DD3" t="n">
-        <v>0</v>
-      </c>
-      <c r="DE3" t="n">
-        <v>2539</v>
-      </c>
-      <c r="DF3" t="n">
-        <v>7597</v>
-      </c>
-      <c r="DG3" t="n">
-        <v>98042</v>
-      </c>
-      <c r="DH3" t="n">
-        <v>0</v>
-      </c>
-      <c r="DI3" t="n">
-        <v>0</v>
-      </c>
-      <c r="DJ3" t="n">
-        <v>74972</v>
-      </c>
-      <c r="DK3" t="n">
-        <v>0</v>
-      </c>
-      <c r="DL3" t="n">
-        <v>899</v>
-      </c>
-      <c r="DM3" t="n">
-        <v>150580</v>
-      </c>
-      <c r="DN3" t="n">
-        <v>14985</v>
-      </c>
-      <c r="DO3" t="n">
-        <v>9446</v>
-      </c>
-      <c r="DP3" t="n">
-        <v>0</v>
-      </c>
-      <c r="DQ3" t="n">
-        <v>2195</v>
-      </c>
-      <c r="DR3" t="n">
-        <v>4799</v>
-      </c>
-      <c r="DS3" t="n">
-        <v>0</v>
-      </c>
-      <c r="DT3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="DU3" t="n">
-        <v>14789</v>
-      </c>
-      <c r="DV3" t="n">
-        <v>10695</v>
-      </c>
-      <c r="DW3" t="n">
-        <v>28381</v>
-      </c>
-      <c r="DX3" t="n">
-        <v>65143</v>
-      </c>
-      <c r="DY3" t="n">
-        <v>629</v>
-      </c>
-      <c r="DZ3" t="n">
-        <v>12089</v>
-      </c>
-      <c r="EA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="EB3" t="n">
-        <v>0</v>
-      </c>
-      <c r="EC3" t="n">
-        <v>64573</v>
-      </c>
-      <c r="ED3" t="n">
-        <v>52871</v>
-      </c>
-      <c r="EE3" t="n">
-        <v>4198</v>
-      </c>
-      <c r="EF3" t="n">
-        <v>7192</v>
-      </c>
-      <c r="EG3" t="n">
-        <v>2098</v>
-      </c>
-      <c r="EH3" t="n">
-        <v>110961</v>
-      </c>
-      <c r="EI3" t="n">
-        <v>11693</v>
-      </c>
-      <c r="EJ3" t="n">
-        <v>8921</v>
-      </c>
-      <c r="EK3" t="n">
-        <v>0</v>
-      </c>
-      <c r="EL3" t="n">
-        <v>17490</v>
-      </c>
-      <c r="EM3" t="n">
-        <v>600</v>
-      </c>
-      <c r="EN3" t="n">
-        <v>0</v>
-      </c>
-      <c r="EO3" t="n">
-        <v>0</v>
-      </c>
-      <c r="EP3" t="n">
-        <v>0</v>
-      </c>
-      <c r="EQ3" t="n">
-        <v>349</v>
-      </c>
-      <c r="ER3" t="n">
-        <v>148222</v>
-      </c>
-      <c r="ES3" t="n">
-        <v>7329</v>
-      </c>
-      <c r="ET3" t="n">
-        <v>0</v>
-      </c>
-      <c r="EU3" t="n">
-        <v>21791</v>
-      </c>
-      <c r="EV3" t="n">
-        <v>91109</v>
-      </c>
-      <c r="EW3" t="n">
-        <v>5697</v>
-      </c>
-      <c r="EX3" t="n">
-        <v>0</v>
-      </c>
-      <c r="EY3" t="n">
-        <v>0</v>
-      </c>
-      <c r="EZ3" t="n">
-        <v>1198</v>
-      </c>
-      <c r="FA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="FB3" t="n">
-        <v>297828</v>
-      </c>
-      <c r="FC3" t="n">
-        <v>0</v>
-      </c>
-      <c r="FD3" t="n">
-        <v>0</v>
-      </c>
-      <c r="FE3" t="n">
-        <v>115977</v>
-      </c>
-      <c r="FF3" t="n">
-        <v>10895</v>
-      </c>
-      <c r="FG3" t="n">
-        <v>87401</v>
-      </c>
-      <c r="FH3" t="n">
-        <v>1138</v>
-      </c>
-      <c r="FI3" t="n">
-        <v>0</v>
-      </c>
-      <c r="FJ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="FK3" t="n">
-        <v>0</v>
-      </c>
-      <c r="FL3" t="n">
+      <c r="FZ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF3" t="n">
         <v>1099</v>
       </c>
-      <c r="FM3" t="n">
-        <v>1595</v>
-      </c>
-      <c r="FN3" t="n">
-        <v>2083325</v>
-      </c>
-      <c r="FO3" t="n">
-        <v>0</v>
-      </c>
-      <c r="FP3" t="n">
-        <v>5199</v>
-      </c>
-      <c r="FQ3" t="n">
-        <v>45000</v>
-      </c>
-      <c r="FR3" t="n">
-        <v>172450</v>
-      </c>
-      <c r="FS3" t="n">
-        <v>499</v>
-      </c>
-      <c r="FT3" t="n">
-        <v>14092</v>
-      </c>
-      <c r="FU3" t="n">
-        <v>4280</v>
-      </c>
-      <c r="FV3" t="n">
-        <v>3499</v>
-      </c>
-      <c r="FW3" t="n">
-        <v>11536</v>
-      </c>
-      <c r="FX3" t="n">
-        <v>2798</v>
-      </c>
-      <c r="FY3" t="n">
-        <v>0</v>
-      </c>
-      <c r="FZ3" t="n">
-        <v>9931</v>
-      </c>
-      <c r="GA3" t="n">
-        <v>7895</v>
-      </c>
-      <c r="GB3" t="n">
-        <v>0</v>
-      </c>
-      <c r="GC3" t="n">
-        <v>1898</v>
-      </c>
-      <c r="GD3" t="n">
-        <v>38267</v>
-      </c>
-      <c r="GE3" t="n">
-        <v>0</v>
-      </c>
-      <c r="GF3" t="n">
-        <v>0</v>
-      </c>
       <c r="GG3" t="n">
-        <v>39616</v>
+        <v>0</v>
       </c>
       <c r="GH3" t="n">
         <v>0</v>
@@ -5153,28 +5485,28 @@
         <v>0</v>
       </c>
       <c r="GJ3" t="n">
-        <v>260992</v>
+        <v>0</v>
       </c>
       <c r="GK3" t="n">
-        <v>10195</v>
+        <v>0</v>
       </c>
       <c r="GL3" t="n">
         <v>0</v>
       </c>
       <c r="GM3" t="n">
-        <v>15037</v>
+        <v>0</v>
       </c>
       <c r="GN3" t="n">
-        <v>20954</v>
+        <v>0</v>
       </c>
       <c r="GO3" t="n">
         <v>0</v>
       </c>
       <c r="GP3" t="n">
-        <v>6198</v>
+        <v>0</v>
       </c>
       <c r="GQ3" t="n">
-        <v>2674</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -5184,598 +5516,598 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>2175291</v>
       </c>
       <c r="C4" t="n">
+        <v>279956</v>
+      </c>
+      <c r="D4" t="n">
+        <v>417767</v>
+      </c>
+      <c r="E4" t="n">
+        <v>119449</v>
+      </c>
+      <c r="F4" t="n">
+        <v>172659</v>
+      </c>
+      <c r="G4" t="n">
+        <v>609532</v>
+      </c>
+      <c r="H4" t="n">
+        <v>150290</v>
+      </c>
+      <c r="I4" t="n">
+        <v>117515</v>
+      </c>
+      <c r="J4" t="n">
+        <v>46286</v>
+      </c>
+      <c r="K4" t="n">
+        <v>84129</v>
+      </c>
+      <c r="L4" t="n">
+        <v>25843</v>
+      </c>
+      <c r="M4" t="n">
+        <v>60404</v>
+      </c>
+      <c r="N4" t="n">
+        <v>62064</v>
+      </c>
+      <c r="O4" t="n">
+        <v>45361</v>
+      </c>
+      <c r="P4" t="n">
+        <v>30801</v>
+      </c>
+      <c r="Q4" t="n">
         <v>32641</v>
       </c>
-      <c r="D4" t="n">
+      <c r="R4" t="n">
+        <v>33785</v>
+      </c>
+      <c r="S4" t="n">
+        <v>24484</v>
+      </c>
+      <c r="T4" t="n">
+        <v>8445</v>
+      </c>
+      <c r="U4" t="n">
+        <v>8616</v>
+      </c>
+      <c r="V4" t="n">
+        <v>19127</v>
+      </c>
+      <c r="W4" t="n">
+        <v>33115</v>
+      </c>
+      <c r="X4" t="n">
+        <v>13692</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>15894</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>23863</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>16751</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>15111</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>9803</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>5295</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>26689</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>12173</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>9447</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>17982</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>12521</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>8395</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>2038</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>8421</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>16259</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>10692</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>7097</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>7403</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>4039</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>3604</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>-5698</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>6396</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>-1437</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>11298</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>1290</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>1131</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>1587</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>3047</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>7381</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>848</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>1548</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>1095</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>249</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>-867</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>3071</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>260</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>1711</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>449</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>548</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>839</v>
+      </c>
+      <c r="BW4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX4" t="n">
+        <v>2399</v>
+      </c>
+      <c r="BY4" t="n">
+        <v>1299</v>
+      </c>
+      <c r="BZ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA4" t="n">
+        <v>1199</v>
+      </c>
+      <c r="CB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD4" t="n">
+        <v>-2399</v>
+      </c>
+      <c r="CE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH4" t="n">
         <v>599</v>
       </c>
-      <c r="E4" t="n">
-        <v>12521</v>
-      </c>
-      <c r="F4" t="n">
+      <c r="CI4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM4" t="n">
+        <v>639</v>
+      </c>
+      <c r="CN4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ4" t="n">
+        <v>1899</v>
+      </c>
+      <c r="CR4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW4" t="n">
+        <v>2377455</v>
+      </c>
+      <c r="CX4" t="n">
+        <v>284221</v>
+      </c>
+      <c r="CY4" t="n">
+        <v>421334</v>
+      </c>
+      <c r="CZ4" t="n">
+        <v>146118</v>
+      </c>
+      <c r="DA4" t="n">
+        <v>195921</v>
+      </c>
+      <c r="DB4" t="n">
+        <v>611692</v>
+      </c>
+      <c r="DC4" t="n">
+        <v>153305</v>
+      </c>
+      <c r="DD4" t="n">
+        <v>133734</v>
+      </c>
+      <c r="DE4" t="n">
+        <v>55566</v>
+      </c>
+      <c r="DF4" t="n">
+        <v>88729</v>
+      </c>
+      <c r="DG4" t="n">
+        <v>28642</v>
+      </c>
+      <c r="DH4" t="n">
+        <v>59143</v>
+      </c>
+      <c r="DI4" t="n">
+        <v>65383</v>
+      </c>
+      <c r="DJ4" t="n">
+        <v>45361</v>
+      </c>
+      <c r="DK4" t="n">
+        <v>32640</v>
+      </c>
+      <c r="DL4" t="n">
+        <v>37151</v>
+      </c>
+      <c r="DM4" t="n">
+        <v>33785</v>
+      </c>
+      <c r="DN4" t="n">
+        <v>24484</v>
+      </c>
+      <c r="DO4" t="n">
+        <v>13395</v>
+      </c>
+      <c r="DP4" t="n">
+        <v>10381</v>
+      </c>
+      <c r="DQ4" t="n">
+        <v>24187</v>
+      </c>
+      <c r="DR4" t="n">
+        <v>35865</v>
+      </c>
+      <c r="DS4" t="n">
+        <v>13692</v>
+      </c>
+      <c r="DT4" t="n">
+        <v>15894</v>
+      </c>
+      <c r="DU4" t="n">
+        <v>22783</v>
+      </c>
+      <c r="DV4" t="n">
+        <v>17101</v>
+      </c>
+      <c r="DW4" t="n">
+        <v>15111</v>
+      </c>
+      <c r="DX4" t="n">
+        <v>12593</v>
+      </c>
+      <c r="DY4" t="n">
+        <v>5295</v>
+      </c>
+      <c r="DZ4" t="n">
+        <v>27767</v>
+      </c>
+      <c r="EA4" t="n">
+        <v>13493</v>
+      </c>
+      <c r="EB4" t="n">
+        <v>10307</v>
+      </c>
+      <c r="EC4" t="n">
+        <v>17982</v>
+      </c>
+      <c r="ED4" t="n">
+        <v>13391</v>
+      </c>
+      <c r="EE4" t="n">
+        <v>8395</v>
+      </c>
+      <c r="EF4" t="n">
+        <v>3398</v>
+      </c>
+      <c r="EG4" t="n">
+        <v>9081</v>
+      </c>
+      <c r="EH4" t="n">
+        <v>19367</v>
+      </c>
+      <c r="EI4" t="n">
+        <v>10692</v>
+      </c>
+      <c r="EJ4" t="n">
+        <v>7097</v>
+      </c>
+      <c r="EK4" t="n">
+        <v>9043</v>
+      </c>
+      <c r="EL4" t="n">
+        <v>4277</v>
+      </c>
+      <c r="EM4" t="n">
+        <v>3484</v>
+      </c>
+      <c r="EN4" t="n">
+        <v>-5698</v>
+      </c>
+      <c r="EO4" t="n">
+        <v>6396</v>
+      </c>
+      <c r="EP4" t="n">
+        <v>-4797</v>
+      </c>
+      <c r="EQ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER4" t="n">
+        <v>11298</v>
+      </c>
+      <c r="ES4" t="n">
+        <v>1500</v>
+      </c>
+      <c r="ET4" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU4" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV4" t="n">
+        <v>1416</v>
+      </c>
+      <c r="EW4" t="n">
+        <v>1587</v>
+      </c>
+      <c r="EX4" t="n">
+        <v>3047</v>
+      </c>
+      <c r="EY4" t="n">
+        <v>7381</v>
+      </c>
+      <c r="EZ4" t="n">
+        <v>1698</v>
+      </c>
+      <c r="FA4" t="n">
+        <v>1548</v>
+      </c>
+      <c r="FB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="FC4" t="n">
+        <v>1095</v>
+      </c>
+      <c r="FD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE4" t="n">
+        <v>499</v>
+      </c>
+      <c r="FF4" t="n">
+        <v>-1737</v>
+      </c>
+      <c r="FG4" t="n">
         <v>3071</v>
       </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>13692</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
+      <c r="FH4" t="n">
+        <v>-300</v>
+      </c>
+      <c r="FI4" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ4" t="n">
+        <v>3507</v>
+      </c>
+      <c r="FK4" t="n">
+        <v>899</v>
+      </c>
+      <c r="FL4" t="n">
+        <v>1098</v>
+      </c>
+      <c r="FM4" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN4" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP4" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ4" t="n">
+        <v>1199</v>
+      </c>
+      <c r="FR4" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS4" t="n">
+        <v>2399</v>
+      </c>
+      <c r="FT4" t="n">
+        <v>1299</v>
+      </c>
+      <c r="FU4" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV4" t="n">
+        <v>2999</v>
+      </c>
+      <c r="FW4" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX4" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY4" t="n">
         <v>-2399</v>
       </c>
-      <c r="K4" t="n">
-        <v>7097</v>
-      </c>
-      <c r="L4" t="n">
-        <v>46286</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>62064</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R4" t="n">
-        <v>119449</v>
-      </c>
-      <c r="S4" t="n">
-        <v>17982</v>
-      </c>
-      <c r="T4" t="n">
-        <v>3604</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" t="n">
-        <v>5295</v>
-      </c>
-      <c r="W4" t="n">
-        <v>11298</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>449</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>10692</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>33785</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>24484</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>33115</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1711</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>3047</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>1299</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>30801</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>23863</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>-5698</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>4039</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>150290</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>9803</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>8616</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>260</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>8395</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>249</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>1548</v>
-      </c>
-      <c r="AT4" t="n">
+      <c r="FZ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="GA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC4" t="n">
+        <v>999</v>
+      </c>
+      <c r="GD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="GH4" t="n">
+        <v>1599</v>
+      </c>
+      <c r="GI4" t="n">
+        <v>0</v>
+      </c>
+      <c r="GJ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="GK4" t="n">
+        <v>0</v>
+      </c>
+      <c r="GL4" t="n">
         <v>1899</v>
       </c>
-      <c r="AU4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>1095</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>172659</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>16751</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>8445</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>60404</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>9447</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>1199</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>548</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>417767</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>117515</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>12173</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>84129</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>-867</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>839</v>
-      </c>
-      <c r="BO4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR4" t="n">
-        <v>1131</v>
-      </c>
-      <c r="BS4" t="n">
-        <v>2175291</v>
-      </c>
-      <c r="BT4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV4" t="n">
-        <v>45361</v>
-      </c>
-      <c r="BW4" t="n">
-        <v>609532</v>
-      </c>
-      <c r="BX4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY4" t="n">
-        <v>15894</v>
-      </c>
-      <c r="BZ4" t="n">
-        <v>7381</v>
-      </c>
-      <c r="CA4" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB4" t="n">
-        <v>8421</v>
-      </c>
-      <c r="CC4" t="n">
-        <v>2038</v>
-      </c>
-      <c r="CD4" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE4" t="n">
-        <v>16259</v>
-      </c>
-      <c r="CF4" t="n">
-        <v>-1437</v>
-      </c>
-      <c r="CG4" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH4" t="n">
-        <v>848</v>
-      </c>
-      <c r="CI4" t="n">
-        <v>25843</v>
-      </c>
-      <c r="CJ4" t="n">
-        <v>639</v>
-      </c>
-      <c r="CK4" t="n">
-        <v>6396</v>
-      </c>
-      <c r="CL4" t="n">
-        <v>26689</v>
-      </c>
-      <c r="CM4" t="n">
-        <v>2399</v>
-      </c>
-      <c r="CN4" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO4" t="n">
-        <v>279956</v>
-      </c>
-      <c r="CP4" t="n">
-        <v>19127</v>
-      </c>
-      <c r="CQ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="CR4" t="n">
-        <v>7403</v>
-      </c>
-      <c r="CS4" t="n">
-        <v>15111</v>
-      </c>
-      <c r="CT4" t="n">
-        <v>0</v>
-      </c>
-      <c r="CU4" t="n">
-        <v>1290</v>
-      </c>
-      <c r="CV4" t="n">
-        <v>1587</v>
-      </c>
-      <c r="CW4" t="n">
-        <v>0</v>
-      </c>
-      <c r="CX4" t="n">
-        <v>37151</v>
-      </c>
-      <c r="CY4" t="n">
-        <v>999</v>
-      </c>
-      <c r="CZ4" t="n">
-        <v>13391</v>
-      </c>
-      <c r="DA4" t="n">
-        <v>3071</v>
-      </c>
-      <c r="DB4" t="n">
-        <v>0</v>
-      </c>
-      <c r="DC4" t="n">
-        <v>13692</v>
-      </c>
-      <c r="DD4" t="n">
-        <v>0</v>
-      </c>
-      <c r="DE4" t="n">
-        <v>-2399</v>
-      </c>
-      <c r="DF4" t="n">
-        <v>7097</v>
-      </c>
-      <c r="DG4" t="n">
-        <v>55566</v>
-      </c>
-      <c r="DH4" t="n">
-        <v>0</v>
-      </c>
-      <c r="DI4" t="n">
-        <v>0</v>
-      </c>
-      <c r="DJ4" t="n">
-        <v>65383</v>
-      </c>
-      <c r="DK4" t="n">
-        <v>0</v>
-      </c>
-      <c r="DL4" t="n">
-        <v>0</v>
-      </c>
-      <c r="DM4" t="n">
-        <v>146118</v>
-      </c>
-      <c r="DN4" t="n">
-        <v>17982</v>
-      </c>
-      <c r="DO4" t="n">
-        <v>3484</v>
-      </c>
-      <c r="DP4" t="n">
-        <v>0</v>
-      </c>
-      <c r="DQ4" t="n">
-        <v>5295</v>
-      </c>
-      <c r="DR4" t="n">
-        <v>11298</v>
-      </c>
-      <c r="DS4" t="n">
-        <v>0</v>
-      </c>
-      <c r="DT4" t="n">
-        <v>899</v>
-      </c>
-      <c r="DU4" t="n">
-        <v>10692</v>
-      </c>
-      <c r="DV4" t="n">
-        <v>33785</v>
-      </c>
-      <c r="DW4" t="n">
-        <v>24484</v>
-      </c>
-      <c r="DX4" t="n">
-        <v>35865</v>
-      </c>
-      <c r="DY4" t="n">
-        <v>3507</v>
-      </c>
-      <c r="DZ4" t="n">
-        <v>3047</v>
-      </c>
-      <c r="EA4" t="n">
-        <v>1299</v>
-      </c>
-      <c r="EB4" t="n">
-        <v>0</v>
-      </c>
-      <c r="EC4" t="n">
-        <v>32640</v>
-      </c>
-      <c r="ED4" t="n">
-        <v>22783</v>
-      </c>
-      <c r="EE4" t="n">
-        <v>-5698</v>
-      </c>
-      <c r="EF4" t="n">
-        <v>4277</v>
-      </c>
-      <c r="EG4" t="n">
-        <v>0</v>
-      </c>
-      <c r="EH4" t="n">
-        <v>153305</v>
-      </c>
-      <c r="EI4" t="n">
-        <v>12593</v>
-      </c>
-      <c r="EJ4" t="n">
-        <v>10381</v>
-      </c>
-      <c r="EK4" t="n">
-        <v>-300</v>
-      </c>
-      <c r="EL4" t="n">
-        <v>8395</v>
-      </c>
-      <c r="EM4" t="n">
-        <v>499</v>
-      </c>
-      <c r="EN4" t="n">
-        <v>1548</v>
-      </c>
-      <c r="EO4" t="n">
-        <v>1899</v>
-      </c>
-      <c r="EP4" t="n">
-        <v>0</v>
-      </c>
-      <c r="EQ4" t="n">
-        <v>1095</v>
-      </c>
-      <c r="ER4" t="n">
-        <v>195921</v>
-      </c>
-      <c r="ES4" t="n">
-        <v>17101</v>
-      </c>
-      <c r="ET4" t="n">
-        <v>0</v>
-      </c>
-      <c r="EU4" t="n">
-        <v>13395</v>
-      </c>
-      <c r="EV4" t="n">
-        <v>59143</v>
-      </c>
-      <c r="EW4" t="n">
-        <v>10307</v>
-      </c>
-      <c r="EX4" t="n">
-        <v>0</v>
-      </c>
-      <c r="EY4" t="n">
-        <v>2999</v>
-      </c>
-      <c r="EZ4" t="n">
-        <v>1098</v>
-      </c>
-      <c r="FA4" t="n">
-        <v>0</v>
-      </c>
-      <c r="FB4" t="n">
-        <v>421334</v>
-      </c>
-      <c r="FC4" t="n">
-        <v>0</v>
-      </c>
-      <c r="FD4" t="n">
-        <v>0</v>
-      </c>
-      <c r="FE4" t="n">
-        <v>133734</v>
-      </c>
-      <c r="FF4" t="n">
-        <v>13493</v>
-      </c>
-      <c r="FG4" t="n">
-        <v>88729</v>
-      </c>
-      <c r="FH4" t="n">
-        <v>-1737</v>
-      </c>
-      <c r="FI4" t="n">
-        <v>1199</v>
-      </c>
-      <c r="FJ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="FK4" t="n">
-        <v>0</v>
-      </c>
-      <c r="FL4" t="n">
-        <v>0</v>
-      </c>
-      <c r="FM4" t="n">
-        <v>1416</v>
-      </c>
-      <c r="FN4" t="n">
-        <v>2377455</v>
-      </c>
-      <c r="FO4" t="n">
-        <v>0</v>
-      </c>
-      <c r="FP4" t="n">
-        <v>0</v>
-      </c>
-      <c r="FQ4" t="n">
-        <v>45361</v>
-      </c>
-      <c r="FR4" t="n">
-        <v>611692</v>
-      </c>
-      <c r="FS4" t="n">
-        <v>0</v>
-      </c>
-      <c r="FT4" t="n">
-        <v>15894</v>
-      </c>
-      <c r="FU4" t="n">
-        <v>7381</v>
-      </c>
-      <c r="FV4" t="n">
-        <v>0</v>
-      </c>
-      <c r="FW4" t="n">
-        <v>9081</v>
-      </c>
-      <c r="FX4" t="n">
-        <v>3398</v>
-      </c>
-      <c r="FY4" t="n">
-        <v>0</v>
-      </c>
-      <c r="FZ4" t="n">
-        <v>19367</v>
-      </c>
-      <c r="GA4" t="n">
-        <v>-4797</v>
-      </c>
-      <c r="GB4" t="n">
-        <v>0</v>
-      </c>
-      <c r="GC4" t="n">
-        <v>1698</v>
-      </c>
-      <c r="GD4" t="n">
-        <v>28642</v>
-      </c>
-      <c r="GE4" t="n">
-        <v>1599</v>
-      </c>
-      <c r="GF4" t="n">
-        <v>6396</v>
-      </c>
-      <c r="GG4" t="n">
-        <v>27767</v>
-      </c>
-      <c r="GH4" t="n">
-        <v>2399</v>
-      </c>
-      <c r="GI4" t="n">
-        <v>0</v>
-      </c>
-      <c r="GJ4" t="n">
-        <v>284221</v>
-      </c>
-      <c r="GK4" t="n">
-        <v>24187</v>
-      </c>
-      <c r="GL4" t="n">
-        <v>0</v>
-      </c>
       <c r="GM4" t="n">
-        <v>9043</v>
+        <v>0</v>
       </c>
       <c r="GN4" t="n">
-        <v>15111</v>
+        <v>0</v>
       </c>
       <c r="GO4" t="n">
         <v>0</v>
       </c>
       <c r="GP4" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="GQ4" t="n">
-        <v>1587</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -5785,598 +6117,598 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>1709006</v>
       </c>
       <c r="C5" t="n">
+        <v>305228</v>
+      </c>
+      <c r="D5" t="n">
+        <v>348130</v>
+      </c>
+      <c r="E5" t="n">
+        <v>140877</v>
+      </c>
+      <c r="F5" t="n">
+        <v>146834</v>
+      </c>
+      <c r="G5" t="n">
+        <v>218943</v>
+      </c>
+      <c r="H5" t="n">
+        <v>138406</v>
+      </c>
+      <c r="I5" t="n">
+        <v>68046</v>
+      </c>
+      <c r="J5" t="n">
+        <v>31478</v>
+      </c>
+      <c r="K5" t="n">
+        <v>64849</v>
+      </c>
+      <c r="L5" t="n">
+        <v>23849</v>
+      </c>
+      <c r="M5" t="n">
+        <v>71724</v>
+      </c>
+      <c r="N5" t="n">
+        <v>52813</v>
+      </c>
+      <c r="O5" t="n">
+        <v>39293</v>
+      </c>
+      <c r="P5" t="n">
+        <v>48574</v>
+      </c>
+      <c r="Q5" t="n">
         <v>20434</v>
       </c>
-      <c r="D5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" t="n">
+      <c r="R5" t="n">
+        <v>25688</v>
+      </c>
+      <c r="S5" t="n">
+        <v>35977</v>
+      </c>
+      <c r="T5" t="n">
+        <v>-619</v>
+      </c>
+      <c r="U5" t="n">
+        <v>22146</v>
+      </c>
+      <c r="V5" t="n">
+        <v>16536</v>
+      </c>
+      <c r="W5" t="n">
+        <v>29494</v>
+      </c>
+      <c r="X5" t="n">
+        <v>9597</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>28283</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>37875</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>14483</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>15135</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>8643</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>12628</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>16503</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>11802</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>2017</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>9986</v>
+      </c>
+      <c r="AI5" t="n">
         <v>6003</v>
       </c>
-      <c r="F5" t="n">
+      <c r="AJ5" t="n">
+        <v>6792</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>2118</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>5148</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>4906</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>11716</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>6377</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>13330</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>3595</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>2970</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>1499</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>6883</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>11839</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>2959</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>5199</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>-95</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>2961</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>5812</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>2265</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>2197</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>825</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>798</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL5" t="n">
         <v>1516</v>
       </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
+      <c r="BM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>-478</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>299</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY5" t="n">
+        <v>5596</v>
+      </c>
+      <c r="BZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK5" t="n">
+        <v>-1647</v>
+      </c>
+      <c r="CL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ5" t="n">
+        <v>2199</v>
+      </c>
+      <c r="CR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW5" t="n">
+        <v>2119620</v>
+      </c>
+      <c r="CX5" t="n">
+        <v>417778</v>
+      </c>
+      <c r="CY5" t="n">
+        <v>358578</v>
+      </c>
+      <c r="CZ5" t="n">
+        <v>178540</v>
+      </c>
+      <c r="DA5" t="n">
+        <v>174182</v>
+      </c>
+      <c r="DB5" t="n">
+        <v>239043</v>
+      </c>
+      <c r="DC5" t="n">
+        <v>147611</v>
+      </c>
+      <c r="DD5" t="n">
+        <v>83393</v>
+      </c>
+      <c r="DE5" t="n">
+        <v>48268</v>
+      </c>
+      <c r="DF5" t="n">
+        <v>79071</v>
+      </c>
+      <c r="DG5" t="n">
+        <v>27595</v>
+      </c>
+      <c r="DH5" t="n">
+        <v>101111</v>
+      </c>
+      <c r="DI5" t="n">
+        <v>70250</v>
+      </c>
+      <c r="DJ5" t="n">
+        <v>39293</v>
+      </c>
+      <c r="DK5" t="n">
+        <v>64527</v>
+      </c>
+      <c r="DL5" t="n">
+        <v>23414</v>
+      </c>
+      <c r="DM5" t="n">
+        <v>25688</v>
+      </c>
+      <c r="DN5" t="n">
+        <v>35977</v>
+      </c>
+      <c r="DO5" t="n">
+        <v>-6299</v>
+      </c>
+      <c r="DP5" t="n">
+        <v>28063</v>
+      </c>
+      <c r="DQ5" t="n">
+        <v>24768</v>
+      </c>
+      <c r="DR5" t="n">
+        <v>43554</v>
+      </c>
+      <c r="DS5" t="n">
         <v>9597</v>
       </c>
-      <c r="I5" t="n">
-        <v>798</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>6377</v>
-      </c>
-      <c r="L5" t="n">
-        <v>31478</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>52813</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>140877</v>
-      </c>
-      <c r="S5" t="n">
-        <v>9986</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2970</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" t="n">
-        <v>12628</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>11716</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>25688</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>35977</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>29494</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>-478</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>5812</v>
-      </c>
-      <c r="AF5" t="n">
+      <c r="DT5" t="n">
+        <v>28283</v>
+      </c>
+      <c r="DU5" t="n">
+        <v>55415</v>
+      </c>
+      <c r="DV5" t="n">
+        <v>14658</v>
+      </c>
+      <c r="DW5" t="n">
+        <v>20655</v>
+      </c>
+      <c r="DX5" t="n">
+        <v>11193</v>
+      </c>
+      <c r="DY5" t="n">
+        <v>16588</v>
+      </c>
+      <c r="DZ5" t="n">
+        <v>24721</v>
+      </c>
+      <c r="EA5" t="n">
+        <v>14092</v>
+      </c>
+      <c r="EB5" t="n">
+        <v>2417</v>
+      </c>
+      <c r="EC5" t="n">
+        <v>13986</v>
+      </c>
+      <c r="ED5" t="n">
+        <v>8193</v>
+      </c>
+      <c r="EE5" t="n">
+        <v>13592</v>
+      </c>
+      <c r="EF5" t="n">
+        <v>2798</v>
+      </c>
+      <c r="EG5" t="n">
+        <v>5798</v>
+      </c>
+      <c r="EH5" t="n">
+        <v>8248</v>
+      </c>
+      <c r="EI5" t="n">
+        <v>18286</v>
+      </c>
+      <c r="EJ5" t="n">
+        <v>9197</v>
+      </c>
+      <c r="EK5" t="n">
+        <v>23235</v>
+      </c>
+      <c r="EL5" t="n">
+        <v>5780</v>
+      </c>
+      <c r="EM5" t="n">
+        <v>3197</v>
+      </c>
+      <c r="EN5" t="n">
+        <v>1499</v>
+      </c>
+      <c r="EO5" t="n">
+        <v>9793</v>
+      </c>
+      <c r="EP5" t="n">
+        <v>13039</v>
+      </c>
+      <c r="EQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER5" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES5" t="n">
+        <v>5100</v>
+      </c>
+      <c r="ET5" t="n">
+        <v>5199</v>
+      </c>
+      <c r="EU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV5" t="n">
+        <v>-310</v>
+      </c>
+      <c r="EW5" t="n">
+        <v>4051</v>
+      </c>
+      <c r="EX5" t="n">
+        <v>8492</v>
+      </c>
+      <c r="EY5" t="n">
+        <v>2265</v>
+      </c>
+      <c r="EZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA5" t="n">
+        <v>2197</v>
+      </c>
+      <c r="FB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FC5" t="n">
+        <v>1065</v>
+      </c>
+      <c r="FD5" t="n">
+        <v>1600</v>
+      </c>
+      <c r="FE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG5" t="n">
+        <v>2212</v>
+      </c>
+      <c r="FH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ5" t="n">
+        <v>-1368</v>
+      </c>
+      <c r="FK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FL5" t="n">
+        <v>599</v>
+      </c>
+      <c r="FM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT5" t="n">
         <v>5596</v>
       </c>
-      <c r="AG5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>48574</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>37875</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>1499</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>3595</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>138406</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>8643</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>22146</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>6792</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>2197</v>
-      </c>
-      <c r="AT5" t="n">
+      <c r="FU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="GA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF5" t="n">
+        <v>-3297</v>
+      </c>
+      <c r="GG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="GH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="GI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="GJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="GK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="GL5" t="n">
         <v>2199</v>
       </c>
-      <c r="AU5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>825</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>146834</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>14483</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>-619</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>71724</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>2017</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>299</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>348130</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>68046</v>
-      </c>
-      <c r="BK5" t="n">
-        <v>11802</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>64849</v>
-      </c>
-      <c r="BM5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ5" t="n">
-        <v>-1647</v>
-      </c>
-      <c r="BR5" t="n">
-        <v>-95</v>
-      </c>
-      <c r="BS5" t="n">
-        <v>1709006</v>
-      </c>
-      <c r="BT5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU5" t="n">
-        <v>5199</v>
-      </c>
-      <c r="BV5" t="n">
-        <v>39293</v>
-      </c>
-      <c r="BW5" t="n">
-        <v>218943</v>
-      </c>
-      <c r="BX5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY5" t="n">
-        <v>28283</v>
-      </c>
-      <c r="BZ5" t="n">
-        <v>2265</v>
-      </c>
-      <c r="CA5" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB5" t="n">
-        <v>5148</v>
-      </c>
-      <c r="CC5" t="n">
-        <v>2118</v>
-      </c>
-      <c r="CD5" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE5" t="n">
-        <v>4906</v>
-      </c>
-      <c r="CF5" t="n">
-        <v>11839</v>
-      </c>
-      <c r="CG5" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH5" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI5" t="n">
-        <v>23849</v>
-      </c>
-      <c r="CJ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="CK5" t="n">
-        <v>6883</v>
-      </c>
-      <c r="CL5" t="n">
-        <v>16503</v>
-      </c>
-      <c r="CM5" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN5" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO5" t="n">
-        <v>305228</v>
-      </c>
-      <c r="CP5" t="n">
-        <v>16536</v>
-      </c>
-      <c r="CQ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="CR5" t="n">
-        <v>13330</v>
-      </c>
-      <c r="CS5" t="n">
-        <v>15135</v>
-      </c>
-      <c r="CT5" t="n">
-        <v>0</v>
-      </c>
-      <c r="CU5" t="n">
-        <v>2959</v>
-      </c>
-      <c r="CV5" t="n">
-        <v>2961</v>
-      </c>
-      <c r="CW5" t="n">
-        <v>0</v>
-      </c>
-      <c r="CX5" t="n">
-        <v>23414</v>
-      </c>
-      <c r="CY5" t="n">
-        <v>0</v>
-      </c>
-      <c r="CZ5" t="n">
-        <v>8193</v>
-      </c>
-      <c r="DA5" t="n">
-        <v>2212</v>
-      </c>
-      <c r="DB5" t="n">
-        <v>0</v>
-      </c>
-      <c r="DC5" t="n">
-        <v>9597</v>
-      </c>
-      <c r="DD5" t="n">
-        <v>1600</v>
-      </c>
-      <c r="DE5" t="n">
-        <v>0</v>
-      </c>
-      <c r="DF5" t="n">
-        <v>9197</v>
-      </c>
-      <c r="DG5" t="n">
-        <v>48268</v>
-      </c>
-      <c r="DH5" t="n">
-        <v>0</v>
-      </c>
-      <c r="DI5" t="n">
-        <v>0</v>
-      </c>
-      <c r="DJ5" t="n">
-        <v>70250</v>
-      </c>
-      <c r="DK5" t="n">
-        <v>0</v>
-      </c>
-      <c r="DL5" t="n">
-        <v>0</v>
-      </c>
-      <c r="DM5" t="n">
-        <v>178540</v>
-      </c>
-      <c r="DN5" t="n">
-        <v>13986</v>
-      </c>
-      <c r="DO5" t="n">
-        <v>3197</v>
-      </c>
-      <c r="DP5" t="n">
-        <v>0</v>
-      </c>
-      <c r="DQ5" t="n">
-        <v>16588</v>
-      </c>
-      <c r="DR5" t="n">
-        <v>0</v>
-      </c>
-      <c r="DS5" t="n">
-        <v>0</v>
-      </c>
-      <c r="DT5" t="n">
-        <v>0</v>
-      </c>
-      <c r="DU5" t="n">
-        <v>18286</v>
-      </c>
-      <c r="DV5" t="n">
-        <v>25688</v>
-      </c>
-      <c r="DW5" t="n">
-        <v>35977</v>
-      </c>
-      <c r="DX5" t="n">
-        <v>43554</v>
-      </c>
-      <c r="DY5" t="n">
-        <v>-1368</v>
-      </c>
-      <c r="DZ5" t="n">
-        <v>8492</v>
-      </c>
-      <c r="EA5" t="n">
-        <v>5596</v>
-      </c>
-      <c r="EB5" t="n">
-        <v>0</v>
-      </c>
-      <c r="EC5" t="n">
-        <v>64527</v>
-      </c>
-      <c r="ED5" t="n">
-        <v>55415</v>
-      </c>
-      <c r="EE5" t="n">
-        <v>1499</v>
-      </c>
-      <c r="EF5" t="n">
-        <v>5780</v>
-      </c>
-      <c r="EG5" t="n">
-        <v>0</v>
-      </c>
-      <c r="EH5" t="n">
-        <v>147611</v>
-      </c>
-      <c r="EI5" t="n">
-        <v>11193</v>
-      </c>
-      <c r="EJ5" t="n">
-        <v>28063</v>
-      </c>
-      <c r="EK5" t="n">
-        <v>0</v>
-      </c>
-      <c r="EL5" t="n">
-        <v>13592</v>
-      </c>
-      <c r="EM5" t="n">
-        <v>0</v>
-      </c>
-      <c r="EN5" t="n">
-        <v>2197</v>
-      </c>
-      <c r="EO5" t="n">
-        <v>2199</v>
-      </c>
-      <c r="EP5" t="n">
-        <v>0</v>
-      </c>
-      <c r="EQ5" t="n">
-        <v>1065</v>
-      </c>
-      <c r="ER5" t="n">
-        <v>174182</v>
-      </c>
-      <c r="ES5" t="n">
-        <v>14658</v>
-      </c>
-      <c r="ET5" t="n">
-        <v>0</v>
-      </c>
-      <c r="EU5" t="n">
-        <v>-6299</v>
-      </c>
-      <c r="EV5" t="n">
-        <v>101111</v>
-      </c>
-      <c r="EW5" t="n">
-        <v>2417</v>
-      </c>
-      <c r="EX5" t="n">
-        <v>0</v>
-      </c>
-      <c r="EY5" t="n">
-        <v>0</v>
-      </c>
-      <c r="EZ5" t="n">
-        <v>599</v>
-      </c>
-      <c r="FA5" t="n">
-        <v>0</v>
-      </c>
-      <c r="FB5" t="n">
-        <v>358578</v>
-      </c>
-      <c r="FC5" t="n">
-        <v>0</v>
-      </c>
-      <c r="FD5" t="n">
-        <v>0</v>
-      </c>
-      <c r="FE5" t="n">
-        <v>83393</v>
-      </c>
-      <c r="FF5" t="n">
-        <v>14092</v>
-      </c>
-      <c r="FG5" t="n">
-        <v>79071</v>
-      </c>
-      <c r="FH5" t="n">
-        <v>0</v>
-      </c>
-      <c r="FI5" t="n">
-        <v>0</v>
-      </c>
-      <c r="FJ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="FK5" t="n">
-        <v>0</v>
-      </c>
-      <c r="FL5" t="n">
-        <v>-3297</v>
-      </c>
-      <c r="FM5" t="n">
-        <v>-310</v>
-      </c>
-      <c r="FN5" t="n">
-        <v>2119620</v>
-      </c>
-      <c r="FO5" t="n">
-        <v>0</v>
-      </c>
-      <c r="FP5" t="n">
-        <v>5199</v>
-      </c>
-      <c r="FQ5" t="n">
-        <v>39293</v>
-      </c>
-      <c r="FR5" t="n">
-        <v>239043</v>
-      </c>
-      <c r="FS5" t="n">
-        <v>0</v>
-      </c>
-      <c r="FT5" t="n">
-        <v>28283</v>
-      </c>
-      <c r="FU5" t="n">
-        <v>2265</v>
-      </c>
-      <c r="FV5" t="n">
-        <v>0</v>
-      </c>
-      <c r="FW5" t="n">
-        <v>5798</v>
-      </c>
-      <c r="FX5" t="n">
-        <v>2798</v>
-      </c>
-      <c r="FY5" t="n">
-        <v>0</v>
-      </c>
-      <c r="FZ5" t="n">
-        <v>8248</v>
-      </c>
-      <c r="GA5" t="n">
-        <v>13039</v>
-      </c>
-      <c r="GB5" t="n">
-        <v>0</v>
-      </c>
-      <c r="GC5" t="n">
-        <v>0</v>
-      </c>
-      <c r="GD5" t="n">
-        <v>27595</v>
-      </c>
-      <c r="GE5" t="n">
-        <v>0</v>
-      </c>
-      <c r="GF5" t="n">
-        <v>9793</v>
-      </c>
-      <c r="GG5" t="n">
-        <v>24721</v>
-      </c>
-      <c r="GH5" t="n">
-        <v>0</v>
-      </c>
-      <c r="GI5" t="n">
-        <v>0</v>
-      </c>
-      <c r="GJ5" t="n">
-        <v>417778</v>
-      </c>
-      <c r="GK5" t="n">
-        <v>24768</v>
-      </c>
-      <c r="GL5" t="n">
-        <v>0</v>
-      </c>
       <c r="GM5" t="n">
-        <v>23235</v>
+        <v>0</v>
       </c>
       <c r="GN5" t="n">
-        <v>20655</v>
+        <v>0</v>
       </c>
       <c r="GO5" t="n">
         <v>0</v>
       </c>
       <c r="GP5" t="n">
-        <v>5100</v>
+        <v>0</v>
       </c>
       <c r="GQ5" t="n">
-        <v>4051</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -6977,6 +7309,607 @@
         <v>0</v>
       </c>
       <c r="GQ6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2545204</v>
+      </c>
+      <c r="C7" t="n">
+        <v>400117</v>
+      </c>
+      <c r="D7" t="n">
+        <v>232688</v>
+      </c>
+      <c r="E7" t="n">
+        <v>176948</v>
+      </c>
+      <c r="F7" t="n">
+        <v>163510</v>
+      </c>
+      <c r="G7" t="n">
+        <v>155807</v>
+      </c>
+      <c r="H7" t="n">
+        <v>128508</v>
+      </c>
+      <c r="I7" t="n">
+        <v>100681</v>
+      </c>
+      <c r="J7" t="n">
+        <v>100229</v>
+      </c>
+      <c r="K7" t="n">
+        <v>98192</v>
+      </c>
+      <c r="L7" t="n">
+        <v>69600</v>
+      </c>
+      <c r="M7" t="n">
+        <v>66595</v>
+      </c>
+      <c r="N7" t="n">
+        <v>54388</v>
+      </c>
+      <c r="O7" t="n">
+        <v>37393</v>
+      </c>
+      <c r="P7" t="n">
+        <v>36382</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>33273</v>
+      </c>
+      <c r="R7" t="n">
+        <v>32985</v>
+      </c>
+      <c r="S7" t="n">
+        <v>26885</v>
+      </c>
+      <c r="T7" t="n">
+        <v>26516</v>
+      </c>
+      <c r="U7" t="n">
+        <v>20968</v>
+      </c>
+      <c r="V7" t="n">
+        <v>20223</v>
+      </c>
+      <c r="W7" t="n">
+        <v>20072</v>
+      </c>
+      <c r="X7" t="n">
+        <v>18696</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>16192</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>15338</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>14273</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>13371</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>13171</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>11064</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>10865</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>9974</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>9851</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>9786</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>9442</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>7911</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>7693</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>6155</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>5546</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>5464</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>4998</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>4827</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>4793</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>4321</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>3798</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>2947</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>2777</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>2449</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>2399</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>2126</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>2030</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>2028</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>1989</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>1765</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>1691</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>1596</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>1556</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>1398</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>1258</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>1154</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>998</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>937</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>807</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>645</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>549</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>279</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>119</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW7" t="n">
+        <v>3134631</v>
+      </c>
+      <c r="CX7" t="n">
+        <v>580302</v>
+      </c>
+      <c r="CY7" t="n">
+        <v>277883</v>
+      </c>
+      <c r="CZ7" t="n">
+        <v>214151</v>
+      </c>
+      <c r="DA7" t="n">
+        <v>194614</v>
+      </c>
+      <c r="DB7" t="n">
+        <v>165047</v>
+      </c>
+      <c r="DC7" t="n">
+        <v>145423</v>
+      </c>
+      <c r="DD7" t="n">
+        <v>134473</v>
+      </c>
+      <c r="DE7" t="n">
+        <v>137365</v>
+      </c>
+      <c r="DF7" t="n">
+        <v>114412</v>
+      </c>
+      <c r="DG7" t="n">
+        <v>77171</v>
+      </c>
+      <c r="DH7" t="n">
+        <v>82332</v>
+      </c>
+      <c r="DI7" t="n">
+        <v>75466</v>
+      </c>
+      <c r="DJ7" t="n">
+        <v>37393</v>
+      </c>
+      <c r="DK7" t="n">
+        <v>44415</v>
+      </c>
+      <c r="DL7" t="n">
+        <v>42193</v>
+      </c>
+      <c r="DM7" t="n">
+        <v>32985</v>
+      </c>
+      <c r="DN7" t="n">
+        <v>26885</v>
+      </c>
+      <c r="DO7" t="n">
+        <v>41586</v>
+      </c>
+      <c r="DP7" t="n">
+        <v>23058</v>
+      </c>
+      <c r="DQ7" t="n">
+        <v>29183</v>
+      </c>
+      <c r="DR7" t="n">
+        <v>27272</v>
+      </c>
+      <c r="DS7" t="n">
+        <v>18696</v>
+      </c>
+      <c r="DT7" t="n">
+        <v>16192</v>
+      </c>
+      <c r="DU7" t="n">
+        <v>21938</v>
+      </c>
+      <c r="DV7" t="n">
+        <v>14658</v>
+      </c>
+      <c r="DW7" t="n">
+        <v>16711</v>
+      </c>
+      <c r="DX7" t="n">
+        <v>16491</v>
+      </c>
+      <c r="DY7" t="n">
+        <v>12384</v>
+      </c>
+      <c r="DZ7" t="n">
+        <v>17585</v>
+      </c>
+      <c r="EA7" t="n">
+        <v>10394</v>
+      </c>
+      <c r="EB7" t="n">
+        <v>10607</v>
+      </c>
+      <c r="EC7" t="n">
+        <v>13986</v>
+      </c>
+      <c r="ED7" t="n">
+        <v>13142</v>
+      </c>
+      <c r="EE7" t="n">
+        <v>15191</v>
+      </c>
+      <c r="EF7" t="n">
+        <v>7693</v>
+      </c>
+      <c r="EG7" t="n">
+        <v>6795</v>
+      </c>
+      <c r="EH7" t="n">
+        <v>8694</v>
+      </c>
+      <c r="EI7" t="n">
+        <v>7494</v>
+      </c>
+      <c r="EJ7" t="n">
+        <v>4998</v>
+      </c>
+      <c r="EK7" t="n">
+        <v>9642</v>
+      </c>
+      <c r="EL7" t="n">
+        <v>4793</v>
+      </c>
+      <c r="EM7" t="n">
+        <v>4501</v>
+      </c>
+      <c r="EN7" t="n">
+        <v>3798</v>
+      </c>
+      <c r="EO7" t="n">
+        <v>5297</v>
+      </c>
+      <c r="EP7" t="n">
+        <v>3897</v>
+      </c>
+      <c r="EQ7" t="n">
+        <v>3499</v>
+      </c>
+      <c r="ER7" t="n">
+        <v>4799</v>
+      </c>
+      <c r="ES7" t="n">
+        <v>3198</v>
+      </c>
+      <c r="ET7" t="n">
+        <v>2900</v>
+      </c>
+      <c r="EU7" t="n">
+        <v>2298</v>
+      </c>
+      <c r="EV7" t="n">
+        <v>2204</v>
+      </c>
+      <c r="EW7" t="n">
+        <v>2325</v>
+      </c>
+      <c r="EX7" t="n">
+        <v>3146</v>
+      </c>
+      <c r="EY7" t="n">
+        <v>1596</v>
+      </c>
+      <c r="EZ7" t="n">
+        <v>3296</v>
+      </c>
+      <c r="FA7" t="n">
+        <v>1398</v>
+      </c>
+      <c r="FB7" t="n">
+        <v>1798</v>
+      </c>
+      <c r="FC7" t="n">
+        <v>1414</v>
+      </c>
+      <c r="FD7" t="n">
+        <v>2000</v>
+      </c>
+      <c r="FE7" t="n">
+        <v>2198</v>
+      </c>
+      <c r="FF7" t="n">
+        <v>1617</v>
+      </c>
+      <c r="FG7" t="n">
+        <v>645</v>
+      </c>
+      <c r="FH7" t="n">
+        <v>1099</v>
+      </c>
+      <c r="FI7" t="n">
+        <v>399</v>
+      </c>
+      <c r="FJ7" t="n">
+        <v>300</v>
+      </c>
+      <c r="FK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="GA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="GH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="GI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="GJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="GK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="GL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="GM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="GN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="GO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="GP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="GQ7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6991,7 +7924,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -7163,6 +8096,31 @@
       </c>
       <c r="G6" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>4293954</v>
+      </c>
+      <c r="C7" t="n">
+        <v>494236</v>
+      </c>
+      <c r="D7" t="n">
+        <v>5337506</v>
+      </c>
+      <c r="E7" t="n">
+        <v>608441</v>
+      </c>
+      <c r="F7" t="n">
+        <v>10681</v>
+      </c>
+      <c r="G7" t="n">
+        <v>775</v>
       </c>
     </row>
   </sheetData>

--- a/data/nelly_inventory.xlsx
+++ b/data/nelly_inventory.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -581,6 +581,25 @@
         <v>0</v>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>6909281</v>
+      </c>
+      <c r="C8" t="n">
+        <v>8634461</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -592,111 +611,111 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CY7"/>
+  <dimension ref="A1:CY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
     <col width="23" customWidth="1" min="5" max="5"/>
-    <col width="28" customWidth="1" min="6" max="6"/>
-    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="7" max="7"/>
     <col width="33" customWidth="1" min="8" max="8"/>
     <col width="28" customWidth="1" min="9" max="9"/>
     <col width="35" customWidth="1" min="10" max="10"/>
     <col width="28" customWidth="1" min="11" max="11"/>
     <col width="24" customWidth="1" min="12" max="12"/>
     <col width="24" customWidth="1" min="13" max="13"/>
-    <col width="24" customWidth="1" min="14" max="14"/>
-    <col width="29" customWidth="1" min="15" max="15"/>
-    <col width="29" customWidth="1" min="16" max="16"/>
+    <col width="29" customWidth="1" min="14" max="14"/>
+    <col width="26" customWidth="1" min="15" max="15"/>
+    <col width="24" customWidth="1" min="16" max="16"/>
     <col width="35" customWidth="1" min="17" max="17"/>
-    <col width="31" customWidth="1" min="18" max="18"/>
-    <col width="26" customWidth="1" min="19" max="19"/>
+    <col width="29" customWidth="1" min="18" max="18"/>
+    <col width="35" customWidth="1" min="19" max="19"/>
     <col width="30" customWidth="1" min="20" max="20"/>
-    <col width="35" customWidth="1" min="21" max="21"/>
-    <col width="24" customWidth="1" min="22" max="22"/>
-    <col width="25" customWidth="1" min="23" max="23"/>
+    <col width="31" customWidth="1" min="21" max="21"/>
+    <col width="34" customWidth="1" min="22" max="22"/>
+    <col width="24" customWidth="1" min="23" max="23"/>
     <col width="25" customWidth="1" min="24" max="24"/>
-    <col width="34" customWidth="1" min="25" max="25"/>
-    <col width="36" customWidth="1" min="26" max="26"/>
+    <col width="25" customWidth="1" min="25" max="25"/>
+    <col width="31" customWidth="1" min="26" max="26"/>
     <col width="30" customWidth="1" min="27" max="27"/>
-    <col width="31" customWidth="1" min="28" max="28"/>
+    <col width="22" customWidth="1" min="28" max="28"/>
     <col width="33" customWidth="1" min="29" max="29"/>
     <col width="28" customWidth="1" min="30" max="30"/>
-    <col width="25" customWidth="1" min="31" max="31"/>
-    <col width="22" customWidth="1" min="32" max="32"/>
-    <col width="37" customWidth="1" min="33" max="33"/>
-    <col width="40" customWidth="1" min="34" max="34"/>
+    <col width="37" customWidth="1" min="31" max="31"/>
+    <col width="25" customWidth="1" min="32" max="32"/>
+    <col width="40" customWidth="1" min="33" max="33"/>
+    <col width="27" customWidth="1" min="34" max="34"/>
     <col width="42" customWidth="1" min="35" max="35"/>
     <col width="31" customWidth="1" min="36" max="36"/>
-    <col width="37" customWidth="1" min="37" max="37"/>
+    <col width="36" customWidth="1" min="37" max="37"/>
     <col width="29" customWidth="1" min="38" max="38"/>
-    <col width="33" customWidth="1" min="39" max="39"/>
-    <col width="40" customWidth="1" min="40" max="40"/>
-    <col width="34" customWidth="1" min="41" max="41"/>
-    <col width="38" customWidth="1" min="42" max="42"/>
-    <col width="39" customWidth="1" min="43" max="43"/>
-    <col width="23" customWidth="1" min="44" max="44"/>
-    <col width="27" customWidth="1" min="45" max="45"/>
-    <col width="16" customWidth="1" min="46" max="46"/>
-    <col width="29" customWidth="1" min="47" max="47"/>
-    <col width="40" customWidth="1" min="48" max="48"/>
-    <col width="16" customWidth="1" min="49" max="49"/>
-    <col width="23" customWidth="1" min="50" max="50"/>
-    <col width="34" customWidth="1" min="51" max="51"/>
+    <col width="16" customWidth="1" min="39" max="39"/>
+    <col width="37" customWidth="1" min="40" max="40"/>
+    <col width="23" customWidth="1" min="41" max="41"/>
+    <col width="40" customWidth="1" min="42" max="42"/>
+    <col width="33" customWidth="1" min="43" max="43"/>
+    <col width="29" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="45" max="45"/>
+    <col width="38" customWidth="1" min="46" max="46"/>
+    <col width="34" customWidth="1" min="47" max="47"/>
+    <col width="39" customWidth="1" min="48" max="48"/>
+    <col width="40" customWidth="1" min="49" max="49"/>
+    <col width="16" customWidth="1" min="50" max="50"/>
+    <col width="23" customWidth="1" min="51" max="51"/>
     <col width="26" customWidth="1" min="52" max="52"/>
     <col width="23" customWidth="1" min="53" max="53"/>
-    <col width="24" customWidth="1" min="54" max="54"/>
-    <col width="35" customWidth="1" min="55" max="55"/>
+    <col width="35" customWidth="1" min="54" max="54"/>
+    <col width="24" customWidth="1" min="55" max="55"/>
     <col width="23" customWidth="1" min="56" max="56"/>
-    <col width="28" customWidth="1" min="57" max="57"/>
-    <col width="24" customWidth="1" min="58" max="58"/>
+    <col width="24" customWidth="1" min="57" max="57"/>
+    <col width="28" customWidth="1" min="58" max="58"/>
     <col width="33" customWidth="1" min="59" max="59"/>
     <col width="28" customWidth="1" min="60" max="60"/>
     <col width="35" customWidth="1" min="61" max="61"/>
     <col width="28" customWidth="1" min="62" max="62"/>
     <col width="24" customWidth="1" min="63" max="63"/>
     <col width="24" customWidth="1" min="64" max="64"/>
-    <col width="24" customWidth="1" min="65" max="65"/>
-    <col width="29" customWidth="1" min="66" max="66"/>
-    <col width="29" customWidth="1" min="67" max="67"/>
+    <col width="29" customWidth="1" min="65" max="65"/>
+    <col width="26" customWidth="1" min="66" max="66"/>
+    <col width="24" customWidth="1" min="67" max="67"/>
     <col width="35" customWidth="1" min="68" max="68"/>
-    <col width="31" customWidth="1" min="69" max="69"/>
-    <col width="26" customWidth="1" min="70" max="70"/>
+    <col width="29" customWidth="1" min="69" max="69"/>
+    <col width="35" customWidth="1" min="70" max="70"/>
     <col width="30" customWidth="1" min="71" max="71"/>
-    <col width="35" customWidth="1" min="72" max="72"/>
-    <col width="24" customWidth="1" min="73" max="73"/>
-    <col width="25" customWidth="1" min="74" max="74"/>
+    <col width="31" customWidth="1" min="72" max="72"/>
+    <col width="34" customWidth="1" min="73" max="73"/>
+    <col width="24" customWidth="1" min="74" max="74"/>
     <col width="25" customWidth="1" min="75" max="75"/>
-    <col width="34" customWidth="1" min="76" max="76"/>
-    <col width="36" customWidth="1" min="77" max="77"/>
+    <col width="25" customWidth="1" min="76" max="76"/>
+    <col width="31" customWidth="1" min="77" max="77"/>
     <col width="30" customWidth="1" min="78" max="78"/>
-    <col width="31" customWidth="1" min="79" max="79"/>
+    <col width="22" customWidth="1" min="79" max="79"/>
     <col width="33" customWidth="1" min="80" max="80"/>
     <col width="28" customWidth="1" min="81" max="81"/>
-    <col width="25" customWidth="1" min="82" max="82"/>
-    <col width="22" customWidth="1" min="83" max="83"/>
-    <col width="37" customWidth="1" min="84" max="84"/>
-    <col width="40" customWidth="1" min="85" max="85"/>
+    <col width="37" customWidth="1" min="82" max="82"/>
+    <col width="25" customWidth="1" min="83" max="83"/>
+    <col width="40" customWidth="1" min="84" max="84"/>
+    <col width="27" customWidth="1" min="85" max="85"/>
     <col width="42" customWidth="1" min="86" max="86"/>
     <col width="31" customWidth="1" min="87" max="87"/>
-    <col width="37" customWidth="1" min="88" max="88"/>
+    <col width="36" customWidth="1" min="88" max="88"/>
     <col width="29" customWidth="1" min="89" max="89"/>
-    <col width="33" customWidth="1" min="90" max="90"/>
-    <col width="40" customWidth="1" min="91" max="91"/>
-    <col width="34" customWidth="1" min="92" max="92"/>
-    <col width="38" customWidth="1" min="93" max="93"/>
-    <col width="39" customWidth="1" min="94" max="94"/>
-    <col width="23" customWidth="1" min="95" max="95"/>
-    <col width="27" customWidth="1" min="96" max="96"/>
-    <col width="16" customWidth="1" min="97" max="97"/>
-    <col width="29" customWidth="1" min="98" max="98"/>
-    <col width="40" customWidth="1" min="99" max="99"/>
-    <col width="16" customWidth="1" min="100" max="100"/>
-    <col width="23" customWidth="1" min="101" max="101"/>
-    <col width="34" customWidth="1" min="102" max="102"/>
+    <col width="16" customWidth="1" min="90" max="90"/>
+    <col width="37" customWidth="1" min="91" max="91"/>
+    <col width="23" customWidth="1" min="92" max="92"/>
+    <col width="40" customWidth="1" min="93" max="93"/>
+    <col width="33" customWidth="1" min="94" max="94"/>
+    <col width="29" customWidth="1" min="95" max="95"/>
+    <col width="34" customWidth="1" min="96" max="96"/>
+    <col width="38" customWidth="1" min="97" max="97"/>
+    <col width="34" customWidth="1" min="98" max="98"/>
+    <col width="39" customWidth="1" min="99" max="99"/>
+    <col width="40" customWidth="1" min="100" max="100"/>
+    <col width="16" customWidth="1" min="101" max="101"/>
+    <col width="23" customWidth="1" min="102" max="102"/>
     <col width="26" customWidth="1" min="103" max="103"/>
   </cols>
   <sheetData>
@@ -713,14 +732,14 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Kläder&gt;Toppar &amp; T-shirts (Sell)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Skor&gt;Sneakers (Sell)</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Kläder&gt;Toppar &amp; T-shirts (Sell)</t>
-        </is>
-      </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Kläder&gt;Byxor (Sell)</t>
@@ -728,14 +747,14 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>Kläder&gt;Tröjor (Sell)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>Kläder&gt;Klänningar (Sell)</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Kläder&gt;Tröjor (Sell)</t>
-        </is>
-      </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Kläder&gt;Jackor &amp; Kappor (Sell)</t>
@@ -758,204 +777,204 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>Kläder&gt;Shorts (Sell)</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>Kläder&gt;Kjolar (Sell)</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Kläder&gt;Shorts (Sell)</t>
-        </is>
-      </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
+          <t>Kläder&gt;Underkläder (Sell)</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Kläder&gt;Skjortor (Sell)</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
           <t>Kläder&gt;Jackor (Sell)</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Kläder&gt;T-Shirts &amp; Linnen (Sell)</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Accessoarer&gt;Väskor (Sell)</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>Kläder&gt;Underkläder (Sell)</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Kläder&gt;Kavajer &amp; Blazers (Sell)</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Skor&gt;Boots &amp; Kängor (Sell)</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Skor&gt;Flats &amp; Lågskor (Sell)</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>Kläder&gt;Skjortor (Sell)</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>Skor&gt;Boots &amp; Kängor (Sell)</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>Kläder&gt;T-Shirts &amp; Linnen (Sell)</t>
-        </is>
-      </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
+          <t>Accessoarer&gt;Solglasögon (Sell)</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
           <t>Skor&gt;Sandaler (Sell)</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Skor&gt;Klackskor (Sell)</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Kläder&gt;Stickat (Sell)</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>Skor&gt;Klackskor (Sell)</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>Accessoarer&gt;Solglasögon (Sell)</t>
-        </is>
-      </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
+          <t>Sport&gt;Träningskläder (Sell)</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>Accessoarer&gt;Smycken (Sell)</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>Kläder&gt;Piké (Sell)</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>Badkläder&gt;Strandkläder (Sell)</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>Kläder&gt;Nattkläder (Sell)</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>Accessoarer&gt;Bälten &amp; Skärp (Sell)</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>Skor&gt;Platåskor (Sell)</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>Kläder&gt;Strumpor &amp; Strumpbyxor (Sell)</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>Kläder&gt;Badkläder (Sell)</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>Accessoarer&gt;Halsdukar &amp; Scarves (Sell)</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>Badkläder&gt;Baddräkter (Sell)</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
           <t>Kläder&gt;Kavajer &amp; Kostymer (Sell)</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>Accessoarer&gt;Smycken (Sell)</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>Sport&gt;Träningskläder (Sell)</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>Badkläder&gt;Strandkläder (Sell)</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>Kläder&gt;Nattkläder (Sell)</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>Skor&gt;Platåskor (Sell)</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>Kläder&gt;Piké (Sell)</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>Accessoarer&gt;Bälten &amp; Skärp (Sell)</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>Kläder&gt;Strumpor &amp; Strumpbyxor (Sell)</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>Accessoarer&gt;Halsdukar &amp; Scarves (Sell)</t>
-        </is>
-      </c>
-      <c r="AJ1" s="1" t="inlineStr">
-        <is>
-          <t>Badkläder&gt;Baddräkter (Sell)</t>
-        </is>
-      </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>Accessoarer&gt;Kepsar (Sell)</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>Sport (Sell)</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>Accessoarer&gt;Håraccessoarer (Sell)</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
-        <is>
-          <t>Accessoarer&gt;Kepsar (Sell)</t>
-        </is>
-      </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>Skor&gt;Finskor (Sell)</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>Kläder&gt;Sovkläder &amp; Loungewear (Sell)</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>Accessoarer&gt;Bag Charms (Sell)</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>Accessoarer&gt;Mössor (Sell)</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>Kläder&gt;Jumpsuits &amp; Sets (Sell)</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>Accessoarer&gt;Mössor &amp; Kepsar (Sell)</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>Accessoarer&gt;Herrsmycken (Sell)</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>Accessoarer&gt;Tech accessoarer (Sell)</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>Accessoarer&gt;Handskar &amp; Vantar (Sell)</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>Accessoarer&gt;Herrsmycken (Sell)</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>Accessoarer&gt;Mössor &amp; Kepsar (Sell)</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>Accessoarer&gt;Tech accessoarer (Sell)</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>Skor&gt;Finskor (Sell)</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>Kläder&gt;Badkläder (Sell)</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>Sport (Sell)</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>Accessoarer&gt;Mössor (Sell)</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>Kläder&gt;Sovkläder &amp; Loungewear (Sell)</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>Other (Sell)</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>Skor&gt;Tofflor (Sell)</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>Kläder&gt;Jumpsuits &amp; Sets (Sell)</t>
-        </is>
-      </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>Skor&gt;Flip-Flops (Sell)</t>
@@ -968,14 +987,14 @@
       </c>
       <c r="BB1" s="1" t="inlineStr">
         <is>
+          <t>Kläder&gt;Toppar &amp; T-shirts (List)</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
           <t>Skor&gt;Sneakers (List)</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>Kläder&gt;Toppar &amp; T-shirts (List)</t>
-        </is>
-      </c>
       <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>Kläder&gt;Byxor (List)</t>
@@ -983,14 +1002,14 @@
       </c>
       <c r="BE1" s="1" t="inlineStr">
         <is>
+          <t>Kläder&gt;Tröjor (List)</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
           <t>Kläder&gt;Klänningar (List)</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
-        <is>
-          <t>Kläder&gt;Tröjor (List)</t>
-        </is>
-      </c>
       <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>Kläder&gt;Jackor &amp; Kappor (List)</t>
@@ -1013,202 +1032,202 @@
       </c>
       <c r="BK1" s="1" t="inlineStr">
         <is>
+          <t>Kläder&gt;Shorts (List)</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
           <t>Kläder&gt;Kjolar (List)</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
-        <is>
-          <t>Kläder&gt;Shorts (List)</t>
-        </is>
-      </c>
       <c r="BM1" s="1" t="inlineStr">
         <is>
+          <t>Kläder&gt;Underkläder (List)</t>
+        </is>
+      </c>
+      <c r="BN1" s="1" t="inlineStr">
+        <is>
+          <t>Kläder&gt;Skjortor (List)</t>
+        </is>
+      </c>
+      <c r="BO1" s="1" t="inlineStr">
+        <is>
           <t>Kläder&gt;Jackor (List)</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
+        <is>
+          <t>Kläder&gt;T-Shirts &amp; Linnen (List)</t>
+        </is>
+      </c>
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>Accessoarer&gt;Väskor (List)</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
-        <is>
-          <t>Kläder&gt;Underkläder (List)</t>
-        </is>
-      </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>Kläder&gt;Kavajer &amp; Blazers (List)</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
+        <is>
+          <t>Skor&gt;Boots &amp; Kängor (List)</t>
+        </is>
+      </c>
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>Skor&gt;Flats &amp; Lågskor (List)</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
-        <is>
-          <t>Kläder&gt;Skjortor (List)</t>
-        </is>
-      </c>
-      <c r="BS1" s="1" t="inlineStr">
-        <is>
-          <t>Skor&gt;Boots &amp; Kängor (List)</t>
-        </is>
-      </c>
-      <c r="BT1" s="1" t="inlineStr">
-        <is>
-          <t>Kläder&gt;T-Shirts &amp; Linnen (List)</t>
-        </is>
-      </c>
       <c r="BU1" s="1" t="inlineStr">
         <is>
+          <t>Accessoarer&gt;Solglasögon (List)</t>
+        </is>
+      </c>
+      <c r="BV1" s="1" t="inlineStr">
+        <is>
           <t>Skor&gt;Sandaler (List)</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="BW1" s="1" t="inlineStr">
+        <is>
+          <t>Skor&gt;Klackskor (List)</t>
+        </is>
+      </c>
+      <c r="BX1" s="1" t="inlineStr">
         <is>
           <t>Kläder&gt;Stickat (List)</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
-        <is>
-          <t>Skor&gt;Klackskor (List)</t>
-        </is>
-      </c>
-      <c r="BX1" s="1" t="inlineStr">
-        <is>
-          <t>Accessoarer&gt;Solglasögon (List)</t>
-        </is>
-      </c>
       <c r="BY1" s="1" t="inlineStr">
         <is>
+          <t>Sport&gt;Träningskläder (List)</t>
+        </is>
+      </c>
+      <c r="BZ1" s="1" t="inlineStr">
+        <is>
+          <t>Accessoarer&gt;Smycken (List)</t>
+        </is>
+      </c>
+      <c r="CA1" s="1" t="inlineStr">
+        <is>
+          <t>Kläder&gt;Piké (List)</t>
+        </is>
+      </c>
+      <c r="CB1" s="1" t="inlineStr">
+        <is>
+          <t>Badkläder&gt;Strandkläder (List)</t>
+        </is>
+      </c>
+      <c r="CC1" s="1" t="inlineStr">
+        <is>
+          <t>Kläder&gt;Nattkläder (List)</t>
+        </is>
+      </c>
+      <c r="CD1" s="1" t="inlineStr">
+        <is>
+          <t>Accessoarer&gt;Bälten &amp; Skärp (List)</t>
+        </is>
+      </c>
+      <c r="CE1" s="1" t="inlineStr">
+        <is>
+          <t>Skor&gt;Platåskor (List)</t>
+        </is>
+      </c>
+      <c r="CF1" s="1" t="inlineStr">
+        <is>
+          <t>Kläder&gt;Strumpor &amp; Strumpbyxor (List)</t>
+        </is>
+      </c>
+      <c r="CG1" s="1" t="inlineStr">
+        <is>
+          <t>Kläder&gt;Badkläder (List)</t>
+        </is>
+      </c>
+      <c r="CH1" s="1" t="inlineStr">
+        <is>
+          <t>Accessoarer&gt;Halsdukar &amp; Scarves (List)</t>
+        </is>
+      </c>
+      <c r="CI1" s="1" t="inlineStr">
+        <is>
+          <t>Badkläder&gt;Baddräkter (List)</t>
+        </is>
+      </c>
+      <c r="CJ1" s="1" t="inlineStr">
+        <is>
           <t>Kläder&gt;Kavajer &amp; Kostymer (List)</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
-        <is>
-          <t>Accessoarer&gt;Smycken (List)</t>
-        </is>
-      </c>
-      <c r="CA1" s="1" t="inlineStr">
-        <is>
-          <t>Sport&gt;Träningskläder (List)</t>
-        </is>
-      </c>
-      <c r="CB1" s="1" t="inlineStr">
-        <is>
-          <t>Badkläder&gt;Strandkläder (List)</t>
-        </is>
-      </c>
-      <c r="CC1" s="1" t="inlineStr">
-        <is>
-          <t>Kläder&gt;Nattkläder (List)</t>
-        </is>
-      </c>
-      <c r="CD1" s="1" t="inlineStr">
-        <is>
-          <t>Skor&gt;Platåskor (List)</t>
-        </is>
-      </c>
-      <c r="CE1" s="1" t="inlineStr">
-        <is>
-          <t>Kläder&gt;Piké (List)</t>
-        </is>
-      </c>
-      <c r="CF1" s="1" t="inlineStr">
-        <is>
-          <t>Accessoarer&gt;Bälten &amp; Skärp (List)</t>
-        </is>
-      </c>
-      <c r="CG1" s="1" t="inlineStr">
-        <is>
-          <t>Kläder&gt;Strumpor &amp; Strumpbyxor (List)</t>
-        </is>
-      </c>
-      <c r="CH1" s="1" t="inlineStr">
-        <is>
-          <t>Accessoarer&gt;Halsdukar &amp; Scarves (List)</t>
-        </is>
-      </c>
-      <c r="CI1" s="1" t="inlineStr">
-        <is>
-          <t>Badkläder&gt;Baddräkter (List)</t>
-        </is>
-      </c>
-      <c r="CJ1" s="1" t="inlineStr">
+      <c r="CK1" s="1" t="inlineStr">
+        <is>
+          <t>Accessoarer&gt;Kepsar (List)</t>
+        </is>
+      </c>
+      <c r="CL1" s="1" t="inlineStr">
+        <is>
+          <t>Sport (List)</t>
+        </is>
+      </c>
+      <c r="CM1" s="1" t="inlineStr">
         <is>
           <t>Accessoarer&gt;Håraccessoarer (List)</t>
         </is>
       </c>
-      <c r="CK1" s="1" t="inlineStr">
-        <is>
-          <t>Accessoarer&gt;Kepsar (List)</t>
-        </is>
-      </c>
-      <c r="CL1" s="1" t="inlineStr">
+      <c r="CN1" s="1" t="inlineStr">
+        <is>
+          <t>Skor&gt;Finskor (List)</t>
+        </is>
+      </c>
+      <c r="CO1" s="1" t="inlineStr">
+        <is>
+          <t>Kläder&gt;Sovkläder &amp; Loungewear (List)</t>
+        </is>
+      </c>
+      <c r="CP1" s="1" t="inlineStr">
         <is>
           <t>Accessoarer&gt;Bag Charms (List)</t>
         </is>
       </c>
-      <c r="CM1" s="1" t="inlineStr">
+      <c r="CQ1" s="1" t="inlineStr">
+        <is>
+          <t>Accessoarer&gt;Mössor (List)</t>
+        </is>
+      </c>
+      <c r="CR1" s="1" t="inlineStr">
+        <is>
+          <t>Kläder&gt;Jumpsuits &amp; Sets (List)</t>
+        </is>
+      </c>
+      <c r="CS1" s="1" t="inlineStr">
+        <is>
+          <t>Accessoarer&gt;Mössor &amp; Kepsar (List)</t>
+        </is>
+      </c>
+      <c r="CT1" s="1" t="inlineStr">
+        <is>
+          <t>Accessoarer&gt;Herrsmycken (List)</t>
+        </is>
+      </c>
+      <c r="CU1" s="1" t="inlineStr">
+        <is>
+          <t>Accessoarer&gt;Tech accessoarer (List)</t>
+        </is>
+      </c>
+      <c r="CV1" s="1" t="inlineStr">
         <is>
           <t>Accessoarer&gt;Handskar &amp; Vantar (List)</t>
         </is>
       </c>
-      <c r="CN1" s="1" t="inlineStr">
-        <is>
-          <t>Accessoarer&gt;Herrsmycken (List)</t>
-        </is>
-      </c>
-      <c r="CO1" s="1" t="inlineStr">
-        <is>
-          <t>Accessoarer&gt;Mössor &amp; Kepsar (List)</t>
-        </is>
-      </c>
-      <c r="CP1" s="1" t="inlineStr">
-        <is>
-          <t>Accessoarer&gt;Tech accessoarer (List)</t>
-        </is>
-      </c>
-      <c r="CQ1" s="1" t="inlineStr">
-        <is>
-          <t>Skor&gt;Finskor (List)</t>
-        </is>
-      </c>
-      <c r="CR1" s="1" t="inlineStr">
-        <is>
-          <t>Kläder&gt;Badkläder (List)</t>
-        </is>
-      </c>
-      <c r="CS1" s="1" t="inlineStr">
-        <is>
-          <t>Sport (List)</t>
-        </is>
-      </c>
-      <c r="CT1" s="1" t="inlineStr">
-        <is>
-          <t>Accessoarer&gt;Mössor (List)</t>
-        </is>
-      </c>
-      <c r="CU1" s="1" t="inlineStr">
-        <is>
-          <t>Kläder&gt;Sovkläder &amp; Loungewear (List)</t>
-        </is>
-      </c>
-      <c r="CV1" s="1" t="inlineStr">
+      <c r="CW1" s="1" t="inlineStr">
         <is>
           <t>Other (List)</t>
         </is>
       </c>
-      <c r="CW1" s="1" t="inlineStr">
+      <c r="CX1" s="1" t="inlineStr">
         <is>
           <t>Skor&gt;Tofflor (List)</t>
-        </is>
-      </c>
-      <c r="CX1" s="1" t="inlineStr">
-        <is>
-          <t>Kläder&gt;Jumpsuits &amp; Sets (List)</t>
         </is>
       </c>
       <c r="CY1" s="1" t="inlineStr">
@@ -1540,19 +1559,19 @@
         <v>898883</v>
       </c>
       <c r="C3" t="n">
+        <v>329934</v>
+      </c>
+      <c r="D3" t="n">
         <v>587055</v>
-      </c>
-      <c r="D3" t="n">
-        <v>329934</v>
       </c>
       <c r="E3" t="n">
         <v>396112</v>
       </c>
       <c r="F3" t="n">
+        <v>395959</v>
+      </c>
+      <c r="G3" t="n">
         <v>228008</v>
-      </c>
-      <c r="G3" t="n">
-        <v>395959</v>
       </c>
       <c r="H3" t="n">
         <v>207571</v>
@@ -1567,55 +1586,55 @@
         <v>127684</v>
       </c>
       <c r="L3" t="n">
+        <v>67339</v>
+      </c>
+      <c r="M3" t="n">
         <v>61336</v>
       </c>
-      <c r="M3" t="n">
-        <v>67339</v>
-      </c>
       <c r="N3" t="n">
+        <v>80844</v>
+      </c>
+      <c r="O3" t="n">
+        <v>73593</v>
+      </c>
+      <c r="P3" t="n">
         <v>100633</v>
       </c>
-      <c r="O3" t="n">
+      <c r="Q3" t="n">
+        <v>49729</v>
+      </c>
+      <c r="R3" t="n">
         <v>50963</v>
       </c>
-      <c r="P3" t="n">
-        <v>80844</v>
-      </c>
-      <c r="Q3" t="n">
+      <c r="S3" t="n">
         <v>36991</v>
-      </c>
-      <c r="R3" t="n">
-        <v>37070</v>
-      </c>
-      <c r="S3" t="n">
-        <v>73593</v>
       </c>
       <c r="T3" t="n">
         <v>37285</v>
       </c>
       <c r="U3" t="n">
-        <v>49729</v>
+        <v>37070</v>
       </c>
       <c r="V3" t="n">
+        <v>6769</v>
+      </c>
+      <c r="W3" t="n">
         <v>35008</v>
-      </c>
-      <c r="W3" t="n">
-        <v>25260</v>
       </c>
       <c r="X3" t="n">
         <v>21182</v>
       </c>
       <c r="Y3" t="n">
-        <v>6769</v>
+        <v>25260</v>
       </c>
       <c r="Z3" t="n">
-        <v>1999</v>
+        <v>2494</v>
       </c>
       <c r="AA3" t="n">
         <v>24186</v>
       </c>
       <c r="AB3" t="n">
-        <v>2494</v>
+        <v>15284</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -1624,16 +1643,16 @@
         <v>6332</v>
       </c>
       <c r="AE3" t="n">
+        <v>7078</v>
+      </c>
+      <c r="AF3" t="n">
         <v>4347</v>
       </c>
-      <c r="AF3" t="n">
-        <v>15284</v>
-      </c>
       <c r="AG3" t="n">
-        <v>7078</v>
+        <v>3023</v>
       </c>
       <c r="AH3" t="n">
-        <v>3023</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
         <v>2493</v>
@@ -1642,49 +1661,49 @@
         <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>1175</v>
+        <v>1999</v>
       </c>
       <c r="AL3" t="n">
         <v>599</v>
       </c>
       <c r="AM3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>1175</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>4598</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ3" t="n">
         <v>707</v>
       </c>
-      <c r="AN3" t="n">
+      <c r="AR3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>119</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>299</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW3" t="n">
         <v>238</v>
       </c>
-      <c r="AO3" t="n">
-        <v>299</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>119</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>4598</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>0</v>
-      </c>
       <c r="AX3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY3" t="n">
         <v>7496</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>0</v>
       </c>
       <c r="AZ3" t="n">
         <v>0</v>
@@ -1693,19 +1712,19 @@
         <v>993055</v>
       </c>
       <c r="BB3" t="n">
+        <v>361040</v>
+      </c>
+      <c r="BC3" t="n">
         <v>604111</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>361040</v>
       </c>
       <c r="BD3" t="n">
         <v>425875</v>
       </c>
       <c r="BE3" t="n">
+        <v>418692</v>
+      </c>
+      <c r="BF3" t="n">
         <v>273379</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>418692</v>
       </c>
       <c r="BG3" t="n">
         <v>223827</v>
@@ -1720,55 +1739,55 @@
         <v>127684</v>
       </c>
       <c r="BK3" t="n">
+        <v>73046</v>
+      </c>
+      <c r="BL3" t="n">
         <v>70803</v>
       </c>
-      <c r="BL3" t="n">
-        <v>73046</v>
-      </c>
       <c r="BM3" t="n">
+        <v>86032</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>79368</v>
+      </c>
+      <c r="BO3" t="n">
         <v>101633</v>
       </c>
-      <c r="BN3" t="n">
+      <c r="BP3" t="n">
+        <v>50749</v>
+      </c>
+      <c r="BQ3" t="n">
         <v>52213</v>
       </c>
-      <c r="BO3" t="n">
-        <v>86032</v>
-      </c>
-      <c r="BP3" t="n">
+      <c r="BR3" t="n">
         <v>38364</v>
-      </c>
-      <c r="BQ3" t="n">
-        <v>40335</v>
-      </c>
-      <c r="BR3" t="n">
-        <v>79368</v>
       </c>
       <c r="BS3" t="n">
         <v>42195</v>
       </c>
       <c r="BT3" t="n">
-        <v>50749</v>
+        <v>40335</v>
       </c>
       <c r="BU3" t="n">
+        <v>7329</v>
+      </c>
+      <c r="BV3" t="n">
         <v>35258</v>
-      </c>
-      <c r="BV3" t="n">
-        <v>33620</v>
       </c>
       <c r="BW3" t="n">
         <v>27287</v>
       </c>
       <c r="BX3" t="n">
-        <v>7329</v>
+        <v>33620</v>
       </c>
       <c r="BY3" t="n">
-        <v>1999</v>
+        <v>2494</v>
       </c>
       <c r="BZ3" t="n">
         <v>24186</v>
       </c>
       <c r="CA3" t="n">
-        <v>2494</v>
+        <v>17169</v>
       </c>
       <c r="CB3" t="n">
         <v>0</v>
@@ -1777,16 +1796,16 @@
         <v>7634</v>
       </c>
       <c r="CD3" t="n">
+        <v>7541</v>
+      </c>
+      <c r="CE3" t="n">
         <v>4347</v>
       </c>
-      <c r="CE3" t="n">
-        <v>17169</v>
-      </c>
       <c r="CF3" t="n">
-        <v>7541</v>
+        <v>3173</v>
       </c>
       <c r="CG3" t="n">
-        <v>3173</v>
+        <v>0</v>
       </c>
       <c r="CH3" t="n">
         <v>2493</v>
@@ -1795,49 +1814,49 @@
         <v>0</v>
       </c>
       <c r="CJ3" t="n">
-        <v>1365</v>
+        <v>1999</v>
       </c>
       <c r="CK3" t="n">
         <v>599</v>
       </c>
       <c r="CL3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM3" t="n">
+        <v>1365</v>
+      </c>
+      <c r="CN3" t="n">
+        <v>4598</v>
+      </c>
+      <c r="CO3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP3" t="n">
         <v>707</v>
       </c>
-      <c r="CM3" t="n">
+      <c r="CQ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS3" t="n">
+        <v>200</v>
+      </c>
+      <c r="CT3" t="n">
+        <v>499</v>
+      </c>
+      <c r="CU3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV3" t="n">
         <v>238</v>
       </c>
-      <c r="CN3" t="n">
-        <v>499</v>
-      </c>
-      <c r="CO3" t="n">
-        <v>200</v>
-      </c>
-      <c r="CP3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ3" t="n">
-        <v>4598</v>
-      </c>
-      <c r="CR3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CS3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CT3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CU3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CV3" t="n">
-        <v>0</v>
-      </c>
       <c r="CW3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX3" t="n">
         <v>7496</v>
-      </c>
-      <c r="CX3" t="n">
-        <v>0</v>
       </c>
       <c r="CY3" t="n">
         <v>0</v>
@@ -1853,19 +1872,19 @@
         <v>961758</v>
       </c>
       <c r="C4" t="n">
+        <v>433947</v>
+      </c>
+      <c r="D4" t="n">
         <v>730742</v>
-      </c>
-      <c r="D4" t="n">
-        <v>433947</v>
       </c>
       <c r="E4" t="n">
         <v>504865</v>
       </c>
       <c r="F4" t="n">
+        <v>421318</v>
+      </c>
+      <c r="G4" t="n">
         <v>231963</v>
-      </c>
-      <c r="G4" t="n">
-        <v>421318</v>
       </c>
       <c r="H4" t="n">
         <v>286834</v>
@@ -1880,55 +1899,55 @@
         <v>194941</v>
       </c>
       <c r="L4" t="n">
+        <v>61562</v>
+      </c>
+      <c r="M4" t="n">
         <v>60245</v>
       </c>
-      <c r="M4" t="n">
-        <v>61562</v>
-      </c>
       <c r="N4" t="n">
+        <v>67239</v>
+      </c>
+      <c r="O4" t="n">
+        <v>217598</v>
+      </c>
+      <c r="P4" t="n">
         <v>75341</v>
       </c>
-      <c r="O4" t="n">
+      <c r="Q4" t="n">
+        <v>116190</v>
+      </c>
+      <c r="R4" t="n">
         <v>47978</v>
       </c>
-      <c r="P4" t="n">
-        <v>67239</v>
-      </c>
-      <c r="Q4" t="n">
+      <c r="S4" t="n">
         <v>58973</v>
-      </c>
-      <c r="R4" t="n">
-        <v>32246</v>
-      </c>
-      <c r="S4" t="n">
-        <v>217598</v>
       </c>
       <c r="T4" t="n">
         <v>24405</v>
       </c>
       <c r="U4" t="n">
-        <v>116190</v>
+        <v>32246</v>
       </c>
       <c r="V4" t="n">
+        <v>21030</v>
+      </c>
+      <c r="W4" t="n">
         <v>24659</v>
-      </c>
-      <c r="W4" t="n">
-        <v>39013</v>
       </c>
       <c r="X4" t="n">
         <v>26881</v>
       </c>
       <c r="Y4" t="n">
-        <v>21030</v>
+        <v>39013</v>
       </c>
       <c r="Z4" t="n">
-        <v>1999</v>
+        <v>1495</v>
       </c>
       <c r="AA4" t="n">
         <v>16702</v>
       </c>
       <c r="AB4" t="n">
-        <v>1495</v>
+        <v>8860</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1937,16 +1956,16 @@
         <v>10252</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1706</v>
       </c>
       <c r="AF4" t="n">
-        <v>8860</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>1706</v>
+        <v>2757</v>
       </c>
       <c r="AH4" t="n">
-        <v>2757</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
         <v>2607</v>
@@ -1955,49 +1974,49 @@
         <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>1145</v>
+        <v>1999</v>
       </c>
       <c r="AL4" t="n">
         <v>1294</v>
       </c>
       <c r="AM4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>1145</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>1899</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ4" t="n">
         <v>1383</v>
       </c>
-      <c r="AN4" t="n">
+      <c r="AR4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>-449</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>600</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>349</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>249</v>
+      </c>
+      <c r="AW4" t="n">
         <v>-240</v>
       </c>
-      <c r="AO4" t="n">
-        <v>349</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>600</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>249</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>1899</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>0</v>
-      </c>
       <c r="AX4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY4" t="n">
         <v>1699</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>-449</v>
       </c>
       <c r="AZ4" t="n">
         <v>0</v>
@@ -2006,19 +2025,19 @@
         <v>1056554</v>
       </c>
       <c r="BB4" t="n">
+        <v>476212</v>
+      </c>
+      <c r="BC4" t="n">
         <v>736222</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>476212</v>
       </c>
       <c r="BD4" t="n">
         <v>531286</v>
       </c>
       <c r="BE4" t="n">
+        <v>453007</v>
+      </c>
+      <c r="BF4" t="n">
         <v>279352</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>453007</v>
       </c>
       <c r="BG4" t="n">
         <v>306138</v>
@@ -2033,55 +2052,55 @@
         <v>194941</v>
       </c>
       <c r="BK4" t="n">
+        <v>67059</v>
+      </c>
+      <c r="BL4" t="n">
         <v>70166</v>
       </c>
-      <c r="BL4" t="n">
-        <v>67059</v>
-      </c>
       <c r="BM4" t="n">
+        <v>71423</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>217648</v>
+      </c>
+      <c r="BO4" t="n">
         <v>79252</v>
       </c>
-      <c r="BN4" t="n">
+      <c r="BP4" t="n">
+        <v>117225</v>
+      </c>
+      <c r="BQ4" t="n">
         <v>49518</v>
       </c>
-      <c r="BO4" t="n">
-        <v>71423</v>
-      </c>
-      <c r="BP4" t="n">
+      <c r="BR4" t="n">
         <v>60409</v>
-      </c>
-      <c r="BQ4" t="n">
-        <v>34311</v>
-      </c>
-      <c r="BR4" t="n">
-        <v>217648</v>
       </c>
       <c r="BS4" t="n">
         <v>29753</v>
       </c>
       <c r="BT4" t="n">
-        <v>117225</v>
+        <v>34311</v>
       </c>
       <c r="BU4" t="n">
+        <v>21380</v>
+      </c>
+      <c r="BV4" t="n">
         <v>28119</v>
-      </c>
-      <c r="BV4" t="n">
-        <v>52773</v>
       </c>
       <c r="BW4" t="n">
         <v>29331</v>
       </c>
       <c r="BX4" t="n">
-        <v>21380</v>
+        <v>52773</v>
       </c>
       <c r="BY4" t="n">
-        <v>1999</v>
+        <v>895</v>
       </c>
       <c r="BZ4" t="n">
         <v>16827</v>
       </c>
       <c r="CA4" t="n">
-        <v>895</v>
+        <v>8478</v>
       </c>
       <c r="CB4" t="n">
         <v>0</v>
@@ -2090,16 +2109,16 @@
         <v>11645</v>
       </c>
       <c r="CD4" t="n">
-        <v>0</v>
+        <v>1931</v>
       </c>
       <c r="CE4" t="n">
-        <v>8478</v>
+        <v>0</v>
       </c>
       <c r="CF4" t="n">
-        <v>1931</v>
+        <v>2782</v>
       </c>
       <c r="CG4" t="n">
-        <v>2782</v>
+        <v>0</v>
       </c>
       <c r="CH4" t="n">
         <v>2607</v>
@@ -2108,49 +2127,49 @@
         <v>0</v>
       </c>
       <c r="CJ4" t="n">
-        <v>1145</v>
+        <v>1999</v>
       </c>
       <c r="CK4" t="n">
         <v>1294</v>
       </c>
       <c r="CL4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM4" t="n">
+        <v>1145</v>
+      </c>
+      <c r="CN4" t="n">
+        <v>1899</v>
+      </c>
+      <c r="CO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP4" t="n">
         <v>1383</v>
       </c>
-      <c r="CM4" t="n">
+      <c r="CQ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR4" t="n">
+        <v>-449</v>
+      </c>
+      <c r="CS4" t="n">
+        <v>600</v>
+      </c>
+      <c r="CT4" t="n">
+        <v>349</v>
+      </c>
+      <c r="CU4" t="n">
+        <v>249</v>
+      </c>
+      <c r="CV4" t="n">
         <v>-240</v>
       </c>
-      <c r="CN4" t="n">
-        <v>349</v>
-      </c>
-      <c r="CO4" t="n">
-        <v>600</v>
-      </c>
-      <c r="CP4" t="n">
-        <v>249</v>
-      </c>
-      <c r="CQ4" t="n">
-        <v>1899</v>
-      </c>
-      <c r="CR4" t="n">
-        <v>0</v>
-      </c>
-      <c r="CS4" t="n">
-        <v>0</v>
-      </c>
-      <c r="CT4" t="n">
-        <v>0</v>
-      </c>
-      <c r="CU4" t="n">
-        <v>0</v>
-      </c>
-      <c r="CV4" t="n">
-        <v>0</v>
-      </c>
       <c r="CW4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX4" t="n">
         <v>1699</v>
-      </c>
-      <c r="CX4" t="n">
-        <v>-449</v>
       </c>
       <c r="CY4" t="n">
         <v>0</v>
@@ -2166,19 +2185,19 @@
         <v>713526</v>
       </c>
       <c r="C5" t="n">
+        <v>328243</v>
+      </c>
+      <c r="D5" t="n">
         <v>690356</v>
-      </c>
-      <c r="D5" t="n">
-        <v>328243</v>
       </c>
       <c r="E5" t="n">
         <v>367286</v>
       </c>
       <c r="F5" t="n">
+        <v>345498</v>
+      </c>
+      <c r="G5" t="n">
         <v>144287</v>
-      </c>
-      <c r="G5" t="n">
-        <v>345498</v>
       </c>
       <c r="H5" t="n">
         <v>288730</v>
@@ -2193,55 +2212,55 @@
         <v>133483</v>
       </c>
       <c r="L5" t="n">
+        <v>74303</v>
+      </c>
+      <c r="M5" t="n">
         <v>56893</v>
       </c>
-      <c r="M5" t="n">
-        <v>74303</v>
-      </c>
       <c r="N5" t="n">
+        <v>48017</v>
+      </c>
+      <c r="O5" t="n">
+        <v>58934</v>
+      </c>
+      <c r="P5" t="n">
         <v>68098</v>
       </c>
-      <c r="O5" t="n">
+      <c r="Q5" t="n">
+        <v>64592</v>
+      </c>
+      <c r="R5" t="n">
         <v>69556</v>
       </c>
-      <c r="P5" t="n">
-        <v>48017</v>
-      </c>
-      <c r="Q5" t="n">
+      <c r="S5" t="n">
         <v>38842</v>
-      </c>
-      <c r="R5" t="n">
-        <v>24236</v>
-      </c>
-      <c r="S5" t="n">
-        <v>58934</v>
       </c>
       <c r="T5" t="n">
         <v>36208</v>
       </c>
       <c r="U5" t="n">
-        <v>64592</v>
+        <v>24236</v>
       </c>
       <c r="V5" t="n">
+        <v>26214</v>
+      </c>
+      <c r="W5" t="n">
         <v>19520</v>
-      </c>
-      <c r="W5" t="n">
-        <v>27278</v>
       </c>
       <c r="X5" t="n">
         <v>22365</v>
       </c>
       <c r="Y5" t="n">
-        <v>26214</v>
+        <v>27278</v>
       </c>
       <c r="Z5" t="n">
-        <v>5496</v>
+        <v>9663</v>
       </c>
       <c r="AA5" t="n">
         <v>17872</v>
       </c>
       <c r="AB5" t="n">
-        <v>9663</v>
+        <v>10005</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -2250,16 +2269,16 @@
         <v>3944</v>
       </c>
       <c r="AE5" t="n">
+        <v>3791</v>
+      </c>
+      <c r="AF5" t="n">
         <v>7453</v>
       </c>
-      <c r="AF5" t="n">
-        <v>10005</v>
-      </c>
       <c r="AG5" t="n">
-        <v>3791</v>
+        <v>1966</v>
       </c>
       <c r="AH5" t="n">
-        <v>1966</v>
+        <v>2097</v>
       </c>
       <c r="AI5" t="n">
         <v>2642</v>
@@ -2268,49 +2287,49 @@
         <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>2329</v>
+        <v>5496</v>
       </c>
       <c r="AL5" t="n">
         <v>359</v>
       </c>
       <c r="AM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>2329</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>3158</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ5" t="n">
         <v>645</v>
       </c>
-      <c r="AN5" t="n">
+      <c r="AR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>-209</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW5" t="n">
         <v>921</v>
       </c>
-      <c r="AO5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>-209</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>3158</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>2097</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>0</v>
-      </c>
       <c r="AX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY5" t="n">
         <v>2718</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>0</v>
       </c>
       <c r="AZ5" t="n">
         <v>0</v>
@@ -2319,19 +2338,19 @@
         <v>927463</v>
       </c>
       <c r="BB5" t="n">
+        <v>378136</v>
+      </c>
+      <c r="BC5" t="n">
         <v>816682</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>378136</v>
       </c>
       <c r="BD5" t="n">
         <v>435706</v>
       </c>
       <c r="BE5" t="n">
+        <v>436078</v>
+      </c>
+      <c r="BF5" t="n">
         <v>165468</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>436078</v>
       </c>
       <c r="BG5" t="n">
         <v>342601</v>
@@ -2346,55 +2365,55 @@
         <v>138503</v>
       </c>
       <c r="BK5" t="n">
+        <v>88168</v>
+      </c>
+      <c r="BL5" t="n">
         <v>61647</v>
       </c>
-      <c r="BL5" t="n">
-        <v>88168</v>
-      </c>
       <c r="BM5" t="n">
+        <v>64575</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>76607</v>
+      </c>
+      <c r="BO5" t="n">
         <v>89339</v>
       </c>
-      <c r="BN5" t="n">
+      <c r="BP5" t="n">
+        <v>75634</v>
+      </c>
+      <c r="BQ5" t="n">
         <v>78026</v>
       </c>
-      <c r="BO5" t="n">
-        <v>64575</v>
-      </c>
-      <c r="BP5" t="n">
+      <c r="BR5" t="n">
         <v>39821</v>
-      </c>
-      <c r="BQ5" t="n">
-        <v>31486</v>
-      </c>
-      <c r="BR5" t="n">
-        <v>76607</v>
       </c>
       <c r="BS5" t="n">
         <v>75103</v>
       </c>
       <c r="BT5" t="n">
-        <v>75634</v>
+        <v>31486</v>
       </c>
       <c r="BU5" t="n">
+        <v>26389</v>
+      </c>
+      <c r="BV5" t="n">
         <v>19820</v>
-      </c>
-      <c r="BV5" t="n">
-        <v>54468</v>
       </c>
       <c r="BW5" t="n">
         <v>25890</v>
       </c>
       <c r="BX5" t="n">
-        <v>26389</v>
+        <v>54468</v>
       </c>
       <c r="BY5" t="n">
-        <v>8596</v>
+        <v>13623</v>
       </c>
       <c r="BZ5" t="n">
         <v>24257</v>
       </c>
       <c r="CA5" t="n">
-        <v>13623</v>
+        <v>13779</v>
       </c>
       <c r="CB5" t="n">
         <v>0</v>
@@ -2403,16 +2422,16 @@
         <v>5402</v>
       </c>
       <c r="CD5" t="n">
+        <v>4379</v>
+      </c>
+      <c r="CE5" t="n">
         <v>10443</v>
       </c>
-      <c r="CE5" t="n">
-        <v>13779</v>
-      </c>
       <c r="CF5" t="n">
-        <v>4379</v>
+        <v>2377</v>
       </c>
       <c r="CG5" t="n">
-        <v>2377</v>
+        <v>2097</v>
       </c>
       <c r="CH5" t="n">
         <v>3377</v>
@@ -2421,49 +2440,49 @@
         <v>0</v>
       </c>
       <c r="CJ5" t="n">
-        <v>3277</v>
+        <v>8596</v>
       </c>
       <c r="CK5" t="n">
         <v>599</v>
       </c>
       <c r="CL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM5" t="n">
+        <v>3277</v>
+      </c>
+      <c r="CN5" t="n">
+        <v>3798</v>
+      </c>
+      <c r="CO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP5" t="n">
         <v>975</v>
       </c>
-      <c r="CM5" t="n">
+      <c r="CQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS5" t="n">
+        <v>-300</v>
+      </c>
+      <c r="CT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV5" t="n">
         <v>1497</v>
       </c>
-      <c r="CN5" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO5" t="n">
-        <v>-300</v>
-      </c>
-      <c r="CP5" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ5" t="n">
-        <v>3798</v>
-      </c>
-      <c r="CR5" t="n">
-        <v>2097</v>
-      </c>
-      <c r="CS5" t="n">
-        <v>0</v>
-      </c>
-      <c r="CT5" t="n">
-        <v>0</v>
-      </c>
-      <c r="CU5" t="n">
-        <v>0</v>
-      </c>
-      <c r="CV5" t="n">
-        <v>0</v>
-      </c>
       <c r="CW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX5" t="n">
         <v>3398</v>
-      </c>
-      <c r="CX5" t="n">
-        <v>0</v>
       </c>
       <c r="CY5" t="n">
         <v>0</v>
@@ -2792,19 +2811,19 @@
         <v>1124651</v>
       </c>
       <c r="C7" t="n">
+        <v>459297</v>
+      </c>
+      <c r="D7" t="n">
         <v>674280</v>
-      </c>
-      <c r="D7" t="n">
-        <v>459297</v>
       </c>
       <c r="E7" t="n">
         <v>453421</v>
       </c>
       <c r="F7" t="n">
+        <v>298970</v>
+      </c>
+      <c r="G7" t="n">
         <v>301080</v>
-      </c>
-      <c r="G7" t="n">
-        <v>298970</v>
       </c>
       <c r="H7" t="n">
         <v>274813</v>
@@ -2819,55 +2838,55 @@
         <v>124602</v>
       </c>
       <c r="L7" t="n">
+        <v>75075</v>
+      </c>
+      <c r="M7" t="n">
         <v>78173</v>
       </c>
-      <c r="M7" t="n">
-        <v>75075</v>
-      </c>
       <c r="N7" t="n">
+        <v>53126</v>
+      </c>
+      <c r="O7" t="n">
+        <v>40461</v>
+      </c>
+      <c r="P7" t="n">
         <v>64179</v>
       </c>
-      <c r="O7" t="n">
+      <c r="Q7" t="n">
+        <v>36394</v>
+      </c>
+      <c r="R7" t="n">
         <v>56918</v>
       </c>
-      <c r="P7" t="n">
-        <v>53126</v>
-      </c>
-      <c r="Q7" t="n">
+      <c r="S7" t="n">
         <v>46615</v>
-      </c>
-      <c r="R7" t="n">
-        <v>41340</v>
-      </c>
-      <c r="S7" t="n">
-        <v>40461</v>
       </c>
       <c r="T7" t="n">
         <v>39969</v>
       </c>
       <c r="U7" t="n">
-        <v>36394</v>
+        <v>41340</v>
       </c>
       <c r="V7" t="n">
+        <v>22115</v>
+      </c>
+      <c r="W7" t="n">
         <v>28257</v>
-      </c>
-      <c r="W7" t="n">
-        <v>24354</v>
       </c>
       <c r="X7" t="n">
         <v>22400</v>
       </c>
       <c r="Y7" t="n">
-        <v>22115</v>
+        <v>24354</v>
       </c>
       <c r="Z7" t="n">
-        <v>19469</v>
+        <v>9563</v>
       </c>
       <c r="AA7" t="n">
         <v>14787</v>
       </c>
       <c r="AB7" t="n">
-        <v>9563</v>
+        <v>5309</v>
       </c>
       <c r="AC7" t="n">
         <v>6086</v>
@@ -2876,16 +2895,16 @@
         <v>6058</v>
       </c>
       <c r="AE7" t="n">
+        <v>3844</v>
+      </c>
+      <c r="AF7" t="n">
         <v>5855</v>
       </c>
-      <c r="AF7" t="n">
-        <v>5309</v>
-      </c>
       <c r="AG7" t="n">
-        <v>3844</v>
+        <v>2309</v>
       </c>
       <c r="AH7" t="n">
-        <v>2309</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
         <v>2255</v>
@@ -2894,43 +2913,43 @@
         <v>1919</v>
       </c>
       <c r="AK7" t="n">
-        <v>1557</v>
+        <v>19469</v>
       </c>
       <c r="AL7" t="n">
         <v>1244</v>
       </c>
       <c r="AM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>1557</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ7" t="n">
         <v>1032</v>
       </c>
-      <c r="AN7" t="n">
+      <c r="AR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>418</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>628</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>298</v>
+      </c>
+      <c r="AW7" t="n">
         <v>714</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>628</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>418</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>298</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>0</v>
       </c>
       <c r="AX7" t="n">
         <v>0</v>
@@ -2945,19 +2964,19 @@
         <v>1454660</v>
       </c>
       <c r="BB7" t="n">
+        <v>526072</v>
+      </c>
+      <c r="BC7" t="n">
         <v>906692</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>526072</v>
       </c>
       <c r="BD7" t="n">
         <v>542333</v>
       </c>
       <c r="BE7" t="n">
+        <v>369652</v>
+      </c>
+      <c r="BF7" t="n">
         <v>366778</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>369652</v>
       </c>
       <c r="BG7" t="n">
         <v>348013</v>
@@ -2972,55 +2991,55 @@
         <v>124842</v>
       </c>
       <c r="BK7" t="n">
+        <v>105397</v>
+      </c>
+      <c r="BL7" t="n">
         <v>88233</v>
       </c>
-      <c r="BL7" t="n">
-        <v>105397</v>
-      </c>
       <c r="BM7" t="n">
+        <v>65745</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>49235</v>
+      </c>
+      <c r="BO7" t="n">
         <v>82050</v>
       </c>
-      <c r="BN7" t="n">
+      <c r="BP7" t="n">
+        <v>41531</v>
+      </c>
+      <c r="BQ7" t="n">
         <v>63763</v>
       </c>
-      <c r="BO7" t="n">
-        <v>65745</v>
-      </c>
-      <c r="BP7" t="n">
+      <c r="BR7" t="n">
         <v>51450</v>
-      </c>
-      <c r="BQ7" t="n">
-        <v>47095</v>
-      </c>
-      <c r="BR7" t="n">
-        <v>49235</v>
       </c>
       <c r="BS7" t="n">
         <v>76809</v>
       </c>
       <c r="BT7" t="n">
-        <v>41531</v>
+        <v>47095</v>
       </c>
       <c r="BU7" t="n">
+        <v>22500</v>
+      </c>
+      <c r="BV7" t="n">
         <v>29217</v>
-      </c>
-      <c r="BV7" t="n">
-        <v>47884</v>
       </c>
       <c r="BW7" t="n">
         <v>25540</v>
       </c>
       <c r="BX7" t="n">
-        <v>22500</v>
+        <v>47884</v>
       </c>
       <c r="BY7" t="n">
-        <v>23789</v>
+        <v>10883</v>
       </c>
       <c r="BZ7" t="n">
         <v>18687</v>
       </c>
       <c r="CA7" t="n">
-        <v>10883</v>
+        <v>8792</v>
       </c>
       <c r="CB7" t="n">
         <v>6086</v>
@@ -3029,16 +3048,16 @@
         <v>7845</v>
       </c>
       <c r="CD7" t="n">
+        <v>4401</v>
+      </c>
+      <c r="CE7" t="n">
         <v>7595</v>
       </c>
-      <c r="CE7" t="n">
-        <v>8792</v>
-      </c>
       <c r="CF7" t="n">
-        <v>4401</v>
+        <v>2616</v>
       </c>
       <c r="CG7" t="n">
-        <v>2616</v>
+        <v>0</v>
       </c>
       <c r="CH7" t="n">
         <v>2725</v>
@@ -3047,51 +3066,364 @@
         <v>2094</v>
       </c>
       <c r="CJ7" t="n">
-        <v>2511</v>
+        <v>23789</v>
       </c>
       <c r="CK7" t="n">
         <v>1244</v>
       </c>
       <c r="CL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM7" t="n">
+        <v>2511</v>
+      </c>
+      <c r="CN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP7" t="n">
         <v>1642</v>
       </c>
-      <c r="CM7" t="n">
+      <c r="CQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS7" t="n">
+        <v>600</v>
+      </c>
+      <c r="CT7" t="n">
+        <v>748</v>
+      </c>
+      <c r="CU7" t="n">
+        <v>398</v>
+      </c>
+      <c r="CV7" t="n">
         <v>1920</v>
       </c>
-      <c r="CN7" t="n">
-        <v>748</v>
-      </c>
-      <c r="CO7" t="n">
+      <c r="CW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1795351</v>
+      </c>
+      <c r="C8" t="n">
+        <v>671820</v>
+      </c>
+      <c r="D8" t="n">
+        <v>667221</v>
+      </c>
+      <c r="E8" t="n">
+        <v>655780</v>
+      </c>
+      <c r="F8" t="n">
+        <v>457175</v>
+      </c>
+      <c r="G8" t="n">
+        <v>382545</v>
+      </c>
+      <c r="H8" t="n">
+        <v>371541</v>
+      </c>
+      <c r="I8" t="n">
+        <v>322879</v>
+      </c>
+      <c r="J8" t="n">
+        <v>272879</v>
+      </c>
+      <c r="K8" t="n">
+        <v>220747</v>
+      </c>
+      <c r="L8" t="n">
+        <v>148655</v>
+      </c>
+      <c r="M8" t="n">
+        <v>102059</v>
+      </c>
+      <c r="N8" t="n">
+        <v>89833</v>
+      </c>
+      <c r="O8" t="n">
+        <v>88964</v>
+      </c>
+      <c r="P8" t="n">
+        <v>86220</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>81346</v>
+      </c>
+      <c r="R8" t="n">
+        <v>76824</v>
+      </c>
+      <c r="S8" t="n">
+        <v>65251</v>
+      </c>
+      <c r="T8" t="n">
+        <v>58223</v>
+      </c>
+      <c r="U8" t="n">
+        <v>50814</v>
+      </c>
+      <c r="V8" t="n">
+        <v>37677</v>
+      </c>
+      <c r="W8" t="n">
+        <v>37646</v>
+      </c>
+      <c r="X8" t="n">
+        <v>36468</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>33746</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>22401</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>19341</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>8715</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>8476</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>6945</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>6235</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>3827</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>3328</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>3240</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>2564</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>2495</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>1598</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>1597</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>1198</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>1148</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>959</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>749</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>654</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>476</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>449</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>418</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>329</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>298</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>177</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>2368354</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>762555</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>845131</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>806166</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>583821</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>468350</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>485023</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>330726</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>327616</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>220867</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>209354</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>116016</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>108297</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>116843</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>126411</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>90587</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>91639</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>75090</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>118547</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>63798</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>38892</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>41006</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>40653</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>67536</v>
+      </c>
+      <c r="BY8" t="n">
+        <v>32731</v>
+      </c>
+      <c r="BZ8" t="n">
+        <v>23551</v>
+      </c>
+      <c r="CA8" t="n">
+        <v>13883</v>
+      </c>
+      <c r="CB8" t="n">
+        <v>8476</v>
+      </c>
+      <c r="CC8" t="n">
+        <v>8531</v>
+      </c>
+      <c r="CD8" t="n">
+        <v>7439</v>
+      </c>
+      <c r="CE8" t="n">
+        <v>4697</v>
+      </c>
+      <c r="CF8" t="n">
+        <v>3634</v>
+      </c>
+      <c r="CG8" t="n">
+        <v>4290</v>
+      </c>
+      <c r="CH8" t="n">
+        <v>3680</v>
+      </c>
+      <c r="CI8" t="n">
+        <v>2495</v>
+      </c>
+      <c r="CJ8" t="n">
+        <v>3998</v>
+      </c>
+      <c r="CK8" t="n">
+        <v>1597</v>
+      </c>
+      <c r="CL8" t="n">
+        <v>1998</v>
+      </c>
+      <c r="CM8" t="n">
+        <v>1982</v>
+      </c>
+      <c r="CN8" t="n">
+        <v>1599</v>
+      </c>
+      <c r="CO8" t="n">
+        <v>1499</v>
+      </c>
+      <c r="CP8" t="n">
+        <v>1184</v>
+      </c>
+      <c r="CQ8" t="n">
+        <v>1596</v>
+      </c>
+      <c r="CR8" t="n">
+        <v>449</v>
+      </c>
+      <c r="CS8" t="n">
         <v>600</v>
       </c>
-      <c r="CP7" t="n">
-        <v>398</v>
-      </c>
-      <c r="CQ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="CR7" t="n">
-        <v>0</v>
-      </c>
-      <c r="CS7" t="n">
-        <v>0</v>
-      </c>
-      <c r="CT7" t="n">
-        <v>0</v>
-      </c>
-      <c r="CU7" t="n">
-        <v>0</v>
-      </c>
-      <c r="CV7" t="n">
-        <v>0</v>
-      </c>
-      <c r="CW7" t="n">
-        <v>0</v>
-      </c>
-      <c r="CX7" t="n">
-        <v>0</v>
-      </c>
-      <c r="CY7" t="n">
+      <c r="CT8" t="n">
+        <v>549</v>
+      </c>
+      <c r="CU8" t="n">
+        <v>298</v>
+      </c>
+      <c r="CV8" t="n">
+        <v>429</v>
+      </c>
+      <c r="CW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3106,208 +3438,208 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:GQ7"/>
+  <dimension ref="A1:GQ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="27" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
     <col width="24" customWidth="1" min="7" max="7"/>
     <col width="19" customWidth="1" min="8" max="8"/>
     <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="24" customWidth="1" min="10" max="10"/>
-    <col width="17" customWidth="1" min="11" max="11"/>
-    <col width="22" customWidth="1" min="12" max="12"/>
-    <col width="23" customWidth="1" min="13" max="13"/>
+    <col width="17" customWidth="1" min="10" max="10"/>
+    <col width="24" customWidth="1" min="11" max="11"/>
+    <col width="23" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
     <col width="22" customWidth="1" min="14" max="14"/>
-    <col width="15" customWidth="1" min="15" max="15"/>
-    <col width="23" customWidth="1" min="16" max="16"/>
-    <col width="19" customWidth="1" min="17" max="17"/>
-    <col width="21" customWidth="1" min="18" max="18"/>
-    <col width="27" customWidth="1" min="19" max="19"/>
-    <col width="17" customWidth="1" min="20" max="20"/>
-    <col width="26" customWidth="1" min="21" max="21"/>
+    <col width="23" customWidth="1" min="15" max="15"/>
+    <col width="19" customWidth="1" min="16" max="16"/>
+    <col width="15" customWidth="1" min="17" max="17"/>
+    <col width="17" customWidth="1" min="18" max="18"/>
+    <col width="19" customWidth="1" min="19" max="19"/>
+    <col width="26" customWidth="1" min="20" max="20"/>
+    <col width="27" customWidth="1" min="21" max="21"/>
     <col width="25" customWidth="1" min="22" max="22"/>
-    <col width="19" customWidth="1" min="23" max="23"/>
-    <col width="22" customWidth="1" min="24" max="24"/>
-    <col width="23" customWidth="1" min="25" max="25"/>
-    <col width="24" customWidth="1" min="26" max="26"/>
-    <col width="21" customWidth="1" min="27" max="27"/>
-    <col width="26" customWidth="1" min="28" max="28"/>
-    <col width="19" customWidth="1" min="29" max="29"/>
-    <col width="16" customWidth="1" min="30" max="30"/>
-    <col width="28" customWidth="1" min="31" max="31"/>
-    <col width="14" customWidth="1" min="32" max="32"/>
-    <col width="19" customWidth="1" min="33" max="33"/>
-    <col width="23" customWidth="1" min="34" max="34"/>
+    <col width="22" customWidth="1" min="23" max="23"/>
+    <col width="24" customWidth="1" min="24" max="24"/>
+    <col width="28" customWidth="1" min="25" max="25"/>
+    <col width="23" customWidth="1" min="26" max="26"/>
+    <col width="16" customWidth="1" min="27" max="27"/>
+    <col width="21" customWidth="1" min="28" max="28"/>
+    <col width="26" customWidth="1" min="29" max="29"/>
+    <col width="21" customWidth="1" min="30" max="30"/>
+    <col width="33" customWidth="1" min="31" max="31"/>
+    <col width="23" customWidth="1" min="32" max="32"/>
+    <col width="14" customWidth="1" min="33" max="33"/>
+    <col width="16" customWidth="1" min="34" max="34"/>
     <col width="19" customWidth="1" min="35" max="35"/>
-    <col width="23" customWidth="1" min="36" max="36"/>
-    <col width="16" customWidth="1" min="37" max="37"/>
-    <col width="33" customWidth="1" min="38" max="38"/>
-    <col width="22" customWidth="1" min="39" max="39"/>
-    <col width="18" customWidth="1" min="40" max="40"/>
-    <col width="18" customWidth="1" min="41" max="41"/>
-    <col width="23" customWidth="1" min="42" max="42"/>
-    <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="17" customWidth="1" min="44" max="44"/>
-    <col width="17" customWidth="1" min="45" max="45"/>
-    <col width="15" customWidth="1" min="46" max="46"/>
-    <col width="15" customWidth="1" min="47" max="47"/>
-    <col width="15" customWidth="1" min="48" max="48"/>
-    <col width="17" customWidth="1" min="49" max="49"/>
+    <col width="19" customWidth="1" min="36" max="36"/>
+    <col width="23" customWidth="1" min="37" max="37"/>
+    <col width="15" customWidth="1" min="38" max="38"/>
+    <col width="17" customWidth="1" min="39" max="39"/>
+    <col width="17" customWidth="1" min="40" max="40"/>
+    <col width="17" customWidth="1" min="41" max="41"/>
+    <col width="15" customWidth="1" min="42" max="42"/>
+    <col width="19" customWidth="1" min="43" max="43"/>
+    <col width="18" customWidth="1" min="44" max="44"/>
+    <col width="23" customWidth="1" min="45" max="45"/>
+    <col width="22" customWidth="1" min="46" max="46"/>
+    <col width="20" customWidth="1" min="47" max="47"/>
+    <col width="22" customWidth="1" min="48" max="48"/>
+    <col width="19" customWidth="1" min="49" max="49"/>
     <col width="16" customWidth="1" min="50" max="50"/>
-    <col width="22" customWidth="1" min="51" max="51"/>
-    <col width="16" customWidth="1" min="52" max="52"/>
+    <col width="24" customWidth="1" min="51" max="51"/>
+    <col width="18" customWidth="1" min="52" max="52"/>
     <col width="18" customWidth="1" min="53" max="53"/>
-    <col width="18" customWidth="1" min="54" max="54"/>
-    <col width="24" customWidth="1" min="55" max="55"/>
-    <col width="20" customWidth="1" min="56" max="56"/>
-    <col width="23" customWidth="1" min="57" max="57"/>
-    <col width="19" customWidth="1" min="58" max="58"/>
-    <col width="24" customWidth="1" min="59" max="59"/>
-    <col width="23" customWidth="1" min="60" max="60"/>
-    <col width="25" customWidth="1" min="61" max="61"/>
-    <col width="17" customWidth="1" min="62" max="62"/>
-    <col width="20" customWidth="1" min="63" max="63"/>
-    <col width="21" customWidth="1" min="64" max="64"/>
-    <col width="17" customWidth="1" min="65" max="65"/>
-    <col width="22" customWidth="1" min="66" max="66"/>
-    <col width="14" customWidth="1" min="67" max="67"/>
-    <col width="16" customWidth="1" min="68" max="68"/>
-    <col width="24" customWidth="1" min="69" max="69"/>
-    <col width="23" customWidth="1" min="70" max="70"/>
-    <col width="14" customWidth="1" min="71" max="71"/>
-    <col width="15" customWidth="1" min="72" max="72"/>
-    <col width="18" customWidth="1" min="73" max="73"/>
+    <col width="17" customWidth="1" min="54" max="54"/>
+    <col width="15" customWidth="1" min="55" max="55"/>
+    <col width="25" customWidth="1" min="56" max="56"/>
+    <col width="17" customWidth="1" min="57" max="57"/>
+    <col width="24" customWidth="1" min="58" max="58"/>
+    <col width="18" customWidth="1" min="59" max="59"/>
+    <col width="24" customWidth="1" min="60" max="60"/>
+    <col width="29" customWidth="1" min="61" max="61"/>
+    <col width="20" customWidth="1" min="62" max="62"/>
+    <col width="19" customWidth="1" min="63" max="63"/>
+    <col width="23" customWidth="1" min="64" max="64"/>
+    <col width="21" customWidth="1" min="65" max="65"/>
+    <col width="23" customWidth="1" min="66" max="66"/>
+    <col width="25" customWidth="1" min="67" max="67"/>
+    <col width="24" customWidth="1" min="68" max="68"/>
+    <col width="23" customWidth="1" min="69" max="69"/>
+    <col width="16" customWidth="1" min="70" max="70"/>
+    <col width="16" customWidth="1" min="71" max="71"/>
+    <col width="14" customWidth="1" min="72" max="72"/>
+    <col width="22" customWidth="1" min="73" max="73"/>
     <col width="14" customWidth="1" min="74" max="74"/>
-    <col width="22" customWidth="1" min="75" max="75"/>
-    <col width="21" customWidth="1" min="76" max="76"/>
-    <col width="25" customWidth="1" min="77" max="77"/>
-    <col width="17" customWidth="1" min="78" max="78"/>
-    <col width="22" customWidth="1" min="79" max="79"/>
-    <col width="25" customWidth="1" min="80" max="80"/>
-    <col width="20" customWidth="1" min="81" max="81"/>
-    <col width="20" customWidth="1" min="82" max="82"/>
-    <col width="22" customWidth="1" min="83" max="83"/>
-    <col width="19" customWidth="1" min="84" max="84"/>
-    <col width="18" customWidth="1" min="85" max="85"/>
-    <col width="16" customWidth="1" min="86" max="86"/>
-    <col width="27" customWidth="1" min="87" max="87"/>
-    <col width="15" customWidth="1" min="88" max="88"/>
-    <col width="29" customWidth="1" min="89" max="89"/>
-    <col width="15" customWidth="1" min="90" max="90"/>
-    <col width="17" customWidth="1" min="91" max="91"/>
-    <col width="24" customWidth="1" min="92" max="92"/>
-    <col width="28" customWidth="1" min="93" max="93"/>
-    <col width="15" customWidth="1" min="94" max="94"/>
-    <col width="18" customWidth="1" min="95" max="95"/>
-    <col width="19" customWidth="1" min="96" max="96"/>
-    <col width="22" customWidth="1" min="97" max="97"/>
+    <col width="20" customWidth="1" min="75" max="75"/>
+    <col width="17" customWidth="1" min="76" max="76"/>
+    <col width="15" customWidth="1" min="77" max="77"/>
+    <col width="22" customWidth="1" min="78" max="78"/>
+    <col width="18" customWidth="1" min="79" max="79"/>
+    <col width="22" customWidth="1" min="80" max="80"/>
+    <col width="27" customWidth="1" min="81" max="81"/>
+    <col width="23" customWidth="1" min="82" max="82"/>
+    <col width="19" customWidth="1" min="83" max="83"/>
+    <col width="22" customWidth="1" min="84" max="84"/>
+    <col width="15" customWidth="1" min="85" max="85"/>
+    <col width="21" customWidth="1" min="86" max="86"/>
+    <col width="16" customWidth="1" min="87" max="87"/>
+    <col width="18" customWidth="1" min="88" max="88"/>
+    <col width="22" customWidth="1" min="89" max="89"/>
+    <col width="28" customWidth="1" min="90" max="90"/>
+    <col width="22" customWidth="1" min="91" max="91"/>
+    <col width="17" customWidth="1" min="92" max="92"/>
+    <col width="14" customWidth="1" min="93" max="93"/>
+    <col width="18" customWidth="1" min="94" max="94"/>
+    <col width="15" customWidth="1" min="95" max="95"/>
+    <col width="20" customWidth="1" min="96" max="96"/>
+    <col width="17" customWidth="1" min="97" max="97"/>
     <col width="15" customWidth="1" min="98" max="98"/>
-    <col width="23" customWidth="1" min="99" max="99"/>
-    <col width="22" customWidth="1" min="100" max="100"/>
+    <col width="25" customWidth="1" min="99" max="99"/>
+    <col width="15" customWidth="1" min="100" max="100"/>
     <col width="16" customWidth="1" min="101" max="101"/>
     <col width="27" customWidth="1" min="102" max="102"/>
-    <col width="22" customWidth="1" min="103" max="103"/>
-    <col width="17" customWidth="1" min="104" max="104"/>
-    <col width="15" customWidth="1" min="105" max="105"/>
+    <col width="17" customWidth="1" min="103" max="103"/>
+    <col width="15" customWidth="1" min="104" max="104"/>
+    <col width="22" customWidth="1" min="105" max="105"/>
     <col width="24" customWidth="1" min="106" max="106"/>
     <col width="19" customWidth="1" min="107" max="107"/>
     <col width="20" customWidth="1" min="108" max="108"/>
-    <col width="24" customWidth="1" min="109" max="109"/>
-    <col width="17" customWidth="1" min="110" max="110"/>
-    <col width="22" customWidth="1" min="111" max="111"/>
-    <col width="23" customWidth="1" min="112" max="112"/>
+    <col width="17" customWidth="1" min="109" max="109"/>
+    <col width="24" customWidth="1" min="110" max="110"/>
+    <col width="23" customWidth="1" min="111" max="111"/>
+    <col width="22" customWidth="1" min="112" max="112"/>
     <col width="22" customWidth="1" min="113" max="113"/>
-    <col width="15" customWidth="1" min="114" max="114"/>
-    <col width="23" customWidth="1" min="115" max="115"/>
-    <col width="19" customWidth="1" min="116" max="116"/>
-    <col width="21" customWidth="1" min="117" max="117"/>
-    <col width="27" customWidth="1" min="118" max="118"/>
-    <col width="17" customWidth="1" min="119" max="119"/>
-    <col width="26" customWidth="1" min="120" max="120"/>
+    <col width="23" customWidth="1" min="114" max="114"/>
+    <col width="19" customWidth="1" min="115" max="115"/>
+    <col width="15" customWidth="1" min="116" max="116"/>
+    <col width="17" customWidth="1" min="117" max="117"/>
+    <col width="19" customWidth="1" min="118" max="118"/>
+    <col width="26" customWidth="1" min="119" max="119"/>
+    <col width="27" customWidth="1" min="120" max="120"/>
     <col width="25" customWidth="1" min="121" max="121"/>
-    <col width="19" customWidth="1" min="122" max="122"/>
-    <col width="22" customWidth="1" min="123" max="123"/>
-    <col width="23" customWidth="1" min="124" max="124"/>
-    <col width="24" customWidth="1" min="125" max="125"/>
-    <col width="21" customWidth="1" min="126" max="126"/>
-    <col width="26" customWidth="1" min="127" max="127"/>
-    <col width="19" customWidth="1" min="128" max="128"/>
-    <col width="16" customWidth="1" min="129" max="129"/>
-    <col width="28" customWidth="1" min="130" max="130"/>
-    <col width="14" customWidth="1" min="131" max="131"/>
-    <col width="19" customWidth="1" min="132" max="132"/>
-    <col width="23" customWidth="1" min="133" max="133"/>
+    <col width="22" customWidth="1" min="122" max="122"/>
+    <col width="24" customWidth="1" min="123" max="123"/>
+    <col width="28" customWidth="1" min="124" max="124"/>
+    <col width="23" customWidth="1" min="125" max="125"/>
+    <col width="16" customWidth="1" min="126" max="126"/>
+    <col width="21" customWidth="1" min="127" max="127"/>
+    <col width="26" customWidth="1" min="128" max="128"/>
+    <col width="21" customWidth="1" min="129" max="129"/>
+    <col width="33" customWidth="1" min="130" max="130"/>
+    <col width="23" customWidth="1" min="131" max="131"/>
+    <col width="14" customWidth="1" min="132" max="132"/>
+    <col width="16" customWidth="1" min="133" max="133"/>
     <col width="19" customWidth="1" min="134" max="134"/>
-    <col width="23" customWidth="1" min="135" max="135"/>
-    <col width="16" customWidth="1" min="136" max="136"/>
-    <col width="33" customWidth="1" min="137" max="137"/>
-    <col width="22" customWidth="1" min="138" max="138"/>
-    <col width="18" customWidth="1" min="139" max="139"/>
-    <col width="18" customWidth="1" min="140" max="140"/>
-    <col width="23" customWidth="1" min="141" max="141"/>
-    <col width="17" customWidth="1" min="142" max="142"/>
-    <col width="17" customWidth="1" min="143" max="143"/>
-    <col width="17" customWidth="1" min="144" max="144"/>
-    <col width="15" customWidth="1" min="145" max="145"/>
-    <col width="15" customWidth="1" min="146" max="146"/>
-    <col width="15" customWidth="1" min="147" max="147"/>
-    <col width="17" customWidth="1" min="148" max="148"/>
+    <col width="19" customWidth="1" min="135" max="135"/>
+    <col width="23" customWidth="1" min="136" max="136"/>
+    <col width="15" customWidth="1" min="137" max="137"/>
+    <col width="17" customWidth="1" min="138" max="138"/>
+    <col width="17" customWidth="1" min="139" max="139"/>
+    <col width="17" customWidth="1" min="140" max="140"/>
+    <col width="15" customWidth="1" min="141" max="141"/>
+    <col width="19" customWidth="1" min="142" max="142"/>
+    <col width="18" customWidth="1" min="143" max="143"/>
+    <col width="23" customWidth="1" min="144" max="144"/>
+    <col width="22" customWidth="1" min="145" max="145"/>
+    <col width="20" customWidth="1" min="146" max="146"/>
+    <col width="22" customWidth="1" min="147" max="147"/>
+    <col width="19" customWidth="1" min="148" max="148"/>
     <col width="16" customWidth="1" min="149" max="149"/>
-    <col width="22" customWidth="1" min="150" max="150"/>
-    <col width="16" customWidth="1" min="151" max="151"/>
+    <col width="24" customWidth="1" min="150" max="150"/>
+    <col width="18" customWidth="1" min="151" max="151"/>
     <col width="18" customWidth="1" min="152" max="152"/>
-    <col width="18" customWidth="1" min="153" max="153"/>
-    <col width="24" customWidth="1" min="154" max="154"/>
-    <col width="20" customWidth="1" min="155" max="155"/>
-    <col width="23" customWidth="1" min="156" max="156"/>
-    <col width="19" customWidth="1" min="157" max="157"/>
-    <col width="24" customWidth="1" min="158" max="158"/>
-    <col width="23" customWidth="1" min="159" max="159"/>
-    <col width="25" customWidth="1" min="160" max="160"/>
-    <col width="17" customWidth="1" min="161" max="161"/>
-    <col width="20" customWidth="1" min="162" max="162"/>
-    <col width="21" customWidth="1" min="163" max="163"/>
-    <col width="17" customWidth="1" min="164" max="164"/>
-    <col width="22" customWidth="1" min="165" max="165"/>
-    <col width="14" customWidth="1" min="166" max="166"/>
-    <col width="16" customWidth="1" min="167" max="167"/>
-    <col width="24" customWidth="1" min="168" max="168"/>
-    <col width="23" customWidth="1" min="169" max="169"/>
-    <col width="14" customWidth="1" min="170" max="170"/>
-    <col width="15" customWidth="1" min="171" max="171"/>
-    <col width="18" customWidth="1" min="172" max="172"/>
+    <col width="17" customWidth="1" min="153" max="153"/>
+    <col width="15" customWidth="1" min="154" max="154"/>
+    <col width="25" customWidth="1" min="155" max="155"/>
+    <col width="17" customWidth="1" min="156" max="156"/>
+    <col width="24" customWidth="1" min="157" max="157"/>
+    <col width="18" customWidth="1" min="158" max="158"/>
+    <col width="24" customWidth="1" min="159" max="159"/>
+    <col width="29" customWidth="1" min="160" max="160"/>
+    <col width="20" customWidth="1" min="161" max="161"/>
+    <col width="19" customWidth="1" min="162" max="162"/>
+    <col width="23" customWidth="1" min="163" max="163"/>
+    <col width="21" customWidth="1" min="164" max="164"/>
+    <col width="23" customWidth="1" min="165" max="165"/>
+    <col width="25" customWidth="1" min="166" max="166"/>
+    <col width="24" customWidth="1" min="167" max="167"/>
+    <col width="23" customWidth="1" min="168" max="168"/>
+    <col width="16" customWidth="1" min="169" max="169"/>
+    <col width="16" customWidth="1" min="170" max="170"/>
+    <col width="14" customWidth="1" min="171" max="171"/>
+    <col width="22" customWidth="1" min="172" max="172"/>
     <col width="14" customWidth="1" min="173" max="173"/>
-    <col width="22" customWidth="1" min="174" max="174"/>
-    <col width="21" customWidth="1" min="175" max="175"/>
-    <col width="25" customWidth="1" min="176" max="176"/>
-    <col width="17" customWidth="1" min="177" max="177"/>
-    <col width="22" customWidth="1" min="178" max="178"/>
-    <col width="25" customWidth="1" min="179" max="179"/>
-    <col width="20" customWidth="1" min="180" max="180"/>
-    <col width="20" customWidth="1" min="181" max="181"/>
-    <col width="22" customWidth="1" min="182" max="182"/>
-    <col width="19" customWidth="1" min="183" max="183"/>
-    <col width="18" customWidth="1" min="184" max="184"/>
-    <col width="16" customWidth="1" min="185" max="185"/>
-    <col width="27" customWidth="1" min="186" max="186"/>
-    <col width="15" customWidth="1" min="187" max="187"/>
-    <col width="29" customWidth="1" min="188" max="188"/>
-    <col width="15" customWidth="1" min="189" max="189"/>
-    <col width="17" customWidth="1" min="190" max="190"/>
-    <col width="24" customWidth="1" min="191" max="191"/>
-    <col width="28" customWidth="1" min="192" max="192"/>
-    <col width="15" customWidth="1" min="193" max="193"/>
-    <col width="18" customWidth="1" min="194" max="194"/>
-    <col width="19" customWidth="1" min="195" max="195"/>
-    <col width="22" customWidth="1" min="196" max="196"/>
+    <col width="20" customWidth="1" min="174" max="174"/>
+    <col width="17" customWidth="1" min="175" max="175"/>
+    <col width="15" customWidth="1" min="176" max="176"/>
+    <col width="22" customWidth="1" min="177" max="177"/>
+    <col width="18" customWidth="1" min="178" max="178"/>
+    <col width="22" customWidth="1" min="179" max="179"/>
+    <col width="27" customWidth="1" min="180" max="180"/>
+    <col width="23" customWidth="1" min="181" max="181"/>
+    <col width="19" customWidth="1" min="182" max="182"/>
+    <col width="22" customWidth="1" min="183" max="183"/>
+    <col width="15" customWidth="1" min="184" max="184"/>
+    <col width="21" customWidth="1" min="185" max="185"/>
+    <col width="16" customWidth="1" min="186" max="186"/>
+    <col width="18" customWidth="1" min="187" max="187"/>
+    <col width="22" customWidth="1" min="188" max="188"/>
+    <col width="28" customWidth="1" min="189" max="189"/>
+    <col width="22" customWidth="1" min="190" max="190"/>
+    <col width="17" customWidth="1" min="191" max="191"/>
+    <col width="14" customWidth="1" min="192" max="192"/>
+    <col width="18" customWidth="1" min="193" max="193"/>
+    <col width="15" customWidth="1" min="194" max="194"/>
+    <col width="20" customWidth="1" min="195" max="195"/>
+    <col width="17" customWidth="1" min="196" max="196"/>
     <col width="15" customWidth="1" min="197" max="197"/>
-    <col width="23" customWidth="1" min="198" max="198"/>
-    <col width="22" customWidth="1" min="199" max="199"/>
+    <col width="25" customWidth="1" min="198" max="198"/>
+    <col width="15" customWidth="1" min="199" max="199"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3328,19 +3660,19 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>Pieces (Sell)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Only (Sell)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>New Balance (Sell)</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Pieces (Sell)</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Only (Sell)</t>
-        </is>
-      </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Que Sera Sera (Sell)</t>
@@ -3358,459 +3690,459 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>Levi's (Sell)</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>True Religion (Sell)</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Levi's (Sell)</t>
-        </is>
-      </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>Selected Men (Sell)</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Only &amp; Sons (Sell)</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>Gina Tricot (Sell)</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Selected Men (Sell)</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Only &amp; Sons (Sell)</t>
-        </is>
-      </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
+          <t>Jack &amp; Jones (Sell)</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Dr Denim (Sell)</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
           <t>Nike (Sell)</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>Jack &amp; Jones (Sell)</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>Dr Denim (Sell)</t>
-        </is>
-      </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
+          <t>Malina (Sell)</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Woodbird (Sell)</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>BECKSÖNDERGAARD (Sell)</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>By Malene Birger (Sell)</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>The North Face (Sell)</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Birkenstock (Sell)</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Samsøe Samsøe (Sell)</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Polo Ralph Lauren (Sell)</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Abrand Jeans (Sell)</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>Aim'n (Sell)</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>A.Kjærbede (Sell)</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>Muli Collection (Sell)</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
           <t>Lois Jeans (Sell)</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>By Malene Birger (Sell)</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>Malina (Sell)</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>BECKSÖNDERGAARD (Sell)</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>The North Face (Sell)</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>Woodbird (Sell)</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>Birkenstock (Sell)</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>Calvin Klein Underwear (Sell)</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>Carhartt WIP (Sell)</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>Samsøe Samsøe (Sell)</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>A.Kjærbede (Sell)</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>Muli Collection (Sell)</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>UGG (Sell)</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>Asics (Sell)</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>Converse (Sell)</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>Les Deux (Sell)</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>Sneaky Steve (Sell)</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>Gant (Sell)</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>Diesel (Sell)</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>Hunter (Sell)</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>DORINA (Sell)</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>Puma (Sell)</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>Pavement (Sell)</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>Aim'n (Sell)</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>Polo Ralph Lauren (Sell)</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>UGG (Sell)</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>Converse (Sell)</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>Abrand Jeans (Sell)</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>Les Deux (Sell)</t>
-        </is>
-      </c>
-      <c r="AJ1" s="1" t="inlineStr">
-        <is>
-          <t>Sneaky Steve (Sell)</t>
-        </is>
-      </c>
-      <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>Asics (Sell)</t>
-        </is>
-      </c>
-      <c r="AL1" s="1" t="inlineStr">
-        <is>
-          <t>Calvin Klein Underwear (Sell)</t>
-        </is>
-      </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>Inuikii (Sell)</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>One Teaspoon (Sell)</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>Hunkemöller (Sell)</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>Havaianas (Sell)</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>ATP ATELIER (Sell)</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>Le Specs (Sell)</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>Solid (Sell)</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>Mads Nørgaard (Sell)</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>Bye Bra (Sell)</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>Ciszere (Sell)</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>Inuikii (Sell)</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>One Teaspoon (Sell)</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>Hunter (Sell)</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>DORINA (Sell)</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>Diesel (Sell)</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>Gant (Sell)</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>Puma (Sell)</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>Colmar (Sell)</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>MONO (Sell)</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>Colmar (Sell)</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>Solid (Sell)</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>ATP ATELIER (Sell)</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>Corlin Eyewear (Sell)</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>ANNARR (Sell)</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>Messy Weekend (Sell)</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>Pilgrim (Sell)</t>
+        </is>
+      </c>
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>Casual Friday (Sell)</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>Calvin Klein Jeans (Sell)</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>Bluebella (Sell)</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>Columbia (Sell)</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>STICKYBESTIE (Sell)</t>
+        </is>
+      </c>
+      <c r="BM1" s="1" t="inlineStr">
+        <is>
+          <t>Björn Borg (Sell)</t>
+        </is>
+      </c>
+      <c r="BN1" s="1" t="inlineStr">
+        <is>
+          <t>Michael Kors (Sell)</t>
+        </is>
+      </c>
+      <c r="BO1" s="1" t="inlineStr">
+        <is>
+          <t>Selected Femme (Sell)</t>
+        </is>
+      </c>
+      <c r="BP1" s="1" t="inlineStr">
+        <is>
+          <t>Juicy Couture (Sell)</t>
+        </is>
+      </c>
+      <c r="BQ1" s="1" t="inlineStr">
+        <is>
+          <t>Brand Island (Sell)</t>
+        </is>
+      </c>
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>Rains (Sell)</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>Bye Bra (Sell)</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>Pilgrim (Sell)</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>Mads Nørgaard (Sell)</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>Havaianas (Sell)</t>
-        </is>
-      </c>
-      <c r="BE1" s="1" t="inlineStr">
-        <is>
-          <t>Brand Island (Sell)</t>
-        </is>
-      </c>
-      <c r="BF1" s="1" t="inlineStr">
-        <is>
-          <t>Le Specs (Sell)</t>
-        </is>
-      </c>
-      <c r="BG1" s="1" t="inlineStr">
-        <is>
-          <t>Casual Friday (Sell)</t>
-        </is>
-      </c>
-      <c r="BH1" s="1" t="inlineStr">
-        <is>
-          <t>STICKYBESTIE (Sell)</t>
-        </is>
-      </c>
-      <c r="BI1" s="1" t="inlineStr">
-        <is>
-          <t>Selected Femme (Sell)</t>
-        </is>
-      </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
+        <is>
+          <t>Spanx (Sell)</t>
+        </is>
+      </c>
+      <c r="BT1" s="1" t="inlineStr">
+        <is>
+          <t>JDY (Sell)</t>
+        </is>
+      </c>
+      <c r="BU1" s="1" t="inlineStr">
+        <is>
+          <t>By Billgren (Sell)</t>
+        </is>
+      </c>
+      <c r="BV1" s="1" t="inlineStr">
+        <is>
+          <t>IRO (Sell)</t>
+        </is>
+      </c>
+      <c r="BW1" s="1" t="inlineStr">
+        <is>
+          <t>Moon Boot (Sell)</t>
+        </is>
+      </c>
+      <c r="BX1" s="1" t="inlineStr">
+        <is>
+          <t>Scholl (Sell)</t>
+        </is>
+      </c>
+      <c r="BY1" s="1" t="inlineStr">
+        <is>
+          <t>Neuw (Sell)</t>
+        </is>
+      </c>
+      <c r="BZ1" s="1" t="inlineStr">
+        <is>
+          <t>ROCKANDBLUE (Sell)</t>
+        </is>
+      </c>
+      <c r="CA1" s="1" t="inlineStr">
+        <is>
+          <t>Dockers (Sell)</t>
+        </is>
+      </c>
+      <c r="CB1" s="1" t="inlineStr">
+        <is>
+          <t>J Lindeberg (Sell)</t>
+        </is>
+      </c>
+      <c r="CC1" s="1" t="inlineStr">
+        <is>
+          <t>Mercer Amsterdam (Sell)</t>
+        </is>
+      </c>
+      <c r="CD1" s="1" t="inlineStr">
+        <is>
+          <t>Lyle &amp; Scott (Sell)</t>
+        </is>
+      </c>
+      <c r="CE1" s="1" t="inlineStr">
+        <is>
+          <t>Shepherd (Sell)</t>
+        </is>
+      </c>
+      <c r="CF1" s="1" t="inlineStr">
+        <is>
+          <t>Marc Jacobs (Sell)</t>
+        </is>
+      </c>
+      <c r="CG1" s="1" t="inlineStr">
+        <is>
+          <t>VANS (Sell)</t>
+        </is>
+      </c>
+      <c r="CH1" s="1" t="inlineStr">
+        <is>
+          <t>Timberland (Sell)</t>
+        </is>
+      </c>
+      <c r="CI1" s="1" t="inlineStr">
+        <is>
+          <t>GABBA (Sell)</t>
+        </is>
+      </c>
+      <c r="CJ1" s="1" t="inlineStr">
+        <is>
+          <t>Playboy (Sell)</t>
+        </is>
+      </c>
+      <c r="CK1" s="1" t="inlineStr">
+        <is>
+          <t>Daily Paper (Sell)</t>
+        </is>
+      </c>
+      <c r="CL1" s="1" t="inlineStr">
+        <is>
+          <t>Magic Bodyfashion (Sell)</t>
+        </is>
+      </c>
+      <c r="CM1" s="1" t="inlineStr">
+        <is>
+          <t>Tommy Jeans (Sell)</t>
+        </is>
+      </c>
+      <c r="CN1" s="1" t="inlineStr">
         <is>
           <t>OBJECT (Sell)</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
-        <is>
-          <t>Bluebella (Sell)</t>
-        </is>
-      </c>
-      <c r="BL1" s="1" t="inlineStr">
-        <is>
-          <t>Björn Borg (Sell)</t>
-        </is>
-      </c>
-      <c r="BM1" s="1" t="inlineStr">
-        <is>
-          <t>ANNARR (Sell)</t>
-        </is>
-      </c>
-      <c r="BN1" s="1" t="inlineStr">
-        <is>
-          <t>By Billgren (Sell)</t>
-        </is>
-      </c>
-      <c r="BO1" s="1" t="inlineStr">
-        <is>
-          <t>JDY (Sell)</t>
-        </is>
-      </c>
-      <c r="BP1" s="1" t="inlineStr">
-        <is>
-          <t>Spanx (Sell)</t>
-        </is>
-      </c>
-      <c r="BQ1" s="1" t="inlineStr">
-        <is>
-          <t>Juicy Couture (Sell)</t>
-        </is>
-      </c>
-      <c r="BR1" s="1" t="inlineStr">
-        <is>
-          <t>Michael Kors (Sell)</t>
-        </is>
-      </c>
-      <c r="BS1" s="1" t="inlineStr">
-        <is>
-          <t>IRO (Sell)</t>
-        </is>
-      </c>
-      <c r="BT1" s="1" t="inlineStr">
-        <is>
-          <t>VANS (Sell)</t>
-        </is>
-      </c>
-      <c r="BU1" s="1" t="inlineStr">
-        <is>
-          <t>Dockers (Sell)</t>
-        </is>
-      </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="CO1" s="1" t="inlineStr">
         <is>
           <t>OAS (Sell)</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
-        <is>
-          <t>Marc Jacobs (Sell)</t>
-        </is>
-      </c>
-      <c r="BX1" s="1" t="inlineStr">
-        <is>
-          <t>Timberland (Sell)</t>
-        </is>
-      </c>
-      <c r="BY1" s="1" t="inlineStr">
-        <is>
-          <t>Corlin Eyewear (Sell)</t>
-        </is>
-      </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="CP1" s="1" t="inlineStr">
+        <is>
+          <t>Dickies (Sell)</t>
+        </is>
+      </c>
+      <c r="CQ1" s="1" t="inlineStr">
+        <is>
+          <t>JJXX (Sell)</t>
+        </is>
+      </c>
+      <c r="CR1" s="1" t="inlineStr">
+        <is>
+          <t>Le Bonnet (Sell)</t>
+        </is>
+      </c>
+      <c r="CS1" s="1" t="inlineStr">
         <is>
           <t>DAY ET (Sell)</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
-        <is>
-          <t>J Lindeberg (Sell)</t>
-        </is>
-      </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CT1" s="1" t="inlineStr">
+        <is>
+          <t>Teva (Sell)</t>
+        </is>
+      </c>
+      <c r="CU1" s="1" t="inlineStr">
         <is>
           <t>Bread &amp; Boxers (Sell)</t>
         </is>
       </c>
-      <c r="CC1" s="1" t="inlineStr">
-        <is>
-          <t>Le Bonnet (Sell)</t>
-        </is>
-      </c>
-      <c r="CD1" s="1" t="inlineStr">
-        <is>
-          <t>Moon Boot (Sell)</t>
-        </is>
-      </c>
-      <c r="CE1" s="1" t="inlineStr">
-        <is>
-          <t>Tommy Jeans (Sell)</t>
-        </is>
-      </c>
-      <c r="CF1" s="1" t="inlineStr">
-        <is>
-          <t>Columbia (Sell)</t>
-        </is>
-      </c>
-      <c r="CG1" s="1" t="inlineStr">
-        <is>
-          <t>Dickies (Sell)</t>
-        </is>
-      </c>
-      <c r="CH1" s="1" t="inlineStr">
-        <is>
-          <t>GABBA (Sell)</t>
-        </is>
-      </c>
-      <c r="CI1" s="1" t="inlineStr">
-        <is>
-          <t>Mercer Amsterdam (Sell)</t>
-        </is>
-      </c>
-      <c r="CJ1" s="1" t="inlineStr">
-        <is>
-          <t>JJXX (Sell)</t>
-        </is>
-      </c>
-      <c r="CK1" s="1" t="inlineStr">
-        <is>
-          <t>Calvin Klein Jeans (Sell)</t>
-        </is>
-      </c>
-      <c r="CL1" s="1" t="inlineStr">
-        <is>
-          <t>Teva (Sell)</t>
-        </is>
-      </c>
-      <c r="CM1" s="1" t="inlineStr">
-        <is>
-          <t>Scholl (Sell)</t>
-        </is>
-      </c>
-      <c r="CN1" s="1" t="inlineStr">
-        <is>
-          <t>Messy Weekend (Sell)</t>
-        </is>
-      </c>
-      <c r="CO1" s="1" t="inlineStr">
-        <is>
-          <t>Magic Bodyfashion (Sell)</t>
-        </is>
-      </c>
-      <c r="CP1" s="1" t="inlineStr">
+      <c r="CV1" s="1" t="inlineStr">
         <is>
           <t>Cras (Sell)</t>
         </is>
       </c>
-      <c r="CQ1" s="1" t="inlineStr">
-        <is>
-          <t>Playboy (Sell)</t>
-        </is>
-      </c>
-      <c r="CR1" s="1" t="inlineStr">
-        <is>
-          <t>Shepherd (Sell)</t>
-        </is>
-      </c>
-      <c r="CS1" s="1" t="inlineStr">
-        <is>
-          <t>ROCKANDBLUE (Sell)</t>
-        </is>
-      </c>
-      <c r="CT1" s="1" t="inlineStr">
-        <is>
-          <t>Neuw (Sell)</t>
-        </is>
-      </c>
-      <c r="CU1" s="1" t="inlineStr">
-        <is>
-          <t>Lyle &amp; Scott (Sell)</t>
-        </is>
-      </c>
-      <c r="CV1" s="1" t="inlineStr">
-        <is>
-          <t>Daily Paper (Sell)</t>
-        </is>
-      </c>
       <c r="CW1" s="1" t="inlineStr">
         <is>
           <t>Nelly (List)</t>
@@ -3823,19 +4155,19 @@
       </c>
       <c r="CY1" s="1" t="inlineStr">
         <is>
+          <t>Pieces (List)</t>
+        </is>
+      </c>
+      <c r="CZ1" s="1" t="inlineStr">
+        <is>
+          <t>Only (List)</t>
+        </is>
+      </c>
+      <c r="DA1" s="1" t="inlineStr">
+        <is>
           <t>New Balance (List)</t>
         </is>
       </c>
-      <c r="CZ1" s="1" t="inlineStr">
-        <is>
-          <t>Pieces (List)</t>
-        </is>
-      </c>
-      <c r="DA1" s="1" t="inlineStr">
-        <is>
-          <t>Only (List)</t>
-        </is>
-      </c>
       <c r="DB1" s="1" t="inlineStr">
         <is>
           <t>Que Sera Sera (List)</t>
@@ -3853,457 +4185,457 @@
       </c>
       <c r="DE1" s="1" t="inlineStr">
         <is>
+          <t>Levi's (List)</t>
+        </is>
+      </c>
+      <c r="DF1" s="1" t="inlineStr">
+        <is>
           <t>True Religion (List)</t>
         </is>
       </c>
-      <c r="DF1" s="1" t="inlineStr">
-        <is>
-          <t>Levi's (List)</t>
-        </is>
-      </c>
       <c r="DG1" s="1" t="inlineStr">
         <is>
+          <t>Selected Men (List)</t>
+        </is>
+      </c>
+      <c r="DH1" s="1" t="inlineStr">
+        <is>
+          <t>Only &amp; Sons (List)</t>
+        </is>
+      </c>
+      <c r="DI1" s="1" t="inlineStr">
+        <is>
           <t>Gina Tricot (List)</t>
         </is>
       </c>
-      <c r="DH1" s="1" t="inlineStr">
-        <is>
-          <t>Selected Men (List)</t>
-        </is>
-      </c>
-      <c r="DI1" s="1" t="inlineStr">
-        <is>
-          <t>Only &amp; Sons (List)</t>
-        </is>
-      </c>
       <c r="DJ1" s="1" t="inlineStr">
         <is>
+          <t>Jack &amp; Jones (List)</t>
+        </is>
+      </c>
+      <c r="DK1" s="1" t="inlineStr">
+        <is>
+          <t>Dr Denim (List)</t>
+        </is>
+      </c>
+      <c r="DL1" s="1" t="inlineStr">
+        <is>
           <t>Nike (List)</t>
         </is>
       </c>
-      <c r="DK1" s="1" t="inlineStr">
-        <is>
-          <t>Jack &amp; Jones (List)</t>
-        </is>
-      </c>
-      <c r="DL1" s="1" t="inlineStr">
-        <is>
-          <t>Dr Denim (List)</t>
-        </is>
-      </c>
       <c r="DM1" s="1" t="inlineStr">
         <is>
+          <t>Malina (List)</t>
+        </is>
+      </c>
+      <c r="DN1" s="1" t="inlineStr">
+        <is>
+          <t>Woodbird (List)</t>
+        </is>
+      </c>
+      <c r="DO1" s="1" t="inlineStr">
+        <is>
+          <t>BECKSÖNDERGAARD (List)</t>
+        </is>
+      </c>
+      <c r="DP1" s="1" t="inlineStr">
+        <is>
+          <t>By Malene Birger (List)</t>
+        </is>
+      </c>
+      <c r="DQ1" s="1" t="inlineStr">
+        <is>
+          <t>The North Face (List)</t>
+        </is>
+      </c>
+      <c r="DR1" s="1" t="inlineStr">
+        <is>
+          <t>Birkenstock (List)</t>
+        </is>
+      </c>
+      <c r="DS1" s="1" t="inlineStr">
+        <is>
+          <t>Samsøe Samsøe (List)</t>
+        </is>
+      </c>
+      <c r="DT1" s="1" t="inlineStr">
+        <is>
+          <t>Polo Ralph Lauren (List)</t>
+        </is>
+      </c>
+      <c r="DU1" s="1" t="inlineStr">
+        <is>
+          <t>Abrand Jeans (List)</t>
+        </is>
+      </c>
+      <c r="DV1" s="1" t="inlineStr">
+        <is>
+          <t>Aim'n (List)</t>
+        </is>
+      </c>
+      <c r="DW1" s="1" t="inlineStr">
+        <is>
+          <t>A.Kjærbede (List)</t>
+        </is>
+      </c>
+      <c r="DX1" s="1" t="inlineStr">
+        <is>
+          <t>Muli Collection (List)</t>
+        </is>
+      </c>
+      <c r="DY1" s="1" t="inlineStr">
+        <is>
           <t>Lois Jeans (List)</t>
         </is>
       </c>
-      <c r="DN1" s="1" t="inlineStr">
-        <is>
-          <t>By Malene Birger (List)</t>
-        </is>
-      </c>
-      <c r="DO1" s="1" t="inlineStr">
-        <is>
-          <t>Malina (List)</t>
-        </is>
-      </c>
-      <c r="DP1" s="1" t="inlineStr">
-        <is>
-          <t>BECKSÖNDERGAARD (List)</t>
-        </is>
-      </c>
-      <c r="DQ1" s="1" t="inlineStr">
-        <is>
-          <t>The North Face (List)</t>
-        </is>
-      </c>
-      <c r="DR1" s="1" t="inlineStr">
-        <is>
-          <t>Woodbird (List)</t>
-        </is>
-      </c>
-      <c r="DS1" s="1" t="inlineStr">
-        <is>
-          <t>Birkenstock (List)</t>
-        </is>
-      </c>
-      <c r="DT1" s="1" t="inlineStr">
+      <c r="DZ1" s="1" t="inlineStr">
+        <is>
+          <t>Calvin Klein Underwear (List)</t>
+        </is>
+      </c>
+      <c r="EA1" s="1" t="inlineStr">
         <is>
           <t>Carhartt WIP (List)</t>
         </is>
       </c>
-      <c r="DU1" s="1" t="inlineStr">
-        <is>
-          <t>Samsøe Samsøe (List)</t>
-        </is>
-      </c>
-      <c r="DV1" s="1" t="inlineStr">
-        <is>
-          <t>A.Kjærbede (List)</t>
-        </is>
-      </c>
-      <c r="DW1" s="1" t="inlineStr">
-        <is>
-          <t>Muli Collection (List)</t>
-        </is>
-      </c>
-      <c r="DX1" s="1" t="inlineStr">
+      <c r="EB1" s="1" t="inlineStr">
+        <is>
+          <t>UGG (List)</t>
+        </is>
+      </c>
+      <c r="EC1" s="1" t="inlineStr">
+        <is>
+          <t>Asics (List)</t>
+        </is>
+      </c>
+      <c r="ED1" s="1" t="inlineStr">
+        <is>
+          <t>Converse (List)</t>
+        </is>
+      </c>
+      <c r="EE1" s="1" t="inlineStr">
+        <is>
+          <t>Les Deux (List)</t>
+        </is>
+      </c>
+      <c r="EF1" s="1" t="inlineStr">
+        <is>
+          <t>Sneaky Steve (List)</t>
+        </is>
+      </c>
+      <c r="EG1" s="1" t="inlineStr">
+        <is>
+          <t>Gant (List)</t>
+        </is>
+      </c>
+      <c r="EH1" s="1" t="inlineStr">
+        <is>
+          <t>Diesel (List)</t>
+        </is>
+      </c>
+      <c r="EI1" s="1" t="inlineStr">
+        <is>
+          <t>Hunter (List)</t>
+        </is>
+      </c>
+      <c r="EJ1" s="1" t="inlineStr">
+        <is>
+          <t>DORINA (List)</t>
+        </is>
+      </c>
+      <c r="EK1" s="1" t="inlineStr">
+        <is>
+          <t>Puma (List)</t>
+        </is>
+      </c>
+      <c r="EL1" s="1" t="inlineStr">
         <is>
           <t>Pavement (List)</t>
         </is>
       </c>
-      <c r="DY1" s="1" t="inlineStr">
-        <is>
-          <t>Aim'n (List)</t>
-        </is>
-      </c>
-      <c r="DZ1" s="1" t="inlineStr">
-        <is>
-          <t>Polo Ralph Lauren (List)</t>
-        </is>
-      </c>
-      <c r="EA1" s="1" t="inlineStr">
-        <is>
-          <t>UGG (List)</t>
-        </is>
-      </c>
-      <c r="EB1" s="1" t="inlineStr">
-        <is>
-          <t>Converse (List)</t>
-        </is>
-      </c>
-      <c r="EC1" s="1" t="inlineStr">
-        <is>
-          <t>Abrand Jeans (List)</t>
-        </is>
-      </c>
-      <c r="ED1" s="1" t="inlineStr">
-        <is>
-          <t>Les Deux (List)</t>
-        </is>
-      </c>
-      <c r="EE1" s="1" t="inlineStr">
-        <is>
-          <t>Sneaky Steve (List)</t>
-        </is>
-      </c>
-      <c r="EF1" s="1" t="inlineStr">
-        <is>
-          <t>Asics (List)</t>
-        </is>
-      </c>
-      <c r="EG1" s="1" t="inlineStr">
-        <is>
-          <t>Calvin Klein Underwear (List)</t>
-        </is>
-      </c>
-      <c r="EH1" s="1" t="inlineStr">
+      <c r="EM1" s="1" t="inlineStr">
+        <is>
+          <t>Inuikii (List)</t>
+        </is>
+      </c>
+      <c r="EN1" s="1" t="inlineStr">
+        <is>
+          <t>One Teaspoon (List)</t>
+        </is>
+      </c>
+      <c r="EO1" s="1" t="inlineStr">
         <is>
           <t>Hunkemöller (List)</t>
         </is>
       </c>
-      <c r="EI1" s="1" t="inlineStr">
+      <c r="EP1" s="1" t="inlineStr">
+        <is>
+          <t>Havaianas (List)</t>
+        </is>
+      </c>
+      <c r="EQ1" s="1" t="inlineStr">
+        <is>
+          <t>ATP ATELIER (List)</t>
+        </is>
+      </c>
+      <c r="ER1" s="1" t="inlineStr">
+        <is>
+          <t>Le Specs (List)</t>
+        </is>
+      </c>
+      <c r="ES1" s="1" t="inlineStr">
+        <is>
+          <t>Solid (List)</t>
+        </is>
+      </c>
+      <c r="ET1" s="1" t="inlineStr">
+        <is>
+          <t>Mads Nørgaard (List)</t>
+        </is>
+      </c>
+      <c r="EU1" s="1" t="inlineStr">
+        <is>
+          <t>Bye Bra (List)</t>
+        </is>
+      </c>
+      <c r="EV1" s="1" t="inlineStr">
         <is>
           <t>Ciszere (List)</t>
         </is>
       </c>
-      <c r="EJ1" s="1" t="inlineStr">
-        <is>
-          <t>Inuikii (List)</t>
-        </is>
-      </c>
-      <c r="EK1" s="1" t="inlineStr">
-        <is>
-          <t>One Teaspoon (List)</t>
-        </is>
-      </c>
-      <c r="EL1" s="1" t="inlineStr">
-        <is>
-          <t>Hunter (List)</t>
-        </is>
-      </c>
-      <c r="EM1" s="1" t="inlineStr">
-        <is>
-          <t>DORINA (List)</t>
-        </is>
-      </c>
-      <c r="EN1" s="1" t="inlineStr">
-        <is>
-          <t>Diesel (List)</t>
-        </is>
-      </c>
-      <c r="EO1" s="1" t="inlineStr">
-        <is>
-          <t>Gant (List)</t>
-        </is>
-      </c>
-      <c r="EP1" s="1" t="inlineStr">
-        <is>
-          <t>Puma (List)</t>
-        </is>
-      </c>
-      <c r="EQ1" s="1" t="inlineStr">
+      <c r="EW1" s="1" t="inlineStr">
+        <is>
+          <t>Colmar (List)</t>
+        </is>
+      </c>
+      <c r="EX1" s="1" t="inlineStr">
         <is>
           <t>MONO (List)</t>
         </is>
       </c>
-      <c r="ER1" s="1" t="inlineStr">
-        <is>
-          <t>Colmar (List)</t>
-        </is>
-      </c>
-      <c r="ES1" s="1" t="inlineStr">
-        <is>
-          <t>Solid (List)</t>
-        </is>
-      </c>
-      <c r="ET1" s="1" t="inlineStr">
-        <is>
-          <t>ATP ATELIER (List)</t>
-        </is>
-      </c>
-      <c r="EU1" s="1" t="inlineStr">
+      <c r="EY1" s="1" t="inlineStr">
+        <is>
+          <t>Corlin Eyewear (List)</t>
+        </is>
+      </c>
+      <c r="EZ1" s="1" t="inlineStr">
+        <is>
+          <t>ANNARR (List)</t>
+        </is>
+      </c>
+      <c r="FA1" s="1" t="inlineStr">
+        <is>
+          <t>Messy Weekend (List)</t>
+        </is>
+      </c>
+      <c r="FB1" s="1" t="inlineStr">
+        <is>
+          <t>Pilgrim (List)</t>
+        </is>
+      </c>
+      <c r="FC1" s="1" t="inlineStr">
+        <is>
+          <t>Casual Friday (List)</t>
+        </is>
+      </c>
+      <c r="FD1" s="1" t="inlineStr">
+        <is>
+          <t>Calvin Klein Jeans (List)</t>
+        </is>
+      </c>
+      <c r="FE1" s="1" t="inlineStr">
+        <is>
+          <t>Bluebella (List)</t>
+        </is>
+      </c>
+      <c r="FF1" s="1" t="inlineStr">
+        <is>
+          <t>Columbia (List)</t>
+        </is>
+      </c>
+      <c r="FG1" s="1" t="inlineStr">
+        <is>
+          <t>STICKYBESTIE (List)</t>
+        </is>
+      </c>
+      <c r="FH1" s="1" t="inlineStr">
+        <is>
+          <t>Björn Borg (List)</t>
+        </is>
+      </c>
+      <c r="FI1" s="1" t="inlineStr">
+        <is>
+          <t>Michael Kors (List)</t>
+        </is>
+      </c>
+      <c r="FJ1" s="1" t="inlineStr">
+        <is>
+          <t>Selected Femme (List)</t>
+        </is>
+      </c>
+      <c r="FK1" s="1" t="inlineStr">
+        <is>
+          <t>Juicy Couture (List)</t>
+        </is>
+      </c>
+      <c r="FL1" s="1" t="inlineStr">
+        <is>
+          <t>Brand Island (List)</t>
+        </is>
+      </c>
+      <c r="FM1" s="1" t="inlineStr">
         <is>
           <t>Rains (List)</t>
         </is>
       </c>
-      <c r="EV1" s="1" t="inlineStr">
-        <is>
-          <t>Bye Bra (List)</t>
-        </is>
-      </c>
-      <c r="EW1" s="1" t="inlineStr">
-        <is>
-          <t>Pilgrim (List)</t>
-        </is>
-      </c>
-      <c r="EX1" s="1" t="inlineStr">
-        <is>
-          <t>Mads Nørgaard (List)</t>
-        </is>
-      </c>
-      <c r="EY1" s="1" t="inlineStr">
-        <is>
-          <t>Havaianas (List)</t>
-        </is>
-      </c>
-      <c r="EZ1" s="1" t="inlineStr">
-        <is>
-          <t>Brand Island (List)</t>
-        </is>
-      </c>
-      <c r="FA1" s="1" t="inlineStr">
-        <is>
-          <t>Le Specs (List)</t>
-        </is>
-      </c>
-      <c r="FB1" s="1" t="inlineStr">
-        <is>
-          <t>Casual Friday (List)</t>
-        </is>
-      </c>
-      <c r="FC1" s="1" t="inlineStr">
-        <is>
-          <t>STICKYBESTIE (List)</t>
-        </is>
-      </c>
-      <c r="FD1" s="1" t="inlineStr">
-        <is>
-          <t>Selected Femme (List)</t>
-        </is>
-      </c>
-      <c r="FE1" s="1" t="inlineStr">
+      <c r="FN1" s="1" t="inlineStr">
+        <is>
+          <t>Spanx (List)</t>
+        </is>
+      </c>
+      <c r="FO1" s="1" t="inlineStr">
+        <is>
+          <t>JDY (List)</t>
+        </is>
+      </c>
+      <c r="FP1" s="1" t="inlineStr">
+        <is>
+          <t>By Billgren (List)</t>
+        </is>
+      </c>
+      <c r="FQ1" s="1" t="inlineStr">
+        <is>
+          <t>IRO (List)</t>
+        </is>
+      </c>
+      <c r="FR1" s="1" t="inlineStr">
+        <is>
+          <t>Moon Boot (List)</t>
+        </is>
+      </c>
+      <c r="FS1" s="1" t="inlineStr">
+        <is>
+          <t>Scholl (List)</t>
+        </is>
+      </c>
+      <c r="FT1" s="1" t="inlineStr">
+        <is>
+          <t>Neuw (List)</t>
+        </is>
+      </c>
+      <c r="FU1" s="1" t="inlineStr">
+        <is>
+          <t>ROCKANDBLUE (List)</t>
+        </is>
+      </c>
+      <c r="FV1" s="1" t="inlineStr">
+        <is>
+          <t>Dockers (List)</t>
+        </is>
+      </c>
+      <c r="FW1" s="1" t="inlineStr">
+        <is>
+          <t>J Lindeberg (List)</t>
+        </is>
+      </c>
+      <c r="FX1" s="1" t="inlineStr">
+        <is>
+          <t>Mercer Amsterdam (List)</t>
+        </is>
+      </c>
+      <c r="FY1" s="1" t="inlineStr">
+        <is>
+          <t>Lyle &amp; Scott (List)</t>
+        </is>
+      </c>
+      <c r="FZ1" s="1" t="inlineStr">
+        <is>
+          <t>Shepherd (List)</t>
+        </is>
+      </c>
+      <c r="GA1" s="1" t="inlineStr">
+        <is>
+          <t>Marc Jacobs (List)</t>
+        </is>
+      </c>
+      <c r="GB1" s="1" t="inlineStr">
+        <is>
+          <t>VANS (List)</t>
+        </is>
+      </c>
+      <c r="GC1" s="1" t="inlineStr">
+        <is>
+          <t>Timberland (List)</t>
+        </is>
+      </c>
+      <c r="GD1" s="1" t="inlineStr">
+        <is>
+          <t>GABBA (List)</t>
+        </is>
+      </c>
+      <c r="GE1" s="1" t="inlineStr">
+        <is>
+          <t>Playboy (List)</t>
+        </is>
+      </c>
+      <c r="GF1" s="1" t="inlineStr">
+        <is>
+          <t>Daily Paper (List)</t>
+        </is>
+      </c>
+      <c r="GG1" s="1" t="inlineStr">
+        <is>
+          <t>Magic Bodyfashion (List)</t>
+        </is>
+      </c>
+      <c r="GH1" s="1" t="inlineStr">
+        <is>
+          <t>Tommy Jeans (List)</t>
+        </is>
+      </c>
+      <c r="GI1" s="1" t="inlineStr">
         <is>
           <t>OBJECT (List)</t>
         </is>
       </c>
-      <c r="FF1" s="1" t="inlineStr">
-        <is>
-          <t>Bluebella (List)</t>
-        </is>
-      </c>
-      <c r="FG1" s="1" t="inlineStr">
-        <is>
-          <t>Björn Borg (List)</t>
-        </is>
-      </c>
-      <c r="FH1" s="1" t="inlineStr">
-        <is>
-          <t>ANNARR (List)</t>
-        </is>
-      </c>
-      <c r="FI1" s="1" t="inlineStr">
-        <is>
-          <t>By Billgren (List)</t>
-        </is>
-      </c>
-      <c r="FJ1" s="1" t="inlineStr">
-        <is>
-          <t>JDY (List)</t>
-        </is>
-      </c>
-      <c r="FK1" s="1" t="inlineStr">
-        <is>
-          <t>Spanx (List)</t>
-        </is>
-      </c>
-      <c r="FL1" s="1" t="inlineStr">
-        <is>
-          <t>Juicy Couture (List)</t>
-        </is>
-      </c>
-      <c r="FM1" s="1" t="inlineStr">
-        <is>
-          <t>Michael Kors (List)</t>
-        </is>
-      </c>
-      <c r="FN1" s="1" t="inlineStr">
-        <is>
-          <t>IRO (List)</t>
-        </is>
-      </c>
-      <c r="FO1" s="1" t="inlineStr">
-        <is>
-          <t>VANS (List)</t>
-        </is>
-      </c>
-      <c r="FP1" s="1" t="inlineStr">
-        <is>
-          <t>Dockers (List)</t>
-        </is>
-      </c>
-      <c r="FQ1" s="1" t="inlineStr">
+      <c r="GJ1" s="1" t="inlineStr">
         <is>
           <t>OAS (List)</t>
         </is>
       </c>
-      <c r="FR1" s="1" t="inlineStr">
-        <is>
-          <t>Marc Jacobs (List)</t>
-        </is>
-      </c>
-      <c r="FS1" s="1" t="inlineStr">
-        <is>
-          <t>Timberland (List)</t>
-        </is>
-      </c>
-      <c r="FT1" s="1" t="inlineStr">
-        <is>
-          <t>Corlin Eyewear (List)</t>
-        </is>
-      </c>
-      <c r="FU1" s="1" t="inlineStr">
+      <c r="GK1" s="1" t="inlineStr">
+        <is>
+          <t>Dickies (List)</t>
+        </is>
+      </c>
+      <c r="GL1" s="1" t="inlineStr">
+        <is>
+          <t>JJXX (List)</t>
+        </is>
+      </c>
+      <c r="GM1" s="1" t="inlineStr">
+        <is>
+          <t>Le Bonnet (List)</t>
+        </is>
+      </c>
+      <c r="GN1" s="1" t="inlineStr">
         <is>
           <t>DAY ET (List)</t>
         </is>
       </c>
-      <c r="FV1" s="1" t="inlineStr">
-        <is>
-          <t>J Lindeberg (List)</t>
-        </is>
-      </c>
-      <c r="FW1" s="1" t="inlineStr">
+      <c r="GO1" s="1" t="inlineStr">
+        <is>
+          <t>Teva (List)</t>
+        </is>
+      </c>
+      <c r="GP1" s="1" t="inlineStr">
         <is>
           <t>Bread &amp; Boxers (List)</t>
         </is>
       </c>
-      <c r="FX1" s="1" t="inlineStr">
-        <is>
-          <t>Le Bonnet (List)</t>
-        </is>
-      </c>
-      <c r="FY1" s="1" t="inlineStr">
-        <is>
-          <t>Moon Boot (List)</t>
-        </is>
-      </c>
-      <c r="FZ1" s="1" t="inlineStr">
-        <is>
-          <t>Tommy Jeans (List)</t>
-        </is>
-      </c>
-      <c r="GA1" s="1" t="inlineStr">
-        <is>
-          <t>Columbia (List)</t>
-        </is>
-      </c>
-      <c r="GB1" s="1" t="inlineStr">
-        <is>
-          <t>Dickies (List)</t>
-        </is>
-      </c>
-      <c r="GC1" s="1" t="inlineStr">
-        <is>
-          <t>GABBA (List)</t>
-        </is>
-      </c>
-      <c r="GD1" s="1" t="inlineStr">
-        <is>
-          <t>Mercer Amsterdam (List)</t>
-        </is>
-      </c>
-      <c r="GE1" s="1" t="inlineStr">
-        <is>
-          <t>JJXX (List)</t>
-        </is>
-      </c>
-      <c r="GF1" s="1" t="inlineStr">
-        <is>
-          <t>Calvin Klein Jeans (List)</t>
-        </is>
-      </c>
-      <c r="GG1" s="1" t="inlineStr">
-        <is>
-          <t>Teva (List)</t>
-        </is>
-      </c>
-      <c r="GH1" s="1" t="inlineStr">
-        <is>
-          <t>Scholl (List)</t>
-        </is>
-      </c>
-      <c r="GI1" s="1" t="inlineStr">
-        <is>
-          <t>Messy Weekend (List)</t>
-        </is>
-      </c>
-      <c r="GJ1" s="1" t="inlineStr">
-        <is>
-          <t>Magic Bodyfashion (List)</t>
-        </is>
-      </c>
-      <c r="GK1" s="1" t="inlineStr">
+      <c r="GQ1" s="1" t="inlineStr">
         <is>
           <t>Cras (List)</t>
-        </is>
-      </c>
-      <c r="GL1" s="1" t="inlineStr">
-        <is>
-          <t>Playboy (List)</t>
-        </is>
-      </c>
-      <c r="GM1" s="1" t="inlineStr">
-        <is>
-          <t>Shepherd (List)</t>
-        </is>
-      </c>
-      <c r="GN1" s="1" t="inlineStr">
-        <is>
-          <t>ROCKANDBLUE (List)</t>
-        </is>
-      </c>
-      <c r="GO1" s="1" t="inlineStr">
-        <is>
-          <t>Neuw (List)</t>
-        </is>
-      </c>
-      <c r="GP1" s="1" t="inlineStr">
-        <is>
-          <t>Lyle &amp; Scott (List)</t>
-        </is>
-      </c>
-      <c r="GQ1" s="1" t="inlineStr">
-        <is>
-          <t>Daily Paper (List)</t>
         </is>
       </c>
     </row>
@@ -4921,13 +5253,13 @@
         <v>252617</v>
       </c>
       <c r="D3" t="n">
+        <v>120751</v>
+      </c>
+      <c r="E3" t="n">
+        <v>134394</v>
+      </c>
+      <c r="F3" t="n">
         <v>290506</v>
-      </c>
-      <c r="E3" t="n">
-        <v>120751</v>
-      </c>
-      <c r="F3" t="n">
-        <v>134394</v>
       </c>
       <c r="G3" t="n">
         <v>169070</v>
@@ -4939,253 +5271,253 @@
         <v>101891</v>
       </c>
       <c r="J3" t="n">
+        <v>82521</v>
+      </c>
+      <c r="K3" t="n">
         <v>81262</v>
       </c>
-      <c r="K3" t="n">
-        <v>82521</v>
-      </c>
       <c r="L3" t="n">
+        <v>89108</v>
+      </c>
+      <c r="M3" t="n">
+        <v>70490</v>
+      </c>
+      <c r="N3" t="n">
         <v>34987</v>
       </c>
-      <c r="M3" t="n">
-        <v>89108</v>
-      </c>
-      <c r="N3" t="n">
-        <v>70490</v>
-      </c>
       <c r="O3" t="n">
+        <v>61938</v>
+      </c>
+      <c r="P3" t="n">
+        <v>30065</v>
+      </c>
+      <c r="Q3" t="n">
         <v>45000</v>
       </c>
-      <c r="P3" t="n">
-        <v>61938</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>30065</v>
-      </c>
       <c r="R3" t="n">
-        <v>10695</v>
+        <v>21791</v>
       </c>
       <c r="S3" t="n">
+        <v>61743</v>
+      </c>
+      <c r="T3" t="n">
+        <v>7731</v>
+      </c>
+      <c r="U3" t="n">
         <v>28381</v>
-      </c>
-      <c r="T3" t="n">
-        <v>21791</v>
-      </c>
-      <c r="U3" t="n">
-        <v>7731</v>
       </c>
       <c r="V3" t="n">
         <v>9035</v>
       </c>
       <c r="W3" t="n">
-        <v>61743</v>
+        <v>29537</v>
       </c>
       <c r="X3" t="n">
-        <v>29537</v>
+        <v>52481</v>
       </c>
       <c r="Y3" t="n">
+        <v>37938</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>14985</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>2195</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>6769</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>20954</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>10695</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>11536</v>
+      </c>
+      <c r="AF3" t="n">
         <v>14092</v>
       </c>
-      <c r="Z3" t="n">
-        <v>52481</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>6769</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>20954</v>
-      </c>
-      <c r="AC3" t="n">
+      <c r="AG3" t="n">
+        <v>10235</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>2118</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>5237</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>20446</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>17490</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>4198</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>7192</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>9071</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>5974</v>
+      </c>
+      <c r="AQ3" t="n">
         <v>11693</v>
       </c>
-      <c r="AD3" t="n">
-        <v>2195</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>37938</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>10235</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>5237</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>14985</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>20446</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>17490</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>2118</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>11536</v>
-      </c>
-      <c r="AM3" t="n">
+      <c r="AR3" t="n">
+        <v>7597</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>12442</v>
+      </c>
+      <c r="AT3" t="n">
         <v>8105</v>
       </c>
-      <c r="AN3" t="n">
-        <v>14429</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>7597</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>12442</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>7192</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>9071</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>4198</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>0</v>
-      </c>
       <c r="AU3" t="n">
-        <v>5974</v>
+        <v>4280</v>
       </c>
       <c r="AV3" t="n">
-        <v>3499</v>
+        <v>5199</v>
       </c>
       <c r="AW3" t="n">
-        <v>4799</v>
+        <v>0</v>
       </c>
       <c r="AX3" t="n">
         <v>5396</v>
       </c>
       <c r="AY3" t="n">
-        <v>5199</v>
+        <v>12089</v>
       </c>
       <c r="AZ3" t="n">
+        <v>1595</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>14429</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>4799</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>3499</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>2674</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>629</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>549</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>568</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>349</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>496</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP3" t="n">
+        <v>598</v>
+      </c>
+      <c r="BQ3" t="n">
+        <v>988</v>
+      </c>
+      <c r="BR3" t="n">
         <v>2098</v>
       </c>
-      <c r="BA3" t="n">
-        <v>1595</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>2674</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>12089</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>4280</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>988</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>629</v>
-      </c>
-      <c r="BH3" t="n">
-        <v>349</v>
-      </c>
-      <c r="BI3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ3" t="n">
+      <c r="BS3" t="n">
+        <v>499</v>
+      </c>
+      <c r="BT3" t="n">
+        <v>314</v>
+      </c>
+      <c r="BU3" t="n">
         <v>299</v>
       </c>
-      <c r="BK3" t="n">
-        <v>568</v>
-      </c>
-      <c r="BL3" t="n">
-        <v>496</v>
-      </c>
-      <c r="BM3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN3" t="n">
+      <c r="BV3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW3" t="n">
+        <v>2539</v>
+      </c>
+      <c r="BX3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN3" t="n">
         <v>299</v>
-      </c>
-      <c r="BO3" t="n">
-        <v>314</v>
-      </c>
-      <c r="BP3" t="n">
-        <v>499</v>
-      </c>
-      <c r="BQ3" t="n">
-        <v>598</v>
-      </c>
-      <c r="BR3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CC3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD3" t="n">
-        <v>2539</v>
-      </c>
-      <c r="CE3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CJ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CK3" t="n">
-        <v>549</v>
-      </c>
-      <c r="CL3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN3" t="n">
-        <v>0</v>
       </c>
       <c r="CO3" t="n">
         <v>0</v>
@@ -5218,13 +5550,13 @@
         <v>260992</v>
       </c>
       <c r="CY3" t="n">
+        <v>150580</v>
+      </c>
+      <c r="CZ3" t="n">
+        <v>148222</v>
+      </c>
+      <c r="DA3" t="n">
         <v>297828</v>
-      </c>
-      <c r="CZ3" t="n">
-        <v>150580</v>
-      </c>
-      <c r="DA3" t="n">
-        <v>148222</v>
       </c>
       <c r="DB3" t="n">
         <v>172450</v>
@@ -5236,253 +5568,253 @@
         <v>115977</v>
       </c>
       <c r="DE3" t="n">
+        <v>87401</v>
+      </c>
+      <c r="DF3" t="n">
         <v>98042</v>
       </c>
-      <c r="DF3" t="n">
-        <v>87401</v>
-      </c>
       <c r="DG3" t="n">
+        <v>91109</v>
+      </c>
+      <c r="DH3" t="n">
+        <v>74972</v>
+      </c>
+      <c r="DI3" t="n">
         <v>38267</v>
       </c>
-      <c r="DH3" t="n">
-        <v>91109</v>
-      </c>
-      <c r="DI3" t="n">
-        <v>74972</v>
-      </c>
       <c r="DJ3" t="n">
+        <v>64573</v>
+      </c>
+      <c r="DK3" t="n">
+        <v>33305</v>
+      </c>
+      <c r="DL3" t="n">
         <v>45000</v>
       </c>
-      <c r="DK3" t="n">
-        <v>64573</v>
-      </c>
-      <c r="DL3" t="n">
-        <v>33305</v>
-      </c>
       <c r="DM3" t="n">
-        <v>10695</v>
+        <v>21791</v>
       </c>
       <c r="DN3" t="n">
+        <v>65143</v>
+      </c>
+      <c r="DO3" t="n">
+        <v>8921</v>
+      </c>
+      <c r="DP3" t="n">
         <v>28381</v>
-      </c>
-      <c r="DO3" t="n">
-        <v>21791</v>
-      </c>
-      <c r="DP3" t="n">
-        <v>8921</v>
       </c>
       <c r="DQ3" t="n">
         <v>10195</v>
       </c>
       <c r="DR3" t="n">
-        <v>65143</v>
+        <v>29537</v>
       </c>
       <c r="DS3" t="n">
-        <v>29537</v>
+        <v>52871</v>
       </c>
       <c r="DT3" t="n">
+        <v>39616</v>
+      </c>
+      <c r="DU3" t="n">
+        <v>14985</v>
+      </c>
+      <c r="DV3" t="n">
+        <v>2195</v>
+      </c>
+      <c r="DW3" t="n">
+        <v>7329</v>
+      </c>
+      <c r="DX3" t="n">
+        <v>20954</v>
+      </c>
+      <c r="DY3" t="n">
+        <v>10695</v>
+      </c>
+      <c r="DZ3" t="n">
+        <v>11536</v>
+      </c>
+      <c r="EA3" t="n">
         <v>14092</v>
       </c>
-      <c r="DU3" t="n">
-        <v>52871</v>
-      </c>
-      <c r="DV3" t="n">
-        <v>7329</v>
-      </c>
-      <c r="DW3" t="n">
-        <v>20954</v>
-      </c>
-      <c r="DX3" t="n">
+      <c r="EB3" t="n">
+        <v>10895</v>
+      </c>
+      <c r="EC3" t="n">
+        <v>2798</v>
+      </c>
+      <c r="ED3" t="n">
+        <v>5697</v>
+      </c>
+      <c r="EE3" t="n">
+        <v>21886</v>
+      </c>
+      <c r="EF3" t="n">
+        <v>17490</v>
+      </c>
+      <c r="EG3" t="n">
+        <v>0</v>
+      </c>
+      <c r="EH3" t="n">
+        <v>4198</v>
+      </c>
+      <c r="EI3" t="n">
+        <v>7192</v>
+      </c>
+      <c r="EJ3" t="n">
+        <v>9446</v>
+      </c>
+      <c r="EK3" t="n">
+        <v>7895</v>
+      </c>
+      <c r="EL3" t="n">
         <v>11693</v>
       </c>
-      <c r="DY3" t="n">
-        <v>2195</v>
-      </c>
-      <c r="DZ3" t="n">
-        <v>39616</v>
-      </c>
-      <c r="EA3" t="n">
-        <v>10895</v>
-      </c>
-      <c r="EB3" t="n">
-        <v>5697</v>
-      </c>
-      <c r="EC3" t="n">
-        <v>14985</v>
-      </c>
-      <c r="ED3" t="n">
-        <v>21886</v>
-      </c>
-      <c r="EE3" t="n">
-        <v>17490</v>
-      </c>
-      <c r="EF3" t="n">
-        <v>2798</v>
-      </c>
-      <c r="EG3" t="n">
-        <v>11536</v>
-      </c>
-      <c r="EH3" t="n">
+      <c r="EM3" t="n">
+        <v>7597</v>
+      </c>
+      <c r="EN3" t="n">
+        <v>15037</v>
+      </c>
+      <c r="EO3" t="n">
         <v>9931</v>
       </c>
-      <c r="EI3" t="n">
-        <v>14789</v>
-      </c>
-      <c r="EJ3" t="n">
-        <v>7597</v>
-      </c>
-      <c r="EK3" t="n">
-        <v>15037</v>
-      </c>
-      <c r="EL3" t="n">
-        <v>7192</v>
-      </c>
-      <c r="EM3" t="n">
-        <v>9446</v>
-      </c>
-      <c r="EN3" t="n">
-        <v>4198</v>
-      </c>
-      <c r="EO3" t="n">
-        <v>0</v>
-      </c>
       <c r="EP3" t="n">
-        <v>7895</v>
+        <v>4280</v>
       </c>
       <c r="EQ3" t="n">
-        <v>3499</v>
+        <v>5199</v>
       </c>
       <c r="ER3" t="n">
-        <v>4799</v>
+        <v>0</v>
       </c>
       <c r="ES3" t="n">
         <v>6198</v>
       </c>
       <c r="ET3" t="n">
-        <v>5199</v>
+        <v>12089</v>
       </c>
       <c r="EU3" t="n">
+        <v>1595</v>
+      </c>
+      <c r="EV3" t="n">
+        <v>14789</v>
+      </c>
+      <c r="EW3" t="n">
+        <v>4799</v>
+      </c>
+      <c r="EX3" t="n">
+        <v>3499</v>
+      </c>
+      <c r="EY3" t="n">
+        <v>0</v>
+      </c>
+      <c r="EZ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB3" t="n">
+        <v>2674</v>
+      </c>
+      <c r="FC3" t="n">
+        <v>899</v>
+      </c>
+      <c r="FD3" t="n">
+        <v>1099</v>
+      </c>
+      <c r="FE3" t="n">
+        <v>1138</v>
+      </c>
+      <c r="FF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG3" t="n">
+        <v>349</v>
+      </c>
+      <c r="FH3" t="n">
+        <v>496</v>
+      </c>
+      <c r="FI3" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="FK3" t="n">
+        <v>1198</v>
+      </c>
+      <c r="FL3" t="n">
+        <v>1898</v>
+      </c>
+      <c r="FM3" t="n">
         <v>2098</v>
       </c>
-      <c r="EV3" t="n">
-        <v>1595</v>
-      </c>
-      <c r="EW3" t="n">
-        <v>2674</v>
-      </c>
-      <c r="EX3" t="n">
-        <v>12089</v>
-      </c>
-      <c r="EY3" t="n">
-        <v>4280</v>
-      </c>
-      <c r="EZ3" t="n">
-        <v>1898</v>
-      </c>
-      <c r="FA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="FB3" t="n">
-        <v>899</v>
-      </c>
-      <c r="FC3" t="n">
-        <v>349</v>
-      </c>
-      <c r="FD3" t="n">
-        <v>0</v>
-      </c>
-      <c r="FE3" t="n">
+      <c r="FN3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="FO3" t="n">
+        <v>629</v>
+      </c>
+      <c r="FP3" t="n">
+        <v>499</v>
+      </c>
+      <c r="FQ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="FR3" t="n">
+        <v>2539</v>
+      </c>
+      <c r="FS3" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT3" t="n">
+        <v>0</v>
+      </c>
+      <c r="FU3" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV3" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW3" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX3" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY3" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GH3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GI3" t="n">
         <v>600</v>
-      </c>
-      <c r="FF3" t="n">
-        <v>1138</v>
-      </c>
-      <c r="FG3" t="n">
-        <v>496</v>
-      </c>
-      <c r="FH3" t="n">
-        <v>0</v>
-      </c>
-      <c r="FI3" t="n">
-        <v>499</v>
-      </c>
-      <c r="FJ3" t="n">
-        <v>629</v>
-      </c>
-      <c r="FK3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="FL3" t="n">
-        <v>1198</v>
-      </c>
-      <c r="FM3" t="n">
-        <v>0</v>
-      </c>
-      <c r="FN3" t="n">
-        <v>0</v>
-      </c>
-      <c r="FO3" t="n">
-        <v>0</v>
-      </c>
-      <c r="FP3" t="n">
-        <v>0</v>
-      </c>
-      <c r="FQ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="FR3" t="n">
-        <v>0</v>
-      </c>
-      <c r="FS3" t="n">
-        <v>0</v>
-      </c>
-      <c r="FT3" t="n">
-        <v>0</v>
-      </c>
-      <c r="FU3" t="n">
-        <v>0</v>
-      </c>
-      <c r="FV3" t="n">
-        <v>0</v>
-      </c>
-      <c r="FW3" t="n">
-        <v>0</v>
-      </c>
-      <c r="FX3" t="n">
-        <v>0</v>
-      </c>
-      <c r="FY3" t="n">
-        <v>2539</v>
-      </c>
-      <c r="FZ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="GA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="GB3" t="n">
-        <v>0</v>
-      </c>
-      <c r="GC3" t="n">
-        <v>0</v>
-      </c>
-      <c r="GD3" t="n">
-        <v>0</v>
-      </c>
-      <c r="GE3" t="n">
-        <v>0</v>
-      </c>
-      <c r="GF3" t="n">
-        <v>1099</v>
-      </c>
-      <c r="GG3" t="n">
-        <v>0</v>
-      </c>
-      <c r="GH3" t="n">
-        <v>0</v>
-      </c>
-      <c r="GI3" t="n">
-        <v>0</v>
       </c>
       <c r="GJ3" t="n">
         <v>0</v>
@@ -5522,13 +5854,13 @@
         <v>279956</v>
       </c>
       <c r="D4" t="n">
+        <v>119449</v>
+      </c>
+      <c r="E4" t="n">
+        <v>172659</v>
+      </c>
+      <c r="F4" t="n">
         <v>417767</v>
-      </c>
-      <c r="E4" t="n">
-        <v>119449</v>
-      </c>
-      <c r="F4" t="n">
-        <v>172659</v>
       </c>
       <c r="G4" t="n">
         <v>609532</v>
@@ -5540,262 +5872,262 @@
         <v>117515</v>
       </c>
       <c r="J4" t="n">
+        <v>84129</v>
+      </c>
+      <c r="K4" t="n">
         <v>46286</v>
       </c>
-      <c r="K4" t="n">
-        <v>84129</v>
-      </c>
       <c r="L4" t="n">
+        <v>60404</v>
+      </c>
+      <c r="M4" t="n">
+        <v>62064</v>
+      </c>
+      <c r="N4" t="n">
         <v>25843</v>
       </c>
-      <c r="M4" t="n">
-        <v>60404</v>
-      </c>
-      <c r="N4" t="n">
-        <v>62064</v>
-      </c>
       <c r="O4" t="n">
+        <v>30801</v>
+      </c>
+      <c r="P4" t="n">
+        <v>32641</v>
+      </c>
+      <c r="Q4" t="n">
         <v>45361</v>
       </c>
-      <c r="P4" t="n">
-        <v>30801</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>32641</v>
-      </c>
       <c r="R4" t="n">
-        <v>33785</v>
+        <v>8445</v>
       </c>
       <c r="S4" t="n">
+        <v>33115</v>
+      </c>
+      <c r="T4" t="n">
+        <v>8616</v>
+      </c>
+      <c r="U4" t="n">
         <v>24484</v>
-      </c>
-      <c r="T4" t="n">
-        <v>8445</v>
-      </c>
-      <c r="U4" t="n">
-        <v>8616</v>
       </c>
       <c r="V4" t="n">
         <v>19127</v>
       </c>
       <c r="W4" t="n">
-        <v>33115</v>
+        <v>13692</v>
       </c>
       <c r="X4" t="n">
-        <v>13692</v>
+        <v>23863</v>
       </c>
       <c r="Y4" t="n">
+        <v>26689</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>17982</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>5295</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>16751</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>15111</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>33785</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>8421</v>
+      </c>
+      <c r="AF4" t="n">
         <v>15894</v>
       </c>
-      <c r="Z4" t="n">
-        <v>23863</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>16751</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>15111</v>
-      </c>
-      <c r="AC4" t="n">
+      <c r="AG4" t="n">
+        <v>12173</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>2038</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>9447</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>12521</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>8395</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>6396</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>-5698</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>4039</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>3604</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>-1437</v>
+      </c>
+      <c r="AQ4" t="n">
         <v>9803</v>
       </c>
-      <c r="AD4" t="n">
-        <v>5295</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>26689</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>12173</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>9447</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>17982</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>12521</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>8395</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>2038</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>8421</v>
-      </c>
-      <c r="AM4" t="n">
+      <c r="AR4" t="n">
+        <v>7097</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>7403</v>
+      </c>
+      <c r="AT4" t="n">
         <v>16259</v>
       </c>
-      <c r="AN4" t="n">
-        <v>10692</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>7097</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>7403</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>4039</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>3604</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>-5698</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>6396</v>
-      </c>
       <c r="AU4" t="n">
-        <v>-1437</v>
+        <v>7381</v>
       </c>
       <c r="AV4" t="n">
         <v>0</v>
       </c>
       <c r="AW4" t="n">
-        <v>11298</v>
+        <v>1548</v>
       </c>
       <c r="AX4" t="n">
         <v>1290</v>
       </c>
       <c r="AY4" t="n">
-        <v>0</v>
+        <v>3047</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>1131</v>
       </c>
       <c r="BA4" t="n">
-        <v>1131</v>
+        <v>10692</v>
       </c>
       <c r="BB4" t="n">
+        <v>11298</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>1299</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>260</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG4" t="n">
         <v>1587</v>
       </c>
-      <c r="BC4" t="n">
-        <v>3047</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>7381</v>
-      </c>
-      <c r="BE4" t="n">
+      <c r="BH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>-867</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>1095</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>3071</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>548</v>
+      </c>
+      <c r="BQ4" t="n">
         <v>848</v>
       </c>
-      <c r="BF4" t="n">
-        <v>1548</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>1095</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ4" t="n">
+      <c r="BR4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>449</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>1711</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW4" t="n">
+        <v>-2399</v>
+      </c>
+      <c r="BX4" t="n">
+        <v>639</v>
+      </c>
+      <c r="BY4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB4" t="n">
+        <v>1199</v>
+      </c>
+      <c r="CC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH4" t="n">
+        <v>2399</v>
+      </c>
+      <c r="CI4" t="n">
+        <v>599</v>
+      </c>
+      <c r="CJ4" t="n">
+        <v>1899</v>
+      </c>
+      <c r="CK4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN4" t="n">
         <v>249</v>
       </c>
-      <c r="BK4" t="n">
-        <v>-867</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>3071</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>260</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO4" t="n">
-        <v>1711</v>
-      </c>
-      <c r="BP4" t="n">
-        <v>449</v>
-      </c>
-      <c r="BQ4" t="n">
-        <v>548</v>
-      </c>
-      <c r="BR4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV4" t="n">
+      <c r="CO4" t="n">
         <v>839</v>
       </c>
-      <c r="BW4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX4" t="n">
-        <v>2399</v>
-      </c>
-      <c r="BY4" t="n">
-        <v>1299</v>
-      </c>
-      <c r="BZ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA4" t="n">
-        <v>1199</v>
-      </c>
-      <c r="CB4" t="n">
-        <v>0</v>
-      </c>
-      <c r="CC4" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD4" t="n">
-        <v>-2399</v>
-      </c>
-      <c r="CE4" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF4" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG4" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH4" t="n">
-        <v>599</v>
-      </c>
-      <c r="CI4" t="n">
-        <v>0</v>
-      </c>
-      <c r="CJ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="CK4" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL4" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM4" t="n">
-        <v>639</v>
-      </c>
-      <c r="CN4" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO4" t="n">
-        <v>0</v>
-      </c>
       <c r="CP4" t="n">
         <v>0</v>
       </c>
       <c r="CQ4" t="n">
-        <v>1899</v>
+        <v>0</v>
       </c>
       <c r="CR4" t="n">
         <v>0</v>
@@ -5819,13 +6151,13 @@
         <v>284221</v>
       </c>
       <c r="CY4" t="n">
+        <v>146118</v>
+      </c>
+      <c r="CZ4" t="n">
+        <v>195921</v>
+      </c>
+      <c r="DA4" t="n">
         <v>421334</v>
-      </c>
-      <c r="CZ4" t="n">
-        <v>146118</v>
-      </c>
-      <c r="DA4" t="n">
-        <v>195921</v>
       </c>
       <c r="DB4" t="n">
         <v>611692</v>
@@ -5837,262 +6169,262 @@
         <v>133734</v>
       </c>
       <c r="DE4" t="n">
+        <v>88729</v>
+      </c>
+      <c r="DF4" t="n">
         <v>55566</v>
       </c>
-      <c r="DF4" t="n">
-        <v>88729</v>
-      </c>
       <c r="DG4" t="n">
+        <v>59143</v>
+      </c>
+      <c r="DH4" t="n">
+        <v>65383</v>
+      </c>
+      <c r="DI4" t="n">
         <v>28642</v>
       </c>
-      <c r="DH4" t="n">
-        <v>59143</v>
-      </c>
-      <c r="DI4" t="n">
-        <v>65383</v>
-      </c>
       <c r="DJ4" t="n">
+        <v>32640</v>
+      </c>
+      <c r="DK4" t="n">
+        <v>37151</v>
+      </c>
+      <c r="DL4" t="n">
         <v>45361</v>
       </c>
-      <c r="DK4" t="n">
-        <v>32640</v>
-      </c>
-      <c r="DL4" t="n">
-        <v>37151</v>
-      </c>
       <c r="DM4" t="n">
-        <v>33785</v>
+        <v>13395</v>
       </c>
       <c r="DN4" t="n">
+        <v>35865</v>
+      </c>
+      <c r="DO4" t="n">
+        <v>10381</v>
+      </c>
+      <c r="DP4" t="n">
         <v>24484</v>
-      </c>
-      <c r="DO4" t="n">
-        <v>13395</v>
-      </c>
-      <c r="DP4" t="n">
-        <v>10381</v>
       </c>
       <c r="DQ4" t="n">
         <v>24187</v>
       </c>
       <c r="DR4" t="n">
-        <v>35865</v>
+        <v>13692</v>
       </c>
       <c r="DS4" t="n">
-        <v>13692</v>
+        <v>22783</v>
       </c>
       <c r="DT4" t="n">
+        <v>27767</v>
+      </c>
+      <c r="DU4" t="n">
+        <v>17982</v>
+      </c>
+      <c r="DV4" t="n">
+        <v>5295</v>
+      </c>
+      <c r="DW4" t="n">
+        <v>17101</v>
+      </c>
+      <c r="DX4" t="n">
+        <v>15111</v>
+      </c>
+      <c r="DY4" t="n">
+        <v>33785</v>
+      </c>
+      <c r="DZ4" t="n">
+        <v>9081</v>
+      </c>
+      <c r="EA4" t="n">
         <v>15894</v>
       </c>
-      <c r="DU4" t="n">
-        <v>22783</v>
-      </c>
-      <c r="DV4" t="n">
-        <v>17101</v>
-      </c>
-      <c r="DW4" t="n">
-        <v>15111</v>
-      </c>
-      <c r="DX4" t="n">
+      <c r="EB4" t="n">
+        <v>13493</v>
+      </c>
+      <c r="EC4" t="n">
+        <v>3398</v>
+      </c>
+      <c r="ED4" t="n">
+        <v>10307</v>
+      </c>
+      <c r="EE4" t="n">
+        <v>13391</v>
+      </c>
+      <c r="EF4" t="n">
+        <v>8395</v>
+      </c>
+      <c r="EG4" t="n">
+        <v>6396</v>
+      </c>
+      <c r="EH4" t="n">
+        <v>-5698</v>
+      </c>
+      <c r="EI4" t="n">
+        <v>4277</v>
+      </c>
+      <c r="EJ4" t="n">
+        <v>3484</v>
+      </c>
+      <c r="EK4" t="n">
+        <v>-4797</v>
+      </c>
+      <c r="EL4" t="n">
         <v>12593</v>
       </c>
-      <c r="DY4" t="n">
-        <v>5295</v>
-      </c>
-      <c r="DZ4" t="n">
-        <v>27767</v>
-      </c>
-      <c r="EA4" t="n">
-        <v>13493</v>
-      </c>
-      <c r="EB4" t="n">
-        <v>10307</v>
-      </c>
-      <c r="EC4" t="n">
-        <v>17982</v>
-      </c>
-      <c r="ED4" t="n">
-        <v>13391</v>
-      </c>
-      <c r="EE4" t="n">
-        <v>8395</v>
-      </c>
-      <c r="EF4" t="n">
-        <v>3398</v>
-      </c>
-      <c r="EG4" t="n">
-        <v>9081</v>
-      </c>
-      <c r="EH4" t="n">
+      <c r="EM4" t="n">
+        <v>7097</v>
+      </c>
+      <c r="EN4" t="n">
+        <v>9043</v>
+      </c>
+      <c r="EO4" t="n">
         <v>19367</v>
       </c>
-      <c r="EI4" t="n">
-        <v>10692</v>
-      </c>
-      <c r="EJ4" t="n">
-        <v>7097</v>
-      </c>
-      <c r="EK4" t="n">
-        <v>9043</v>
-      </c>
-      <c r="EL4" t="n">
-        <v>4277</v>
-      </c>
-      <c r="EM4" t="n">
-        <v>3484</v>
-      </c>
-      <c r="EN4" t="n">
-        <v>-5698</v>
-      </c>
-      <c r="EO4" t="n">
-        <v>6396</v>
-      </c>
       <c r="EP4" t="n">
-        <v>-4797</v>
+        <v>7381</v>
       </c>
       <c r="EQ4" t="n">
         <v>0</v>
       </c>
       <c r="ER4" t="n">
-        <v>11298</v>
+        <v>1548</v>
       </c>
       <c r="ES4" t="n">
         <v>1500</v>
       </c>
       <c r="ET4" t="n">
-        <v>0</v>
+        <v>3047</v>
       </c>
       <c r="EU4" t="n">
-        <v>0</v>
+        <v>1416</v>
       </c>
       <c r="EV4" t="n">
-        <v>1416</v>
+        <v>10692</v>
       </c>
       <c r="EW4" t="n">
+        <v>11298</v>
+      </c>
+      <c r="EX4" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY4" t="n">
+        <v>1299</v>
+      </c>
+      <c r="EZ4" t="n">
+        <v>-300</v>
+      </c>
+      <c r="FA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB4" t="n">
         <v>1587</v>
       </c>
-      <c r="EX4" t="n">
-        <v>3047</v>
-      </c>
-      <c r="EY4" t="n">
-        <v>7381</v>
-      </c>
-      <c r="EZ4" t="n">
+      <c r="FC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE4" t="n">
+        <v>-1737</v>
+      </c>
+      <c r="FF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG4" t="n">
+        <v>1095</v>
+      </c>
+      <c r="FH4" t="n">
+        <v>3071</v>
+      </c>
+      <c r="FI4" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="FK4" t="n">
+        <v>1098</v>
+      </c>
+      <c r="FL4" t="n">
         <v>1698</v>
       </c>
-      <c r="FA4" t="n">
-        <v>1548</v>
-      </c>
-      <c r="FB4" t="n">
-        <v>0</v>
-      </c>
-      <c r="FC4" t="n">
-        <v>1095</v>
-      </c>
-      <c r="FD4" t="n">
-        <v>0</v>
-      </c>
-      <c r="FE4" t="n">
+      <c r="FM4" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN4" t="n">
+        <v>899</v>
+      </c>
+      <c r="FO4" t="n">
+        <v>3507</v>
+      </c>
+      <c r="FP4" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="FR4" t="n">
+        <v>-2399</v>
+      </c>
+      <c r="FS4" t="n">
+        <v>1599</v>
+      </c>
+      <c r="FT4" t="n">
+        <v>0</v>
+      </c>
+      <c r="FU4" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV4" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW4" t="n">
+        <v>2999</v>
+      </c>
+      <c r="FX4" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY4" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="GA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC4" t="n">
+        <v>2399</v>
+      </c>
+      <c r="GD4" t="n">
+        <v>999</v>
+      </c>
+      <c r="GE4" t="n">
+        <v>1899</v>
+      </c>
+      <c r="GF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="GH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="GI4" t="n">
         <v>499</v>
       </c>
-      <c r="FF4" t="n">
-        <v>-1737</v>
-      </c>
-      <c r="FG4" t="n">
-        <v>3071</v>
-      </c>
-      <c r="FH4" t="n">
-        <v>-300</v>
-      </c>
-      <c r="FI4" t="n">
-        <v>0</v>
-      </c>
-      <c r="FJ4" t="n">
-        <v>3507</v>
-      </c>
-      <c r="FK4" t="n">
-        <v>899</v>
-      </c>
-      <c r="FL4" t="n">
-        <v>1098</v>
-      </c>
-      <c r="FM4" t="n">
-        <v>0</v>
-      </c>
-      <c r="FN4" t="n">
-        <v>0</v>
-      </c>
-      <c r="FO4" t="n">
-        <v>0</v>
-      </c>
-      <c r="FP4" t="n">
-        <v>0</v>
-      </c>
-      <c r="FQ4" t="n">
+      <c r="GJ4" t="n">
         <v>1199</v>
       </c>
-      <c r="FR4" t="n">
-        <v>0</v>
-      </c>
-      <c r="FS4" t="n">
-        <v>2399</v>
-      </c>
-      <c r="FT4" t="n">
-        <v>1299</v>
-      </c>
-      <c r="FU4" t="n">
-        <v>0</v>
-      </c>
-      <c r="FV4" t="n">
-        <v>2999</v>
-      </c>
-      <c r="FW4" t="n">
-        <v>0</v>
-      </c>
-      <c r="FX4" t="n">
-        <v>0</v>
-      </c>
-      <c r="FY4" t="n">
-        <v>-2399</v>
-      </c>
-      <c r="FZ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="GA4" t="n">
-        <v>0</v>
-      </c>
-      <c r="GB4" t="n">
-        <v>0</v>
-      </c>
-      <c r="GC4" t="n">
-        <v>999</v>
-      </c>
-      <c r="GD4" t="n">
-        <v>0</v>
-      </c>
-      <c r="GE4" t="n">
-        <v>0</v>
-      </c>
-      <c r="GF4" t="n">
-        <v>0</v>
-      </c>
-      <c r="GG4" t="n">
-        <v>0</v>
-      </c>
-      <c r="GH4" t="n">
-        <v>1599</v>
-      </c>
-      <c r="GI4" t="n">
-        <v>0</v>
-      </c>
-      <c r="GJ4" t="n">
-        <v>0</v>
-      </c>
       <c r="GK4" t="n">
         <v>0</v>
       </c>
       <c r="GL4" t="n">
-        <v>1899</v>
+        <v>0</v>
       </c>
       <c r="GM4" t="n">
         <v>0</v>
@@ -6123,13 +6455,13 @@
         <v>305228</v>
       </c>
       <c r="D5" t="n">
+        <v>140877</v>
+      </c>
+      <c r="E5" t="n">
+        <v>146834</v>
+      </c>
+      <c r="F5" t="n">
         <v>348130</v>
-      </c>
-      <c r="E5" t="n">
-        <v>140877</v>
-      </c>
-      <c r="F5" t="n">
-        <v>146834</v>
       </c>
       <c r="G5" t="n">
         <v>218943</v>
@@ -6141,194 +6473,194 @@
         <v>68046</v>
       </c>
       <c r="J5" t="n">
+        <v>64849</v>
+      </c>
+      <c r="K5" t="n">
         <v>31478</v>
       </c>
-      <c r="K5" t="n">
-        <v>64849</v>
-      </c>
       <c r="L5" t="n">
+        <v>71724</v>
+      </c>
+      <c r="M5" t="n">
+        <v>52813</v>
+      </c>
+      <c r="N5" t="n">
         <v>23849</v>
       </c>
-      <c r="M5" t="n">
-        <v>71724</v>
-      </c>
-      <c r="N5" t="n">
-        <v>52813</v>
-      </c>
       <c r="O5" t="n">
+        <v>48574</v>
+      </c>
+      <c r="P5" t="n">
+        <v>20434</v>
+      </c>
+      <c r="Q5" t="n">
         <v>39293</v>
       </c>
-      <c r="P5" t="n">
-        <v>48574</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>20434</v>
-      </c>
       <c r="R5" t="n">
-        <v>25688</v>
+        <v>-619</v>
       </c>
       <c r="S5" t="n">
+        <v>29494</v>
+      </c>
+      <c r="T5" t="n">
+        <v>22146</v>
+      </c>
+      <c r="U5" t="n">
         <v>35977</v>
-      </c>
-      <c r="T5" t="n">
-        <v>-619</v>
-      </c>
-      <c r="U5" t="n">
-        <v>22146</v>
       </c>
       <c r="V5" t="n">
         <v>16536</v>
       </c>
       <c r="W5" t="n">
-        <v>29494</v>
+        <v>9597</v>
       </c>
       <c r="X5" t="n">
-        <v>9597</v>
+        <v>37875</v>
       </c>
       <c r="Y5" t="n">
+        <v>16503</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>9986</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>12628</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>14483</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>15135</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>25688</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>5148</v>
+      </c>
+      <c r="AF5" t="n">
         <v>28283</v>
       </c>
-      <c r="Z5" t="n">
-        <v>37875</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>14483</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>15135</v>
-      </c>
-      <c r="AC5" t="n">
+      <c r="AG5" t="n">
+        <v>11802</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>2118</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>2017</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>6003</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>6792</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>6883</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>1499</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>3595</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>2970</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>11839</v>
+      </c>
+      <c r="AQ5" t="n">
         <v>8643</v>
       </c>
-      <c r="AD5" t="n">
-        <v>12628</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>16503</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>11802</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>2017</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>9986</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>6003</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>6792</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>2118</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>5148</v>
-      </c>
-      <c r="AM5" t="n">
+      <c r="AR5" t="n">
+        <v>6377</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>13330</v>
+      </c>
+      <c r="AT5" t="n">
         <v>4906</v>
       </c>
-      <c r="AN5" t="n">
-        <v>11716</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>6377</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>13330</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>3595</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>2970</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>1499</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>6883</v>
-      </c>
       <c r="AU5" t="n">
-        <v>11839</v>
+        <v>2265</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>5199</v>
       </c>
       <c r="AW5" t="n">
-        <v>0</v>
+        <v>2197</v>
       </c>
       <c r="AX5" t="n">
         <v>2959</v>
       </c>
       <c r="AY5" t="n">
-        <v>5199</v>
+        <v>5812</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>-95</v>
       </c>
       <c r="BA5" t="n">
-        <v>-95</v>
+        <v>11716</v>
       </c>
       <c r="BB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>5596</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG5" t="n">
         <v>2961</v>
       </c>
-      <c r="BC5" t="n">
-        <v>5812</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>2265</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>2197</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>0</v>
-      </c>
       <c r="BH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>-1647</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL5" t="n">
         <v>825</v>
       </c>
-      <c r="BI5" t="n">
+      <c r="BM5" t="n">
+        <v>1516</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO5" t="n">
         <v>798</v>
       </c>
-      <c r="BJ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>1516</v>
-      </c>
-      <c r="BM5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO5" t="n">
+      <c r="BP5" t="n">
+        <v>299</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT5" t="n">
         <v>-478</v>
       </c>
-      <c r="BP5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ5" t="n">
-        <v>299</v>
-      </c>
-      <c r="BR5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT5" t="n">
-        <v>0</v>
-      </c>
       <c r="BU5" t="n">
         <v>0</v>
       </c>
@@ -6342,7 +6674,7 @@
         <v>0</v>
       </c>
       <c r="BY5" t="n">
-        <v>5596</v>
+        <v>0</v>
       </c>
       <c r="BZ5" t="n">
         <v>0</v>
@@ -6375,10 +6707,10 @@
         <v>0</v>
       </c>
       <c r="CJ5" t="n">
-        <v>0</v>
+        <v>2199</v>
       </c>
       <c r="CK5" t="n">
-        <v>-1647</v>
+        <v>0</v>
       </c>
       <c r="CL5" t="n">
         <v>0</v>
@@ -6396,7 +6728,7 @@
         <v>0</v>
       </c>
       <c r="CQ5" t="n">
-        <v>2199</v>
+        <v>0</v>
       </c>
       <c r="CR5" t="n">
         <v>0</v>
@@ -6420,13 +6752,13 @@
         <v>417778</v>
       </c>
       <c r="CY5" t="n">
+        <v>178540</v>
+      </c>
+      <c r="CZ5" t="n">
+        <v>174182</v>
+      </c>
+      <c r="DA5" t="n">
         <v>358578</v>
-      </c>
-      <c r="CZ5" t="n">
-        <v>178540</v>
-      </c>
-      <c r="DA5" t="n">
-        <v>174182</v>
       </c>
       <c r="DB5" t="n">
         <v>239043</v>
@@ -6438,194 +6770,194 @@
         <v>83393</v>
       </c>
       <c r="DE5" t="n">
+        <v>79071</v>
+      </c>
+      <c r="DF5" t="n">
         <v>48268</v>
       </c>
-      <c r="DF5" t="n">
-        <v>79071</v>
-      </c>
       <c r="DG5" t="n">
+        <v>101111</v>
+      </c>
+      <c r="DH5" t="n">
+        <v>70250</v>
+      </c>
+      <c r="DI5" t="n">
         <v>27595</v>
       </c>
-      <c r="DH5" t="n">
-        <v>101111</v>
-      </c>
-      <c r="DI5" t="n">
-        <v>70250</v>
-      </c>
       <c r="DJ5" t="n">
+        <v>64527</v>
+      </c>
+      <c r="DK5" t="n">
+        <v>23414</v>
+      </c>
+      <c r="DL5" t="n">
         <v>39293</v>
       </c>
-      <c r="DK5" t="n">
-        <v>64527</v>
-      </c>
-      <c r="DL5" t="n">
-        <v>23414</v>
-      </c>
       <c r="DM5" t="n">
-        <v>25688</v>
+        <v>-6299</v>
       </c>
       <c r="DN5" t="n">
+        <v>43554</v>
+      </c>
+      <c r="DO5" t="n">
+        <v>28063</v>
+      </c>
+      <c r="DP5" t="n">
         <v>35977</v>
-      </c>
-      <c r="DO5" t="n">
-        <v>-6299</v>
-      </c>
-      <c r="DP5" t="n">
-        <v>28063</v>
       </c>
       <c r="DQ5" t="n">
         <v>24768</v>
       </c>
       <c r="DR5" t="n">
-        <v>43554</v>
+        <v>9597</v>
       </c>
       <c r="DS5" t="n">
-        <v>9597</v>
+        <v>55415</v>
       </c>
       <c r="DT5" t="n">
+        <v>24721</v>
+      </c>
+      <c r="DU5" t="n">
+        <v>13986</v>
+      </c>
+      <c r="DV5" t="n">
+        <v>16588</v>
+      </c>
+      <c r="DW5" t="n">
+        <v>14658</v>
+      </c>
+      <c r="DX5" t="n">
+        <v>20655</v>
+      </c>
+      <c r="DY5" t="n">
+        <v>25688</v>
+      </c>
+      <c r="DZ5" t="n">
+        <v>5798</v>
+      </c>
+      <c r="EA5" t="n">
         <v>28283</v>
       </c>
-      <c r="DU5" t="n">
-        <v>55415</v>
-      </c>
-      <c r="DV5" t="n">
-        <v>14658</v>
-      </c>
-      <c r="DW5" t="n">
-        <v>20655</v>
-      </c>
-      <c r="DX5" t="n">
+      <c r="EB5" t="n">
+        <v>14092</v>
+      </c>
+      <c r="EC5" t="n">
+        <v>2798</v>
+      </c>
+      <c r="ED5" t="n">
+        <v>2417</v>
+      </c>
+      <c r="EE5" t="n">
+        <v>8193</v>
+      </c>
+      <c r="EF5" t="n">
+        <v>13592</v>
+      </c>
+      <c r="EG5" t="n">
+        <v>9793</v>
+      </c>
+      <c r="EH5" t="n">
+        <v>1499</v>
+      </c>
+      <c r="EI5" t="n">
+        <v>5780</v>
+      </c>
+      <c r="EJ5" t="n">
+        <v>3197</v>
+      </c>
+      <c r="EK5" t="n">
+        <v>13039</v>
+      </c>
+      <c r="EL5" t="n">
         <v>11193</v>
       </c>
-      <c r="DY5" t="n">
-        <v>16588</v>
-      </c>
-      <c r="DZ5" t="n">
-        <v>24721</v>
-      </c>
-      <c r="EA5" t="n">
-        <v>14092</v>
-      </c>
-      <c r="EB5" t="n">
-        <v>2417</v>
-      </c>
-      <c r="EC5" t="n">
-        <v>13986</v>
-      </c>
-      <c r="ED5" t="n">
-        <v>8193</v>
-      </c>
-      <c r="EE5" t="n">
-        <v>13592</v>
-      </c>
-      <c r="EF5" t="n">
-        <v>2798</v>
-      </c>
-      <c r="EG5" t="n">
-        <v>5798</v>
-      </c>
-      <c r="EH5" t="n">
+      <c r="EM5" t="n">
+        <v>9197</v>
+      </c>
+      <c r="EN5" t="n">
+        <v>23235</v>
+      </c>
+      <c r="EO5" t="n">
         <v>8248</v>
       </c>
-      <c r="EI5" t="n">
-        <v>18286</v>
-      </c>
-      <c r="EJ5" t="n">
-        <v>9197</v>
-      </c>
-      <c r="EK5" t="n">
-        <v>23235</v>
-      </c>
-      <c r="EL5" t="n">
-        <v>5780</v>
-      </c>
-      <c r="EM5" t="n">
-        <v>3197</v>
-      </c>
-      <c r="EN5" t="n">
-        <v>1499</v>
-      </c>
-      <c r="EO5" t="n">
-        <v>9793</v>
-      </c>
       <c r="EP5" t="n">
-        <v>13039</v>
+        <v>2265</v>
       </c>
       <c r="EQ5" t="n">
-        <v>0</v>
+        <v>5199</v>
       </c>
       <c r="ER5" t="n">
-        <v>0</v>
+        <v>2197</v>
       </c>
       <c r="ES5" t="n">
         <v>5100</v>
       </c>
       <c r="ET5" t="n">
-        <v>5199</v>
+        <v>8492</v>
       </c>
       <c r="EU5" t="n">
-        <v>0</v>
+        <v>-310</v>
       </c>
       <c r="EV5" t="n">
-        <v>-310</v>
+        <v>18286</v>
       </c>
       <c r="EW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY5" t="n">
+        <v>5596</v>
+      </c>
+      <c r="EZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB5" t="n">
         <v>4051</v>
       </c>
-      <c r="EX5" t="n">
-        <v>8492</v>
-      </c>
-      <c r="EY5" t="n">
-        <v>2265</v>
-      </c>
-      <c r="EZ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="FA5" t="n">
-        <v>2197</v>
-      </c>
-      <c r="FB5" t="n">
-        <v>0</v>
-      </c>
       <c r="FC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD5" t="n">
+        <v>-3297</v>
+      </c>
+      <c r="FE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG5" t="n">
         <v>1065</v>
       </c>
-      <c r="FD5" t="n">
+      <c r="FH5" t="n">
+        <v>2212</v>
+      </c>
+      <c r="FI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ5" t="n">
         <v>1600</v>
       </c>
-      <c r="FE5" t="n">
-        <v>0</v>
-      </c>
-      <c r="FF5" t="n">
-        <v>0</v>
-      </c>
-      <c r="FG5" t="n">
-        <v>2212</v>
-      </c>
-      <c r="FH5" t="n">
-        <v>0</v>
-      </c>
-      <c r="FI5" t="n">
-        <v>0</v>
-      </c>
-      <c r="FJ5" t="n">
+      <c r="FK5" t="n">
+        <v>599</v>
+      </c>
+      <c r="FL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO5" t="n">
         <v>-1368</v>
       </c>
-      <c r="FK5" t="n">
-        <v>0</v>
-      </c>
-      <c r="FL5" t="n">
-        <v>599</v>
-      </c>
-      <c r="FM5" t="n">
-        <v>0</v>
-      </c>
-      <c r="FN5" t="n">
-        <v>0</v>
-      </c>
-      <c r="FO5" t="n">
-        <v>0</v>
-      </c>
       <c r="FP5" t="n">
         <v>0</v>
       </c>
@@ -6639,7 +6971,7 @@
         <v>0</v>
       </c>
       <c r="FT5" t="n">
-        <v>5596</v>
+        <v>0</v>
       </c>
       <c r="FU5" t="n">
         <v>0</v>
@@ -6672,10 +7004,10 @@
         <v>0</v>
       </c>
       <c r="GE5" t="n">
-        <v>0</v>
+        <v>2199</v>
       </c>
       <c r="GF5" t="n">
-        <v>-3297</v>
+        <v>0</v>
       </c>
       <c r="GG5" t="n">
         <v>0</v>
@@ -6693,7 +7025,7 @@
         <v>0</v>
       </c>
       <c r="GL5" t="n">
-        <v>2199</v>
+        <v>0</v>
       </c>
       <c r="GM5" t="n">
         <v>0</v>
@@ -7325,13 +7657,13 @@
         <v>400117</v>
       </c>
       <c r="D7" t="n">
+        <v>176948</v>
+      </c>
+      <c r="E7" t="n">
+        <v>163510</v>
+      </c>
+      <c r="F7" t="n">
         <v>232688</v>
-      </c>
-      <c r="E7" t="n">
-        <v>176948</v>
-      </c>
-      <c r="F7" t="n">
-        <v>163510</v>
       </c>
       <c r="G7" t="n">
         <v>155807</v>
@@ -7343,253 +7675,253 @@
         <v>100681</v>
       </c>
       <c r="J7" t="n">
+        <v>98192</v>
+      </c>
+      <c r="K7" t="n">
         <v>100229</v>
       </c>
-      <c r="K7" t="n">
-        <v>98192</v>
-      </c>
       <c r="L7" t="n">
+        <v>66595</v>
+      </c>
+      <c r="M7" t="n">
+        <v>54388</v>
+      </c>
+      <c r="N7" t="n">
         <v>69600</v>
       </c>
-      <c r="M7" t="n">
-        <v>66595</v>
-      </c>
-      <c r="N7" t="n">
-        <v>54388</v>
-      </c>
       <c r="O7" t="n">
+        <v>36382</v>
+      </c>
+      <c r="P7" t="n">
+        <v>33273</v>
+      </c>
+      <c r="Q7" t="n">
         <v>37393</v>
       </c>
-      <c r="P7" t="n">
-        <v>36382</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>33273</v>
-      </c>
       <c r="R7" t="n">
-        <v>32985</v>
+        <v>26516</v>
       </c>
       <c r="S7" t="n">
+        <v>20072</v>
+      </c>
+      <c r="T7" t="n">
+        <v>20968</v>
+      </c>
+      <c r="U7" t="n">
         <v>26885</v>
-      </c>
-      <c r="T7" t="n">
-        <v>26516</v>
-      </c>
-      <c r="U7" t="n">
-        <v>20968</v>
       </c>
       <c r="V7" t="n">
         <v>20223</v>
       </c>
       <c r="W7" t="n">
-        <v>20072</v>
+        <v>18696</v>
       </c>
       <c r="X7" t="n">
-        <v>18696</v>
+        <v>15338</v>
       </c>
       <c r="Y7" t="n">
+        <v>10865</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>9786</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>11064</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>14273</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>13371</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>32985</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>6155</v>
+      </c>
+      <c r="AF7" t="n">
         <v>16192</v>
       </c>
-      <c r="Z7" t="n">
-        <v>15338</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>14273</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>13371</v>
-      </c>
-      <c r="AC7" t="n">
+      <c r="AG7" t="n">
+        <v>9974</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>7693</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>9851</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>9442</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>7911</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>2947</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>3798</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>4793</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>4321</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>2777</v>
+      </c>
+      <c r="AQ7" t="n">
         <v>13171</v>
       </c>
-      <c r="AD7" t="n">
-        <v>11064</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>10865</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>9974</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>9851</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>9786</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>9442</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>7911</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>7693</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>6155</v>
-      </c>
-      <c r="AM7" t="n">
+      <c r="AR7" t="n">
+        <v>4998</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>4827</v>
+      </c>
+      <c r="AT7" t="n">
         <v>5546</v>
       </c>
-      <c r="AN7" t="n">
-        <v>5464</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>4998</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>4827</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>4793</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>4321</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>3798</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>2947</v>
-      </c>
       <c r="AU7" t="n">
-        <v>2777</v>
+        <v>1596</v>
       </c>
       <c r="AV7" t="n">
-        <v>2449</v>
+        <v>2030</v>
       </c>
       <c r="AW7" t="n">
-        <v>2399</v>
+        <v>1398</v>
       </c>
       <c r="AX7" t="n">
         <v>2126</v>
       </c>
       <c r="AY7" t="n">
-        <v>2030</v>
+        <v>1691</v>
       </c>
       <c r="AZ7" t="n">
+        <v>1989</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>5464</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>2399</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>2449</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>549</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>1765</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>1258</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>807</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>1154</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>645</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>998</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>1556</v>
+      </c>
+      <c r="BR7" t="n">
         <v>2028</v>
       </c>
-      <c r="BA7" t="n">
-        <v>1989</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>1765</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>1691</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>1596</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>1556</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>1398</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>1258</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>1154</v>
-      </c>
-      <c r="BI7" t="n">
-        <v>998</v>
-      </c>
-      <c r="BJ7" t="n">
+      <c r="BS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>119</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>279</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN7" t="n">
         <v>937</v>
-      </c>
-      <c r="BK7" t="n">
-        <v>807</v>
-      </c>
-      <c r="BL7" t="n">
-        <v>645</v>
-      </c>
-      <c r="BM7" t="n">
-        <v>549</v>
-      </c>
-      <c r="BN7" t="n">
-        <v>279</v>
-      </c>
-      <c r="BO7" t="n">
-        <v>119</v>
-      </c>
-      <c r="BP7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA7" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB7" t="n">
-        <v>0</v>
-      </c>
-      <c r="CC7" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD7" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE7" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF7" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG7" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH7" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI7" t="n">
-        <v>0</v>
-      </c>
-      <c r="CJ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="CK7" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL7" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM7" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN7" t="n">
-        <v>0</v>
       </c>
       <c r="CO7" t="n">
         <v>0</v>
@@ -7622,13 +7954,13 @@
         <v>580302</v>
       </c>
       <c r="CY7" t="n">
+        <v>214151</v>
+      </c>
+      <c r="CZ7" t="n">
+        <v>194614</v>
+      </c>
+      <c r="DA7" t="n">
         <v>277883</v>
-      </c>
-      <c r="CZ7" t="n">
-        <v>214151</v>
-      </c>
-      <c r="DA7" t="n">
-        <v>194614</v>
       </c>
       <c r="DB7" t="n">
         <v>165047</v>
@@ -7640,254 +7972,254 @@
         <v>134473</v>
       </c>
       <c r="DE7" t="n">
+        <v>114412</v>
+      </c>
+      <c r="DF7" t="n">
         <v>137365</v>
       </c>
-      <c r="DF7" t="n">
-        <v>114412</v>
-      </c>
       <c r="DG7" t="n">
+        <v>82332</v>
+      </c>
+      <c r="DH7" t="n">
+        <v>75466</v>
+      </c>
+      <c r="DI7" t="n">
         <v>77171</v>
       </c>
-      <c r="DH7" t="n">
-        <v>82332</v>
-      </c>
-      <c r="DI7" t="n">
-        <v>75466</v>
-      </c>
       <c r="DJ7" t="n">
+        <v>44415</v>
+      </c>
+      <c r="DK7" t="n">
+        <v>42193</v>
+      </c>
+      <c r="DL7" t="n">
         <v>37393</v>
       </c>
-      <c r="DK7" t="n">
-        <v>44415</v>
-      </c>
-      <c r="DL7" t="n">
-        <v>42193</v>
-      </c>
       <c r="DM7" t="n">
-        <v>32985</v>
+        <v>41586</v>
       </c>
       <c r="DN7" t="n">
+        <v>27272</v>
+      </c>
+      <c r="DO7" t="n">
+        <v>23058</v>
+      </c>
+      <c r="DP7" t="n">
         <v>26885</v>
-      </c>
-      <c r="DO7" t="n">
-        <v>41586</v>
-      </c>
-      <c r="DP7" t="n">
-        <v>23058</v>
       </c>
       <c r="DQ7" t="n">
         <v>29183</v>
       </c>
       <c r="DR7" t="n">
-        <v>27272</v>
+        <v>18696</v>
       </c>
       <c r="DS7" t="n">
-        <v>18696</v>
+        <v>21938</v>
       </c>
       <c r="DT7" t="n">
+        <v>17585</v>
+      </c>
+      <c r="DU7" t="n">
+        <v>13986</v>
+      </c>
+      <c r="DV7" t="n">
+        <v>12384</v>
+      </c>
+      <c r="DW7" t="n">
+        <v>14658</v>
+      </c>
+      <c r="DX7" t="n">
+        <v>16711</v>
+      </c>
+      <c r="DY7" t="n">
+        <v>32985</v>
+      </c>
+      <c r="DZ7" t="n">
+        <v>6795</v>
+      </c>
+      <c r="EA7" t="n">
         <v>16192</v>
       </c>
-      <c r="DU7" t="n">
-        <v>21938</v>
-      </c>
-      <c r="DV7" t="n">
-        <v>14658</v>
-      </c>
-      <c r="DW7" t="n">
-        <v>16711</v>
-      </c>
-      <c r="DX7" t="n">
+      <c r="EB7" t="n">
+        <v>10394</v>
+      </c>
+      <c r="EC7" t="n">
+        <v>7693</v>
+      </c>
+      <c r="ED7" t="n">
+        <v>10607</v>
+      </c>
+      <c r="EE7" t="n">
+        <v>13142</v>
+      </c>
+      <c r="EF7" t="n">
+        <v>15191</v>
+      </c>
+      <c r="EG7" t="n">
+        <v>5297</v>
+      </c>
+      <c r="EH7" t="n">
+        <v>3798</v>
+      </c>
+      <c r="EI7" t="n">
+        <v>4793</v>
+      </c>
+      <c r="EJ7" t="n">
+        <v>4501</v>
+      </c>
+      <c r="EK7" t="n">
+        <v>3897</v>
+      </c>
+      <c r="EL7" t="n">
         <v>16491</v>
       </c>
-      <c r="DY7" t="n">
-        <v>12384</v>
-      </c>
-      <c r="DZ7" t="n">
-        <v>17585</v>
-      </c>
-      <c r="EA7" t="n">
-        <v>10394</v>
-      </c>
-      <c r="EB7" t="n">
-        <v>10607</v>
-      </c>
-      <c r="EC7" t="n">
-        <v>13986</v>
-      </c>
-      <c r="ED7" t="n">
-        <v>13142</v>
-      </c>
-      <c r="EE7" t="n">
-        <v>15191</v>
-      </c>
-      <c r="EF7" t="n">
-        <v>7693</v>
-      </c>
-      <c r="EG7" t="n">
-        <v>6795</v>
-      </c>
-      <c r="EH7" t="n">
+      <c r="EM7" t="n">
+        <v>4998</v>
+      </c>
+      <c r="EN7" t="n">
+        <v>9642</v>
+      </c>
+      <c r="EO7" t="n">
         <v>8694</v>
       </c>
-      <c r="EI7" t="n">
-        <v>7494</v>
-      </c>
-      <c r="EJ7" t="n">
-        <v>4998</v>
-      </c>
-      <c r="EK7" t="n">
-        <v>9642</v>
-      </c>
-      <c r="EL7" t="n">
-        <v>4793</v>
-      </c>
-      <c r="EM7" t="n">
-        <v>4501</v>
-      </c>
-      <c r="EN7" t="n">
-        <v>3798</v>
-      </c>
-      <c r="EO7" t="n">
-        <v>5297</v>
-      </c>
       <c r="EP7" t="n">
-        <v>3897</v>
+        <v>1596</v>
       </c>
       <c r="EQ7" t="n">
-        <v>3499</v>
+        <v>2900</v>
       </c>
       <c r="ER7" t="n">
-        <v>4799</v>
+        <v>1398</v>
       </c>
       <c r="ES7" t="n">
         <v>3198</v>
       </c>
       <c r="ET7" t="n">
-        <v>2900</v>
+        <v>3146</v>
       </c>
       <c r="EU7" t="n">
+        <v>2204</v>
+      </c>
+      <c r="EV7" t="n">
+        <v>7494</v>
+      </c>
+      <c r="EW7" t="n">
+        <v>4799</v>
+      </c>
+      <c r="EX7" t="n">
+        <v>3499</v>
+      </c>
+      <c r="EY7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EZ7" t="n">
+        <v>1099</v>
+      </c>
+      <c r="FA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB7" t="n">
+        <v>2325</v>
+      </c>
+      <c r="FC7" t="n">
+        <v>1798</v>
+      </c>
+      <c r="FD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE7" t="n">
+        <v>1617</v>
+      </c>
+      <c r="FF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG7" t="n">
+        <v>1414</v>
+      </c>
+      <c r="FH7" t="n">
+        <v>645</v>
+      </c>
+      <c r="FI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ7" t="n">
+        <v>2000</v>
+      </c>
+      <c r="FK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FL7" t="n">
+        <v>3296</v>
+      </c>
+      <c r="FM7" t="n">
         <v>2298</v>
       </c>
-      <c r="EV7" t="n">
-        <v>2204</v>
-      </c>
-      <c r="EW7" t="n">
-        <v>2325</v>
-      </c>
-      <c r="EX7" t="n">
-        <v>3146</v>
-      </c>
-      <c r="EY7" t="n">
-        <v>1596</v>
-      </c>
-      <c r="EZ7" t="n">
-        <v>3296</v>
-      </c>
-      <c r="FA7" t="n">
-        <v>1398</v>
-      </c>
-      <c r="FB7" t="n">
-        <v>1798</v>
-      </c>
-      <c r="FC7" t="n">
-        <v>1414</v>
-      </c>
-      <c r="FD7" t="n">
-        <v>2000</v>
-      </c>
-      <c r="FE7" t="n">
+      <c r="FN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO7" t="n">
+        <v>300</v>
+      </c>
+      <c r="FP7" t="n">
+        <v>399</v>
+      </c>
+      <c r="FQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="GA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="GH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="GI7" t="n">
         <v>2198</v>
       </c>
-      <c r="FF7" t="n">
-        <v>1617</v>
-      </c>
-      <c r="FG7" t="n">
-        <v>645</v>
-      </c>
-      <c r="FH7" t="n">
-        <v>1099</v>
-      </c>
-      <c r="FI7" t="n">
-        <v>399</v>
-      </c>
-      <c r="FJ7" t="n">
-        <v>300</v>
-      </c>
-      <c r="FK7" t="n">
-        <v>0</v>
-      </c>
-      <c r="FL7" t="n">
-        <v>0</v>
-      </c>
-      <c r="FM7" t="n">
-        <v>0</v>
-      </c>
-      <c r="FN7" t="n">
-        <v>0</v>
-      </c>
-      <c r="FO7" t="n">
-        <v>0</v>
-      </c>
-      <c r="FP7" t="n">
-        <v>0</v>
-      </c>
-      <c r="FQ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="FR7" t="n">
-        <v>0</v>
-      </c>
-      <c r="FS7" t="n">
-        <v>0</v>
-      </c>
-      <c r="FT7" t="n">
-        <v>0</v>
-      </c>
-      <c r="FU7" t="n">
-        <v>0</v>
-      </c>
-      <c r="FV7" t="n">
-        <v>0</v>
-      </c>
-      <c r="FW7" t="n">
-        <v>0</v>
-      </c>
-      <c r="FX7" t="n">
-        <v>0</v>
-      </c>
-      <c r="FY7" t="n">
-        <v>0</v>
-      </c>
-      <c r="FZ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="GA7" t="n">
-        <v>0</v>
-      </c>
-      <c r="GB7" t="n">
-        <v>0</v>
-      </c>
-      <c r="GC7" t="n">
-        <v>0</v>
-      </c>
-      <c r="GD7" t="n">
-        <v>0</v>
-      </c>
-      <c r="GE7" t="n">
-        <v>0</v>
-      </c>
-      <c r="GF7" t="n">
-        <v>0</v>
-      </c>
-      <c r="GG7" t="n">
-        <v>0</v>
-      </c>
-      <c r="GH7" t="n">
-        <v>0</v>
-      </c>
-      <c r="GI7" t="n">
-        <v>0</v>
-      </c>
       <c r="GJ7" t="n">
         <v>0</v>
       </c>
@@ -7910,6 +8242,607 @@
         <v>0</v>
       </c>
       <c r="GQ7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>3900024</v>
+      </c>
+      <c r="C8" t="n">
+        <v>345471</v>
+      </c>
+      <c r="D8" t="n">
+        <v>269182</v>
+      </c>
+      <c r="E8" t="n">
+        <v>259781</v>
+      </c>
+      <c r="F8" t="n">
+        <v>248970</v>
+      </c>
+      <c r="G8" t="n">
+        <v>237455</v>
+      </c>
+      <c r="H8" t="n">
+        <v>188277</v>
+      </c>
+      <c r="I8" t="n">
+        <v>142125</v>
+      </c>
+      <c r="J8" t="n">
+        <v>139902</v>
+      </c>
+      <c r="K8" t="n">
+        <v>120509</v>
+      </c>
+      <c r="L8" t="n">
+        <v>113889</v>
+      </c>
+      <c r="M8" t="n">
+        <v>101504</v>
+      </c>
+      <c r="N8" t="n">
+        <v>83214</v>
+      </c>
+      <c r="O8" t="n">
+        <v>83058</v>
+      </c>
+      <c r="P8" t="n">
+        <v>52950</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>48747</v>
+      </c>
+      <c r="R8" t="n">
+        <v>46788</v>
+      </c>
+      <c r="S8" t="n">
+        <v>40072</v>
+      </c>
+      <c r="T8" t="n">
+        <v>31042</v>
+      </c>
+      <c r="U8" t="n">
+        <v>29677</v>
+      </c>
+      <c r="V8" t="n">
+        <v>29034</v>
+      </c>
+      <c r="W8" t="n">
+        <v>25813</v>
+      </c>
+      <c r="X8" t="n">
+        <v>25807</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>24314</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>21968</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>21689</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>20205</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>18044</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>17192</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>16507</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>13589</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>13572</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>13108</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>12205</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>11971</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>11646</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>10718</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>9494</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>9374</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>9194</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>8492</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>7922</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>7876</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>7831</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>6212</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>6144</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>5899</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>5412</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>4880</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>4223</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>3659</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>3198</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>2399</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>2099</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>1499</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>1428</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>1198</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>1197</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>1118</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>1098</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>1086</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>849</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>685</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>684</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>599</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>599</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>598</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>596</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>559</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>499</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>334</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>329</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW8" t="n">
+        <v>4860186</v>
+      </c>
+      <c r="CX8" t="n">
+        <v>468949</v>
+      </c>
+      <c r="CY8" t="n">
+        <v>322883</v>
+      </c>
+      <c r="CZ8" t="n">
+        <v>303333</v>
+      </c>
+      <c r="DA8" t="n">
+        <v>295027</v>
+      </c>
+      <c r="DB8" t="n">
+        <v>255345</v>
+      </c>
+      <c r="DC8" t="n">
+        <v>223322</v>
+      </c>
+      <c r="DD8" t="n">
+        <v>191373</v>
+      </c>
+      <c r="DE8" t="n">
+        <v>163177</v>
+      </c>
+      <c r="DF8" t="n">
+        <v>177289</v>
+      </c>
+      <c r="DG8" t="n">
+        <v>172781</v>
+      </c>
+      <c r="DH8" t="n">
+        <v>140542</v>
+      </c>
+      <c r="DI8" t="n">
+        <v>92292</v>
+      </c>
+      <c r="DJ8" t="n">
+        <v>111567</v>
+      </c>
+      <c r="DK8" t="n">
+        <v>65510</v>
+      </c>
+      <c r="DL8" t="n">
+        <v>48747</v>
+      </c>
+      <c r="DM8" t="n">
+        <v>60378</v>
+      </c>
+      <c r="DN8" t="n">
+        <v>52252</v>
+      </c>
+      <c r="DO8" t="n">
+        <v>38221</v>
+      </c>
+      <c r="DP8" t="n">
+        <v>29677</v>
+      </c>
+      <c r="DQ8" t="n">
+        <v>46274</v>
+      </c>
+      <c r="DR8" t="n">
+        <v>27132</v>
+      </c>
+      <c r="DS8" t="n">
+        <v>37177</v>
+      </c>
+      <c r="DT8" t="n">
+        <v>37040</v>
+      </c>
+      <c r="DU8" t="n">
+        <v>31968</v>
+      </c>
+      <c r="DV8" t="n">
+        <v>32019</v>
+      </c>
+      <c r="DW8" t="n">
+        <v>20940</v>
+      </c>
+      <c r="DX8" t="n">
+        <v>21904</v>
+      </c>
+      <c r="DY8" t="n">
+        <v>17192</v>
+      </c>
+      <c r="DZ8" t="n">
+        <v>17447</v>
+      </c>
+      <c r="EA8" t="n">
+        <v>13589</v>
+      </c>
+      <c r="EB8" t="n">
+        <v>16192</v>
+      </c>
+      <c r="EC8" t="n">
+        <v>13788</v>
+      </c>
+      <c r="ED8" t="n">
+        <v>12665</v>
+      </c>
+      <c r="EE8" t="n">
+        <v>16491</v>
+      </c>
+      <c r="EF8" t="n">
+        <v>22986</v>
+      </c>
+      <c r="EG8" t="n">
+        <v>18088</v>
+      </c>
+      <c r="EH8" t="n">
+        <v>9494</v>
+      </c>
+      <c r="EI8" t="n">
+        <v>12068</v>
+      </c>
+      <c r="EJ8" t="n">
+        <v>9513</v>
+      </c>
+      <c r="EK8" t="n">
+        <v>9092</v>
+      </c>
+      <c r="EL8" t="n">
+        <v>12992</v>
+      </c>
+      <c r="EM8" t="n">
+        <v>9996</v>
+      </c>
+      <c r="EN8" t="n">
+        <v>13686</v>
+      </c>
+      <c r="EO8" t="n">
+        <v>9045</v>
+      </c>
+      <c r="EP8" t="n">
+        <v>6144</v>
+      </c>
+      <c r="EQ8" t="n">
+        <v>5899</v>
+      </c>
+      <c r="ER8" t="n">
+        <v>5892</v>
+      </c>
+      <c r="ES8" t="n">
+        <v>6996</v>
+      </c>
+      <c r="ET8" t="n">
+        <v>6193</v>
+      </c>
+      <c r="EU8" t="n">
+        <v>3659</v>
+      </c>
+      <c r="EV8" t="n">
+        <v>3198</v>
+      </c>
+      <c r="EW8" t="n">
+        <v>4799</v>
+      </c>
+      <c r="EX8" t="n">
+        <v>2999</v>
+      </c>
+      <c r="EY8" t="n">
+        <v>1499</v>
+      </c>
+      <c r="EZ8" t="n">
+        <v>2498</v>
+      </c>
+      <c r="FA8" t="n">
+        <v>1998</v>
+      </c>
+      <c r="FB8" t="n">
+        <v>1547</v>
+      </c>
+      <c r="FC8" t="n">
+        <v>1598</v>
+      </c>
+      <c r="FD8" t="n">
+        <v>2198</v>
+      </c>
+      <c r="FE8" t="n">
+        <v>2176</v>
+      </c>
+      <c r="FF8" t="n">
+        <v>1699</v>
+      </c>
+      <c r="FG8" t="n">
+        <v>945</v>
+      </c>
+      <c r="FH8" t="n">
+        <v>684</v>
+      </c>
+      <c r="FI8" t="n">
+        <v>1999</v>
+      </c>
+      <c r="FJ8" t="n">
+        <v>1200</v>
+      </c>
+      <c r="FK8" t="n">
+        <v>1198</v>
+      </c>
+      <c r="FL8" t="n">
+        <v>2796</v>
+      </c>
+      <c r="FM8" t="n">
+        <v>799</v>
+      </c>
+      <c r="FN8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="FO8" t="n">
+        <v>669</v>
+      </c>
+      <c r="FP8" t="n">
+        <v>549</v>
+      </c>
+      <c r="FQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GQ8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7924,7 +8857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -8121,6 +9054,31 @@
       </c>
       <c r="G7" t="n">
         <v>775</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>6118912</v>
+      </c>
+      <c r="C8" t="n">
+        <v>790368</v>
+      </c>
+      <c r="D8" t="n">
+        <v>7607988</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1026473</v>
+      </c>
+      <c r="F8" t="n">
+        <v>15943</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1405</v>
       </c>
     </row>
   </sheetData>
